--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/semantic-engine/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/semantic-engine/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0ED3C4-8465-1E43-BFDC-D1C55C6120F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F797B11D-33A9-8A42-8E30-36B76597FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21460" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="176">
   <si>
     <t>essere</t>
   </si>
@@ -106,9 +106,6 @@
     <t>vB</t>
   </si>
   <si>
-    <t>Brainstorming</t>
-  </si>
-  <si>
     <t>Vettori semantici: su vettore fisso o su vettore mobile?</t>
   </si>
   <si>
@@ -278,9 +275,6 @@
   </si>
   <si>
     <t>Note</t>
-  </si>
-  <si>
-    <t>Concetti chiave SSLM (Smart Semantic Language Model)</t>
   </si>
   <si>
     <t>base</t>
@@ -482,9 +476,6 @@
   </si>
   <si>
     <t>quando</t>
-  </si>
-  <si>
-    <t>vocabulary (db)</t>
   </si>
   <si>
     <t xml:space="preserve">rappresenta la tabella delle parole base + le estese (a coprire tutti I vocabolari, multilingua). </t>
@@ -692,6 +683,21 @@
   </si>
   <si>
     <t>NLTK!!! Super libreria di linguaggio naturale</t>
+  </si>
+  <si>
+    <t>Concetti chiave SSLM (Smart Semantic Language Model) : TokenKino</t>
+  </si>
+  <si>
+    <t>dictionary (db)</t>
+  </si>
+  <si>
+    <t>places (db)</t>
+  </si>
+  <si>
+    <t>events (db)</t>
+  </si>
+  <si>
+    <t>names (db)</t>
   </si>
 </sst>
 </file>
@@ -988,6 +994,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -996,9 +1005,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1340,7 +1346,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B2:N52"/>
+  <dimension ref="B2:N58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="21" customWidth="1"/>
@@ -1357,24 +1363,24 @@
   <sheetData>
     <row r="2" spans="2:12" ht="27" x14ac:dyDescent="0.2">
       <c r="C2" s="22" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I3" s="23" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J3" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.2">
@@ -1382,19 +1388,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K4" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="21" t="s">
         <v>158</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
@@ -1402,19 +1408,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
@@ -1422,19 +1428,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
@@ -1442,7 +1448,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
@@ -1450,7 +1456,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
@@ -1458,7 +1464,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
@@ -1466,7 +1472,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
@@ -1474,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
@@ -1482,10 +1488,10 @@
     </row>
     <row r="13" spans="2:12" ht="27" x14ac:dyDescent="0.2">
       <c r="C13" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
@@ -1493,10 +1499,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
@@ -1504,10 +1510,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>50</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
@@ -1515,10 +1521,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -1526,10 +1532,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -1537,10 +1543,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H18" s="24"/>
     </row>
@@ -1549,10 +1555,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H19" s="24"/>
     </row>
@@ -1561,10 +1567,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H20" s="24"/>
     </row>
@@ -1573,10 +1579,10 @@
         <v>8</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H21" s="24"/>
     </row>
@@ -1585,10 +1591,10 @@
         <v>9</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H22" s="24"/>
     </row>
@@ -1597,48 +1603,48 @@
         <v>10</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="27" x14ac:dyDescent="0.2">
       <c r="C25" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="19" x14ac:dyDescent="0.2">
       <c r="C26" s="28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="N26" s="39" t="s">
-        <v>171</v>
+        <v>121</v>
+      </c>
+      <c r="N26" s="36" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I27" s="26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="19" x14ac:dyDescent="0.2">
       <c r="C28" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I28" s="33" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
@@ -1646,19 +1652,19 @@
         <v>1</v>
       </c>
       <c r="C29" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>69</v>
-      </c>
       <c r="E29" s="27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1666,19 +1672,19 @@
         <v>2</v>
       </c>
       <c r="C30" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
+      <c r="E30" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
       <c r="I30" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
@@ -1686,27 +1692,27 @@
         <v>3</v>
       </c>
       <c r="C31" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>65</v>
-      </c>
       <c r="E31" s="27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="23" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="19" x14ac:dyDescent="0.2">
       <c r="C33" s="28" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
@@ -1714,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="C34" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="21" t="s">
-        <v>69</v>
-      </c>
       <c r="E34" s="27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
@@ -1728,13 +1734,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
@@ -1742,44 +1748,44 @@
         <v>3</v>
       </c>
       <c r="C36" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
+      <c r="E36" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B37" s="23">
         <v>4</v>
       </c>
       <c r="C37" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="21" t="s">
-        <v>65</v>
-      </c>
       <c r="E37" s="27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="19" x14ac:dyDescent="0.2">
       <c r="C39" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
@@ -1787,13 +1793,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="21" t="s">
-        <v>69</v>
-      </c>
       <c r="E40" s="27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
@@ -1801,13 +1807,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
@@ -1815,13 +1821,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>65</v>
-      </c>
       <c r="E42" s="34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
@@ -1829,13 +1835,13 @@
         <v>4</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
@@ -1843,13 +1849,13 @@
         <v>5</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
@@ -1857,21 +1863,21 @@
         <v>6</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C47" s="23" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
@@ -1879,13 +1885,13 @@
         <v>1</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
@@ -1893,13 +1899,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
@@ -1910,15 +1916,30 @@
         <v>1</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C52" s="23" t="s">
-        <v>166</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C54" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C56" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C58" s="23" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1939,14 +1960,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="27" x14ac:dyDescent="0.35">
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1973,62 +1990,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B2" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="O6" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="O6" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
@@ -2059,10 +2076,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="2"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
@@ -2092,10 +2109,10 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
@@ -2213,49 +2230,49 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" t="s">
         <v>24</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>25</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="V14" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="V14" t="s">
-        <v>32</v>
-      </c>
-      <c r="W14" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="X14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Y14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="AA14" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AC14" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="AD14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AE14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF14" s="6" t="s">
+      <c r="AG14" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="AG14" s="6" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.2">
@@ -2287,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O15" s="8">
         <v>1</v>
@@ -2374,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O16" s="9">
         <v>1</v>
@@ -2461,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" s="9">
         <v>3</v>
@@ -2569,16 +2586,16 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.2">
       <c r="O19" t="s">
+        <v>23</v>
+      </c>
+      <c r="P19" t="s">
         <v>24</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" t="s">
-        <v>26</v>
-      </c>
       <c r="R19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V19" s="10">
         <v>7</v>
@@ -2630,7 +2647,7 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N20" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O20" s="8">
         <v>1</v>
@@ -2706,7 +2723,7 @@
         <v>3</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O21" s="9">
         <v>1</v>
@@ -2779,7 +2796,7 @@
         <v>10</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O22" s="9">
         <v>3</v>
@@ -2852,7 +2869,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O23" s="9">
         <v>4</v>
@@ -2964,29 +2981,29 @@
       </c>
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B25" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
+      <c r="B25" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
       <c r="O25" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25" t="s">
         <v>24</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>25</v>
       </c>
-      <c r="Q25" t="s">
-        <v>26</v>
-      </c>
       <c r="R25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S25" t="s">
+        <v>29</v>
+      </c>
+      <c r="T25" t="s">
         <v>30</v>
-      </c>
-      <c r="T25" t="s">
-        <v>31</v>
       </c>
       <c r="U25" s="6"/>
       <c r="V25" s="10">
@@ -3038,12 +3055,12 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
       <c r="N26" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O26" s="8">
         <v>1</v>
@@ -3112,12 +3129,12 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
       <c r="N27" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O27" s="9">
         <v>1</v>
@@ -3186,12 +3203,12 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
       <c r="N28" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O28" s="9">
         <v>3</v>
@@ -3260,12 +3277,12 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
       <c r="N29" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O29" s="9">
         <v>4</v>
@@ -3335,7 +3352,7 @@
     </row>
     <row r="30" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N30" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O30" s="9">
         <v>7</v>
@@ -3411,16 +3428,16 @@
         <v>14</v>
       </c>
       <c r="E31" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O31" s="9">
         <v>7</v>
@@ -3598,7 +3615,7 @@
     </row>
     <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="O34" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V34" s="10">
         <v>21</v>
@@ -3713,13 +3730,13 @@
         <v>0.5</v>
       </c>
       <c r="O36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q36" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="V36" s="10">
         <v>23</v>
@@ -3771,14 +3788,14 @@
     </row>
     <row r="37" spans="2:33" ht="24" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="4">
         <f>ACOS(C36)</f>
         <v>1.0471975511965976</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P37" s="6">
         <v>1</v>
@@ -3843,7 +3860,7 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P38" s="6">
         <v>1</v>
@@ -3908,7 +3925,7 @@
         <v>60</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P39" s="6">
         <v>2</v>
@@ -3917,43 +3934,43 @@
         <v>1</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V39" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X39" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AG39" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="2:33" ht="25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3965,7 +3982,7 @@
         <v>0.66670000000000007</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P40" s="6">
         <v>1</v>
@@ -3974,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V40" s="10">
         <v>74550</v>
@@ -4026,7 +4043,7 @@
     </row>
     <row r="41" spans="2:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="O41" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P41" s="6">
         <v>2</v>
@@ -4087,7 +4104,7 @@
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="O42" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P42" s="6">
         <v>3</v>
@@ -4148,7 +4165,7 @@
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="O43" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P43" s="6">
         <v>1</v>
@@ -4159,7 +4176,7 @@
     </row>
     <row r="44" spans="2:33" ht="27" x14ac:dyDescent="0.2">
       <c r="B44" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -4169,7 +4186,7 @@
       <c r="H44" s="21"/>
       <c r="I44" s="21"/>
       <c r="O44" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P44" s="6">
         <v>2</v>
@@ -4188,7 +4205,7 @@
       <c r="H45" s="21"/>
       <c r="I45" s="21"/>
       <c r="O45" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P45" s="6">
         <v>3</v>
@@ -4199,21 +4216,21 @@
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B46" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C46" s="23"/>
       <c r="D46" s="23"/>
       <c r="E46" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F46" s="23"/>
       <c r="G46" s="23"/>
       <c r="H46" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I46" s="21"/>
       <c r="O46" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P46" s="6">
         <v>4</v>
@@ -4224,27 +4241,27 @@
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B47" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D47" s="21"/>
       <c r="E47" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G47" s="21"/>
       <c r="H47" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P47" s="6">
         <v>1</v>
@@ -4255,27 +4272,27 @@
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B48" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D48" s="21"/>
       <c r="E48" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F48" s="29" t="s">
         <v>4</v>
       </c>
       <c r="G48" s="21"/>
       <c r="H48" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P48" s="6">
         <v>2</v>
@@ -4286,27 +4303,27 @@
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B49" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" s="21"/>
       <c r="E49" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G49" s="21"/>
       <c r="H49" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P49" s="6">
         <v>3</v>
@@ -4325,7 +4342,7 @@
       <c r="H50" s="21"/>
       <c r="I50" s="21"/>
       <c r="O50" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P50" s="6">
         <v>4</v>
@@ -4336,19 +4353,19 @@
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B51" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G51" s="21"/>
       <c r="H51" s="21"/>
       <c r="I51" s="21"/>
       <c r="O51" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P51" s="6">
         <v>5</v>
@@ -4359,10 +4376,10 @@
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B52" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -4371,7 +4388,7 @@
       <c r="H52" s="21"/>
       <c r="I52" s="21"/>
       <c r="O52" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P52" s="6">
         <v>1</v>
@@ -4382,10 +4399,10 @@
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B53" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -4394,7 +4411,7 @@
       <c r="H53" s="21"/>
       <c r="I53" s="21"/>
       <c r="O53" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P53" s="6">
         <v>2</v>
@@ -4405,21 +4422,21 @@
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B54" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G54" s="21"/>
       <c r="H54" s="21"/>
       <c r="I54" s="21"/>
       <c r="O54" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P54" s="6">
         <v>3</v>
@@ -4430,7 +4447,7 @@
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B55" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C55" s="21">
         <v>-1</v>
@@ -4442,7 +4459,7 @@
       <c r="H55" s="21"/>
       <c r="I55" s="21"/>
       <c r="O55" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P55" s="6">
         <v>4</v>
@@ -4461,7 +4478,7 @@
       <c r="H56" s="21"/>
       <c r="I56" s="21"/>
       <c r="O56" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P56" s="6">
         <v>5</v>
@@ -4473,7 +4490,7 @@
     <row r="57" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B57" s="21"/>
       <c r="C57" s="31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
@@ -4482,7 +4499,7 @@
       <c r="H57" s="21"/>
       <c r="I57" s="21"/>
       <c r="O57" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P57" s="6">
         <v>6</v>
@@ -4493,7 +4510,7 @@
     </row>
     <row r="58" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B58" s="23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
@@ -4505,11 +4522,11 @@
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B59" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" s="21"/>
       <c r="D59" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
@@ -4519,11 +4536,11 @@
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B60" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="21"/>
@@ -4531,26 +4548,26 @@
       <c r="H60" s="21"/>
       <c r="I60" s="21"/>
       <c r="O60" s="25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B61" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61" s="21"/>
       <c r="D61" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G61" s="21"/>
       <c r="H61" s="21"/>
       <c r="I61" s="21"/>
       <c r="O61" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
@@ -4558,11 +4575,11 @@
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B62" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62" s="21"/>
       <c r="D62" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="32">
@@ -4591,7 +4608,7 @@
     <row r="64" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B64" s="21"/>
       <c r="C64" s="31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D64" s="29"/>
       <c r="E64" s="30"/>
@@ -4612,13 +4629,13 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G66" s="21"/>
     </row>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/semantic-engine/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokenkino/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F797B11D-33A9-8A42-8E30-36B76597FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A6565F-AE36-E84B-A2A4-1FDDE567F600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21460" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21420" activeTab="1" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="177">
   <si>
     <t>essere</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>names (db)</t>
+  </si>
+  <si>
+    <t>SL</t>
   </si>
 </sst>
 </file>
@@ -1960,7 +1963,9 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="27" x14ac:dyDescent="0.35">
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="2"/>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokenkino/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A6565F-AE36-E84B-A2A4-1FDDE567F600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D727BC18-9C3F-2049-9D3C-AA407D50BB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21420" activeTab="1" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21460" activeTab="1" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="227">
   <si>
     <t>essere</t>
   </si>
@@ -702,12 +702,162 @@
   <si>
     <t>SL</t>
   </si>
+  <si>
+    <t>Definizione del linguaggio</t>
+  </si>
+  <si>
+    <t>Linguaggio deve contenere entità fuzzy valutabili</t>
+  </si>
+  <si>
+    <t>Esempi fuzzy</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>verb</t>
+  </si>
+  <si>
+    <t>subject-object</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>when?</t>
+  </si>
+  <si>
+    <t>object?</t>
+  </si>
+  <si>
+    <t>where?</t>
+  </si>
+  <si>
+    <t>why?</t>
+  </si>
+  <si>
+    <t>how?</t>
+  </si>
+  <si>
+    <t>Analisi di IF</t>
+  </si>
+  <si>
+    <t>Analisi di NOT</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>core-statement|adv</t>
+  </si>
+  <si>
+    <t>statement entities</t>
+  </si>
+  <si>
+    <t>pure entities</t>
+  </si>
+  <si>
+    <t>place</t>
+  </si>
+  <si>
+    <t>properties</t>
+  </si>
+  <si>
+    <t>semantic vector</t>
+  </si>
+  <si>
+    <t>absolute number</t>
+  </si>
+  <si>
+    <t>entity in place</t>
+  </si>
+  <si>
+    <t>cause</t>
+  </si>
+  <si>
+    <t>statement</t>
+  </si>
+  <si>
+    <t>facts</t>
+  </si>
+  <si>
+    <t>believes</t>
+  </si>
+  <si>
+    <t>collection</t>
+  </si>
+  <si>
+    <t>statements[]</t>
+  </si>
+  <si>
+    <t>opinions</t>
+  </si>
+  <si>
+    <t>hardcoded</t>
+  </si>
+  <si>
+    <t>experienced</t>
+  </si>
+  <si>
+    <t>collections</t>
+  </si>
+  <si>
+    <t>operations</t>
+  </si>
+  <si>
+    <t>eval(statement)</t>
+  </si>
+  <si>
+    <t>low level</t>
+  </si>
+  <si>
+    <t>similarity to facts, believes, opinions -&gt; fuzzy (-1,1)</t>
+  </si>
+  <si>
+    <t>find something clever</t>
+  </si>
+  <si>
+    <t>code myself</t>
+  </si>
+  <si>
+    <t>find common sense statements</t>
+  </si>
+  <si>
+    <t>spaCy costruisce SL da NL</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>base|place|core-statement</t>
+  </si>
+  <si>
+    <t>base|core-statement|op + timestamp</t>
+  </si>
+  <si>
+    <t>base (verb, adverb, adjective, noun, cong)</t>
+  </si>
+  <si>
+    <t>conj</t>
+  </si>
+  <si>
+    <t>vector|location</t>
+  </si>
+  <si>
+    <t>scalar equation/inequation</t>
+  </si>
+  <si>
+    <t>core-statement</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -804,6 +954,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -912,9 +1068,8 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -998,6 +1153,24 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1352,596 +1525,596 @@
   <dimension ref="B2:N58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="21" customWidth="1"/>
-    <col min="2" max="2" width="3.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" style="21" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="21" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="21"/>
-    <col min="7" max="7" width="2.5" style="21" customWidth="1"/>
-    <col min="8" max="8" width="62.6640625" style="21" customWidth="1"/>
-    <col min="9" max="10" width="10.83203125" style="21"/>
-    <col min="11" max="11" width="35.33203125" style="21" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="21"/>
+    <col min="1" max="1" width="3.6640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="3.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5" style="20" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="20" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="20"/>
+    <col min="7" max="7" width="2.5" style="20" customWidth="1"/>
+    <col min="8" max="8" width="62.6640625" style="20" customWidth="1"/>
+    <col min="9" max="10" width="10.83203125" style="20"/>
+    <col min="11" max="11" width="35.33203125" style="20" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="20"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="22" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="23">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="22">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="20" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>2</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="20" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="23">
+      <c r="B6" s="22">
         <v>3</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="20" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="23">
+      <c r="B7" s="22">
         <v>4</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <v>5</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <v>6</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="23">
+      <c r="B10" s="22">
         <v>7</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="23">
+      <c r="B11" s="22">
         <v>8</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="23"/>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="2:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="23">
-        <v>1</v>
-      </c>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="22">
+        <v>1</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="20" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="23">
+      <c r="B15" s="22">
         <v>2</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="23">
+      <c r="B16" s="22">
         <v>3</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="20" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B17" s="23">
+      <c r="B17" s="22">
         <v>4</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="23">
+      <c r="B18" s="22">
         <v>5</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="24"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B19" s="23">
+      <c r="B19" s="22">
         <v>6</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="G19" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="24"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <v>7</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="H20" s="24"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <v>8</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H21" s="24"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="23">
+      <c r="B22" s="22">
         <v>9</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="H22" s="24"/>
+      <c r="H22" s="23"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>10</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="20" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="27" x14ac:dyDescent="0.2">
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="22" t="s">
+      <c r="I25" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="I26" s="26" t="s">
+      <c r="I26" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="N26" s="36" t="s">
+      <c r="N26" s="35" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="I27" s="26" t="s">
+      <c r="I27" s="25" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="19" x14ac:dyDescent="0.2">
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="I28" s="33" t="s">
+      <c r="I28" s="32" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="23">
-        <v>1</v>
-      </c>
-      <c r="C29" s="26" t="s">
+      <c r="B29" s="22">
+        <v>1</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="26" t="s">
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="25" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="23">
+      <c r="B30" s="22">
         <v>2</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="E30" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="23" t="s">
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="22" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <v>3</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="23" t="s">
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="22" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="19" x14ac:dyDescent="0.2">
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="26" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B34" s="23">
-        <v>1</v>
-      </c>
-      <c r="C34" s="26" t="s">
+      <c r="B34" s="22">
+        <v>1</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="26" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <v>2</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="26" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B36" s="23">
+      <c r="B36" s="22">
         <v>3</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="37" t="s">
+      <c r="E36" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B37" s="23">
+      <c r="B37" s="22">
         <v>4</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E37" s="26" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="19" x14ac:dyDescent="0.2">
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="I39" s="21" t="s">
+      <c r="I39" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="J39" s="21" t="s">
+      <c r="J39" s="20" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B40" s="23">
-        <v>1</v>
-      </c>
-      <c r="C40" s="26" t="s">
+      <c r="B40" s="22">
+        <v>1</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" s="26" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="23">
+      <c r="B41" s="22">
         <v>2</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="26" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="23">
+      <c r="B42" s="22">
         <v>3</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="33" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="23">
+      <c r="B43" s="22">
         <v>4</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="E43" s="27" t="s">
+      <c r="E43" s="26" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B44" s="23">
+      <c r="B44" s="22">
         <v>5</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="E44" s="26" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B45" s="23">
+      <c r="B45" s="22">
         <v>6</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E45" s="26" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="26" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="23">
-        <v>1</v>
-      </c>
-      <c r="C48" s="26" t="s">
+      <c r="B48" s="22">
+        <v>1</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="27" t="s">
+      <c r="E48" s="26" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B49" s="23">
+      <c r="B49" s="22">
         <v>2</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E49" s="27" t="s">
+      <c r="E49" s="26" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="23">
+      <c r="B50" s="22">
         <v>4</v>
       </c>
-      <c r="C50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="21" t="s">
+      <c r="C50" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E50" s="21" t="s">
+      <c r="E50" s="20" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="22" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="22" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="22" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="22" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1956,19 +2129,328 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FCF69A-7541-8F49-8917-87CA28DC0269}">
-  <dimension ref="B2:C3"/>
+  <dimension ref="B2:M28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="3.83203125" customWidth="1"/>
+    <col min="1" max="2" width="3.83203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="19" style="20" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="20"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="27" x14ac:dyDescent="0.35">
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="2:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="C2" s="21" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="2"/>
+      <c r="E2" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="22"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C4" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="M4" s="37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="C5" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="J5" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C6" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C7" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="L7" s="31"/>
+    </row>
+    <row r="8" spans="2:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="C8" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="L8" s="39"/>
+    </row>
+    <row r="9" spans="2:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="E9" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="39"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E10" s="22"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+    </row>
+    <row r="12" spans="2:13" ht="19" x14ac:dyDescent="0.2">
+      <c r="E12" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="E13" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E14" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E15" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" ht="19" x14ac:dyDescent="0.2">
+      <c r="E17" s="27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="E18" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="E19" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="E20" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" ht="19" x14ac:dyDescent="0.2">
+      <c r="E22" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="E23" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="3:10" ht="27" x14ac:dyDescent="0.2">
+      <c r="C25" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="G26" s="36"/>
+      <c r="J26" s="36"/>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F28" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1995,99 +2477,99 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="M3" s="2"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="O6" s="39" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="O6" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
+      <c r="L9" s="1"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C10">
@@ -2114,13 +2596,13 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C11">
@@ -2149,7 +2631,7 @@
       </c>
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C12">
@@ -2178,7 +2660,7 @@
       </c>
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C13">
@@ -2207,7 +2689,7 @@
       </c>
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14">
@@ -2246,42 +2728,42 @@
       <c r="V14" t="s">
         <v>31</v>
       </c>
-      <c r="W14" s="6" t="s">
+      <c r="W14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="X14" s="6" t="s">
+      <c r="X14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Y14" s="6" t="s">
+      <c r="Y14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Z14" s="6" t="s">
+      <c r="Z14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AA14" s="6" t="s">
+      <c r="AA14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AB14" s="6" t="s">
+      <c r="AB14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AC14" s="6" t="s">
+      <c r="AC14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AD14" s="6" t="s">
+      <c r="AD14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AE14" s="6" t="s">
+      <c r="AE14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AF14" s="6" t="s">
+      <c r="AF14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AG14" s="6" t="s">
+      <c r="AG14" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C15">
@@ -2308,67 +2790,67 @@
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="O15" s="8">
-        <v>1</v>
-      </c>
-      <c r="P15" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="8">
+      <c r="O15" s="7">
+        <v>1</v>
+      </c>
+      <c r="P15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="7">
         <v>3</v>
       </c>
-      <c r="V15" s="10">
+      <c r="V15" s="9">
         <v>3</v>
       </c>
-      <c r="W15" s="8">
+      <c r="W15" s="7">
         <v>9</v>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="11">
         <f>((V15-1) * V15) / 2</f>
         <v>3</v>
       </c>
-      <c r="Y15" s="11">
+      <c r="Y15" s="10">
         <f t="shared" ref="Y15:Y31" si="0">X15*100/W15</f>
         <v>33.333333333333336</v>
       </c>
-      <c r="Z15" s="11">
+      <c r="Z15" s="10">
         <f>(V15 * (V15+1)) / 2</f>
         <v>6</v>
       </c>
-      <c r="AA15" s="11">
+      <c r="AA15" s="10">
         <f>Z15*100/W15</f>
         <v>66.666666666666671</v>
       </c>
-      <c r="AB15" s="11">
+      <c r="AB15" s="10">
         <f t="shared" ref="AB15:AB20" si="1">((V15 * (V15+1)) / 2)*4*V15</f>
         <v>72</v>
       </c>
-      <c r="AC15" s="11">
+      <c r="AC15" s="10">
         <f>AB15/(1024*1024*1024)</f>
         <v>6.7055225372314453E-8</v>
       </c>
-      <c r="AD15" s="11">
+      <c r="AD15" s="10">
         <f>5000*V15</f>
         <v>15000</v>
       </c>
-      <c r="AE15" s="11">
+      <c r="AE15" s="10">
         <f>AD15/(1024*1024*1024)</f>
         <v>1.3969838619232178E-5</v>
       </c>
-      <c r="AF15" s="11">
+      <c r="AF15" s="10">
         <f>AD15/(1024*1024)</f>
         <v>1.430511474609375E-2</v>
       </c>
-      <c r="AG15" s="11">
+      <c r="AG15" s="10">
         <f>AD15/1024</f>
         <v>14.6484375</v>
       </c>
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C16">
@@ -2395,67 +2877,67 @@
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O16" s="9">
-        <v>1</v>
-      </c>
-      <c r="P16" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="8">
+      <c r="O16" s="8">
+        <v>1</v>
+      </c>
+      <c r="P16" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="7">
         <v>2</v>
       </c>
-      <c r="V16" s="10">
+      <c r="V16" s="9">
         <v>4</v>
       </c>
-      <c r="W16" s="8">
+      <c r="W16" s="7">
         <v>16</v>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="11">
         <f>((V16-1) * V16) / 2</f>
         <v>6</v>
       </c>
-      <c r="Y16" s="11">
+      <c r="Y16" s="10">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
-      <c r="Z16" s="11">
+      <c r="Z16" s="10">
         <f>(V16 * (V16+1)) / 2</f>
         <v>10</v>
       </c>
-      <c r="AA16" s="11">
+      <c r="AA16" s="10">
         <f t="shared" ref="AA16:AA42" si="2">Z16*100/W16</f>
         <v>62.5</v>
       </c>
-      <c r="AB16" s="11">
+      <c r="AB16" s="10">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="AC16" s="11">
+      <c r="AC16" s="10">
         <f t="shared" ref="AC16:AC42" si="3">AB16/(1024*1024*1024)</f>
         <v>1.4901161193847656E-7</v>
       </c>
-      <c r="AD16" s="11">
+      <c r="AD16" s="10">
         <f t="shared" ref="AD16:AD42" si="4">5000*V16</f>
         <v>20000</v>
       </c>
-      <c r="AE16" s="11">
+      <c r="AE16" s="10">
         <f t="shared" ref="AE16:AE42" si="5">AD16/(1024*1024*1024)</f>
         <v>1.862645149230957E-5</v>
       </c>
-      <c r="AF16" s="11">
+      <c r="AF16" s="10">
         <f t="shared" ref="AF16:AF42" si="6">AD16/(1024*1024)</f>
         <v>1.9073486328125E-2</v>
       </c>
-      <c r="AG16" s="11">
+      <c r="AG16" s="10">
         <f t="shared" ref="AG16:AG42" si="7">AD16/1024</f>
         <v>19.53125</v>
       </c>
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17">
@@ -2482,109 +2964,109 @@
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="N17" s="7" t="s">
+      <c r="N17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="8">
         <v>3</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="8">
         <v>2</v>
       </c>
-      <c r="Q17" s="8">
-        <v>1</v>
-      </c>
-      <c r="V17" s="10">
+      <c r="Q17" s="7">
+        <v>1</v>
+      </c>
+      <c r="V17" s="9">
         <v>5</v>
       </c>
-      <c r="W17" s="8">
+      <c r="W17" s="7">
         <v>25</v>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="11">
         <f>((V17-1) * V17) / 2</f>
         <v>10</v>
       </c>
-      <c r="Y17" s="11">
+      <c r="Y17" s="10">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="Z17" s="11">
+      <c r="Z17" s="10">
         <f>(V17 * (V17+1)) / 2</f>
         <v>15</v>
       </c>
-      <c r="AA17" s="11">
+      <c r="AA17" s="10">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="AB17" s="11">
+      <c r="AB17" s="10">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="AC17" s="11">
+      <c r="AC17" s="10">
         <f t="shared" si="3"/>
         <v>2.7939677238464355E-7</v>
       </c>
-      <c r="AD17" s="11">
+      <c r="AD17" s="10">
         <f t="shared" si="4"/>
         <v>25000</v>
       </c>
-      <c r="AE17" s="11">
+      <c r="AE17" s="10">
         <f t="shared" si="5"/>
         <v>2.3283064365386963E-5</v>
       </c>
-      <c r="AF17" s="11">
+      <c r="AF17" s="10">
         <f t="shared" si="6"/>
         <v>2.384185791015625E-2</v>
       </c>
-      <c r="AG17" s="11">
+      <c r="AG17" s="10">
         <f t="shared" si="7"/>
         <v>24.4140625</v>
       </c>
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="V18" s="10">
+      <c r="V18" s="9">
         <v>6</v>
       </c>
-      <c r="W18" s="8">
+      <c r="W18" s="7">
         <v>36</v>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="11">
         <f>((V18-1) * V18) / 2</f>
         <v>15</v>
       </c>
-      <c r="Y18" s="11">
+      <c r="Y18" s="10">
         <f t="shared" si="0"/>
         <v>41.666666666666664</v>
       </c>
-      <c r="Z18" s="11">
+      <c r="Z18" s="10">
         <f t="shared" ref="Z18:Z42" si="8">(V18 * (V18+1)) / 2</f>
         <v>21</v>
       </c>
-      <c r="AA18" s="11">
+      <c r="AA18" s="10">
         <f t="shared" si="2"/>
         <v>58.333333333333336</v>
       </c>
-      <c r="AB18" s="11">
+      <c r="AB18" s="10">
         <f t="shared" si="1"/>
         <v>504</v>
       </c>
-      <c r="AC18" s="11">
+      <c r="AC18" s="10">
         <f t="shared" si="3"/>
         <v>4.6938657760620117E-7</v>
       </c>
-      <c r="AD18" s="11">
+      <c r="AD18" s="10">
         <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="AE18" s="11">
+      <c r="AE18" s="10">
         <f t="shared" si="5"/>
         <v>2.7939677238464355E-5</v>
       </c>
-      <c r="AF18" s="11">
+      <c r="AF18" s="10">
         <f t="shared" si="6"/>
         <v>2.86102294921875E-2</v>
       </c>
-      <c r="AG18" s="11">
+      <c r="AG18" s="10">
         <f t="shared" si="7"/>
         <v>29.296875</v>
       </c>
@@ -2602,114 +3084,114 @@
       <c r="R19" t="s">
         <v>27</v>
       </c>
-      <c r="V19" s="10">
+      <c r="V19" s="9">
         <v>7</v>
       </c>
-      <c r="W19" s="8">
+      <c r="W19" s="7">
         <f t="shared" ref="W19:W31" si="9">V19*V19</f>
         <v>49</v>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="11">
         <f>((V19-1) * V19) / 2</f>
         <v>21</v>
       </c>
-      <c r="Y19" s="11">
+      <c r="Y19" s="10">
         <f t="shared" si="0"/>
         <v>42.857142857142854</v>
       </c>
-      <c r="Z19" s="11">
+      <c r="Z19" s="10">
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="AA19" s="11">
+      <c r="AA19" s="10">
         <f t="shared" si="2"/>
         <v>57.142857142857146</v>
       </c>
-      <c r="AB19" s="11">
+      <c r="AB19" s="10">
         <f t="shared" si="1"/>
         <v>784</v>
       </c>
-      <c r="AC19" s="11">
+      <c r="AC19" s="10">
         <f t="shared" si="3"/>
         <v>7.3015689849853516E-7</v>
       </c>
-      <c r="AD19" s="11">
+      <c r="AD19" s="10">
         <f t="shared" si="4"/>
         <v>35000</v>
       </c>
-      <c r="AE19" s="11">
+      <c r="AE19" s="10">
         <f t="shared" si="5"/>
         <v>3.2596290111541748E-5</v>
       </c>
-      <c r="AF19" s="11">
+      <c r="AF19" s="10">
         <f t="shared" si="6"/>
         <v>3.337860107421875E-2</v>
       </c>
-      <c r="AG19" s="11">
+      <c r="AG19" s="10">
         <f t="shared" si="7"/>
         <v>34.1796875</v>
       </c>
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="N20" s="7" t="s">
+      <c r="N20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="O20" s="8">
-        <v>1</v>
-      </c>
-      <c r="P20" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="8">
+      <c r="O20" s="7">
+        <v>1</v>
+      </c>
+      <c r="P20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="7">
         <v>3</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="7">
         <v>4</v>
       </c>
-      <c r="V20" s="10">
+      <c r="V20" s="9">
         <v>8</v>
       </c>
-      <c r="W20" s="8">
+      <c r="W20" s="7">
         <f t="shared" si="9"/>
         <v>64</v>
       </c>
-      <c r="X20" s="12">
+      <c r="X20" s="11">
         <f t="shared" ref="X20:X42" si="10">((V20-1) * V20) / 2</f>
         <v>28</v>
       </c>
-      <c r="Y20" s="11">
+      <c r="Y20" s="10">
         <f t="shared" si="0"/>
         <v>43.75</v>
       </c>
-      <c r="Z20" s="11">
+      <c r="Z20" s="10">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
-      <c r="AA20" s="11">
+      <c r="AA20" s="10">
         <f t="shared" si="2"/>
         <v>56.25</v>
       </c>
-      <c r="AB20" s="11">
+      <c r="AB20" s="10">
         <f t="shared" si="1"/>
         <v>1152</v>
       </c>
-      <c r="AC20" s="11">
+      <c r="AC20" s="10">
         <f t="shared" si="3"/>
         <v>1.0728836059570312E-6</v>
       </c>
-      <c r="AD20" s="11">
+      <c r="AD20" s="10">
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="AE20" s="11">
+      <c r="AE20" s="10">
         <f t="shared" si="5"/>
         <v>3.7252902984619141E-5</v>
       </c>
-      <c r="AF20" s="11">
+      <c r="AF20" s="10">
         <f t="shared" si="6"/>
         <v>3.814697265625E-2</v>
       </c>
-      <c r="AG20" s="11">
+      <c r="AG20" s="10">
         <f t="shared" si="7"/>
         <v>39.0625</v>
       </c>
@@ -2727,65 +3209,65 @@
       <c r="F21" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="N21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O21" s="9">
-        <v>1</v>
-      </c>
-      <c r="P21" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="8">
+      <c r="O21" s="8">
+        <v>1</v>
+      </c>
+      <c r="P21" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="7">
         <v>2</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="7">
         <v>5</v>
       </c>
-      <c r="V21" s="10">
+      <c r="V21" s="9">
         <v>9</v>
       </c>
-      <c r="W21" s="8">
+      <c r="W21" s="7">
         <f t="shared" si="9"/>
         <v>81</v>
       </c>
-      <c r="X21" s="12">
+      <c r="X21" s="11">
         <f t="shared" si="10"/>
         <v>36</v>
       </c>
-      <c r="Y21" s="11">
+      <c r="Y21" s="10">
         <f t="shared" si="0"/>
         <v>44.444444444444443</v>
       </c>
-      <c r="Z21" s="11">
+      <c r="Z21" s="10">
         <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="AA21" s="11">
+      <c r="AA21" s="10">
         <f t="shared" si="2"/>
         <v>55.555555555555557</v>
       </c>
-      <c r="AB21" s="11">
+      <c r="AB21" s="10">
         <f t="shared" ref="AB21:AB42" si="11">((V21 * (V21+1)) / 2)*4*V21</f>
         <v>1620</v>
       </c>
-      <c r="AC21" s="11">
+      <c r="AC21" s="10">
         <f t="shared" si="3"/>
         <v>1.5087425708770752E-6</v>
       </c>
-      <c r="AD21" s="11">
+      <c r="AD21" s="10">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="AE21" s="11">
+      <c r="AE21" s="10">
         <f t="shared" si="5"/>
         <v>4.1909515857696533E-5</v>
       </c>
-      <c r="AF21" s="11">
+      <c r="AF21" s="10">
         <f t="shared" si="6"/>
         <v>4.291534423828125E-2</v>
       </c>
-      <c r="AG21" s="11">
+      <c r="AG21" s="10">
         <f t="shared" si="7"/>
         <v>43.9453125</v>
       </c>
@@ -2800,65 +3282,65 @@
       <c r="E22" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="N22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="8">
         <v>3</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="8">
         <v>2</v>
       </c>
-      <c r="Q22" s="8">
-        <v>1</v>
-      </c>
-      <c r="R22" s="8">
+      <c r="Q22" s="7">
+        <v>1</v>
+      </c>
+      <c r="R22" s="7">
         <v>6</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22" s="9">
         <v>10</v>
       </c>
-      <c r="W22" s="8">
+      <c r="W22" s="7">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="X22" s="12">
+      <c r="X22" s="11">
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
-      <c r="Y22" s="11">
+      <c r="Y22" s="10">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="Z22" s="11">
+      <c r="Z22" s="10">
         <f t="shared" si="8"/>
         <v>55</v>
       </c>
-      <c r="AA22" s="11">
+      <c r="AA22" s="10">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="AB22" s="11">
+      <c r="AB22" s="10">
         <f t="shared" si="11"/>
         <v>2200</v>
       </c>
-      <c r="AC22" s="11">
+      <c r="AC22" s="10">
         <f t="shared" si="3"/>
         <v>2.0489096641540527E-6</v>
       </c>
-      <c r="AD22" s="11">
+      <c r="AD22" s="10">
         <f t="shared" si="4"/>
         <v>50000</v>
       </c>
-      <c r="AE22" s="11">
+      <c r="AE22" s="10">
         <f t="shared" si="5"/>
         <v>4.6566128730773926E-5</v>
       </c>
-      <c r="AF22" s="11">
+      <c r="AF22" s="10">
         <f t="shared" si="6"/>
         <v>4.76837158203125E-2</v>
       </c>
-      <c r="AG22" s="11">
+      <c r="AG22" s="10">
         <f t="shared" si="7"/>
         <v>48.828125</v>
       </c>
@@ -2873,125 +3355,125 @@
       <c r="E23" t="s">
         <v>6</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="N23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="8">
         <v>4</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="8">
         <v>5</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="Q23" s="8">
         <v>6</v>
       </c>
-      <c r="R23" s="8">
-        <v>1</v>
-      </c>
-      <c r="V23" s="10">
+      <c r="R23" s="7">
+        <v>1</v>
+      </c>
+      <c r="V23" s="9">
         <v>11</v>
       </c>
-      <c r="W23" s="8">
+      <c r="W23" s="7">
         <f t="shared" si="9"/>
         <v>121</v>
       </c>
-      <c r="X23" s="12">
+      <c r="X23" s="11">
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
-      <c r="Y23" s="11">
+      <c r="Y23" s="10">
         <f t="shared" si="0"/>
         <v>45.454545454545453</v>
       </c>
-      <c r="Z23" s="11">
+      <c r="Z23" s="10">
         <f t="shared" si="8"/>
         <v>66</v>
       </c>
-      <c r="AA23" s="11">
+      <c r="AA23" s="10">
         <f t="shared" si="2"/>
         <v>54.545454545454547</v>
       </c>
-      <c r="AB23" s="11">
+      <c r="AB23" s="10">
         <f t="shared" si="11"/>
         <v>2904</v>
       </c>
-      <c r="AC23" s="11">
+      <c r="AC23" s="10">
         <f t="shared" si="3"/>
         <v>2.7045607566833496E-6</v>
       </c>
-      <c r="AD23" s="11">
+      <c r="AD23" s="10">
         <f t="shared" si="4"/>
         <v>55000</v>
       </c>
-      <c r="AE23" s="11">
+      <c r="AE23" s="10">
         <f t="shared" si="5"/>
         <v>5.1222741603851318E-5</v>
       </c>
-      <c r="AF23" s="11">
+      <c r="AF23" s="10">
         <f t="shared" si="6"/>
         <v>5.245208740234375E-2</v>
       </c>
-      <c r="AG23" s="11">
+      <c r="AG23" s="10">
         <f t="shared" si="7"/>
         <v>53.7109375</v>
       </c>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="V24" s="10">
+      <c r="V24" s="9">
         <v>12</v>
       </c>
-      <c r="W24" s="8">
+      <c r="W24" s="7">
         <f t="shared" si="9"/>
         <v>144</v>
       </c>
-      <c r="X24" s="12">
+      <c r="X24" s="11">
         <f t="shared" si="10"/>
         <v>66</v>
       </c>
-      <c r="Y24" s="11">
+      <c r="Y24" s="10">
         <f t="shared" si="0"/>
         <v>45.833333333333336</v>
       </c>
-      <c r="Z24" s="11">
+      <c r="Z24" s="10">
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
-      <c r="AA24" s="11">
+      <c r="AA24" s="10">
         <f t="shared" si="2"/>
         <v>54.166666666666664</v>
       </c>
-      <c r="AB24" s="11">
+      <c r="AB24" s="10">
         <f t="shared" si="11"/>
         <v>3744</v>
       </c>
-      <c r="AC24" s="11">
+      <c r="AC24" s="10">
         <f t="shared" si="3"/>
         <v>3.4868717193603516E-6</v>
       </c>
-      <c r="AD24" s="11">
+      <c r="AD24" s="10">
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="AE24" s="11">
+      <c r="AE24" s="10">
         <f t="shared" si="5"/>
         <v>5.5879354476928711E-5</v>
       </c>
-      <c r="AF24" s="11">
+      <c r="AF24" s="10">
         <f t="shared" si="6"/>
         <v>5.7220458984375E-2</v>
       </c>
-      <c r="AG24" s="11">
+      <c r="AG24" s="10">
         <f t="shared" si="7"/>
         <v>58.59375</v>
       </c>
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
       <c r="O25" t="s">
         <v>23</v>
       </c>
@@ -3010,502 +3492,502 @@
       <c r="T25" t="s">
         <v>30</v>
       </c>
-      <c r="U25" s="6"/>
-      <c r="V25" s="10">
+      <c r="U25" s="5"/>
+      <c r="V25" s="9">
         <v>13</v>
       </c>
-      <c r="W25" s="8">
+      <c r="W25" s="7">
         <f t="shared" si="9"/>
         <v>169</v>
       </c>
-      <c r="X25" s="12">
+      <c r="X25" s="11">
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="Y25" s="11">
+      <c r="Y25" s="10">
         <f t="shared" si="0"/>
         <v>46.153846153846153</v>
       </c>
-      <c r="Z25" s="11">
+      <c r="Z25" s="10">
         <f t="shared" si="8"/>
         <v>91</v>
       </c>
-      <c r="AA25" s="11">
+      <c r="AA25" s="10">
         <f t="shared" si="2"/>
         <v>53.846153846153847</v>
       </c>
-      <c r="AB25" s="11">
+      <c r="AB25" s="10">
         <f t="shared" si="11"/>
         <v>4732</v>
       </c>
-      <c r="AC25" s="11">
+      <c r="AC25" s="10">
         <f t="shared" si="3"/>
         <v>4.4070184230804443E-6</v>
       </c>
-      <c r="AD25" s="11">
+      <c r="AD25" s="10">
         <f t="shared" si="4"/>
         <v>65000</v>
       </c>
-      <c r="AE25" s="11">
+      <c r="AE25" s="10">
         <f t="shared" si="5"/>
         <v>6.0535967350006104E-5</v>
       </c>
-      <c r="AF25" s="11">
+      <c r="AF25" s="10">
         <f t="shared" si="6"/>
         <v>6.198883056640625E-2</v>
       </c>
-      <c r="AG25" s="11">
+      <c r="AG25" s="10">
         <f t="shared" si="7"/>
         <v>63.4765625</v>
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="N26" s="7" t="s">
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="N26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="O26" s="8">
-        <v>1</v>
-      </c>
-      <c r="P26" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="8">
+      <c r="O26" s="7">
+        <v>1</v>
+      </c>
+      <c r="P26" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="7">
         <v>3</v>
       </c>
-      <c r="R26" s="8">
+      <c r="R26" s="7">
         <v>4</v>
       </c>
-      <c r="S26" s="8">
+      <c r="S26" s="7">
         <v>7</v>
       </c>
-      <c r="T26" s="8">
+      <c r="T26" s="7">
         <v>7</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26" s="9">
         <v>14</v>
       </c>
-      <c r="W26" s="8">
+      <c r="W26" s="7">
         <f t="shared" si="9"/>
         <v>196</v>
       </c>
-      <c r="X26" s="12">
+      <c r="X26" s="11">
         <f t="shared" si="10"/>
         <v>91</v>
       </c>
-      <c r="Y26" s="11">
+      <c r="Y26" s="10">
         <f t="shared" si="0"/>
         <v>46.428571428571431</v>
       </c>
-      <c r="Z26" s="11">
+      <c r="Z26" s="10">
         <f t="shared" si="8"/>
         <v>105</v>
       </c>
-      <c r="AA26" s="11">
+      <c r="AA26" s="10">
         <f t="shared" si="2"/>
         <v>53.571428571428569</v>
       </c>
-      <c r="AB26" s="11">
+      <c r="AB26" s="10">
         <f t="shared" si="11"/>
         <v>5880</v>
       </c>
-      <c r="AC26" s="11">
+      <c r="AC26" s="10">
         <f t="shared" si="3"/>
         <v>5.4761767387390137E-6</v>
       </c>
-      <c r="AD26" s="11">
+      <c r="AD26" s="10">
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="AE26" s="11">
+      <c r="AE26" s="10">
         <f t="shared" si="5"/>
         <v>6.5192580223083496E-5</v>
       </c>
-      <c r="AF26" s="11">
+      <c r="AF26" s="10">
         <f t="shared" si="6"/>
         <v>6.67572021484375E-2</v>
       </c>
-      <c r="AG26" s="11">
+      <c r="AG26" s="10">
         <f t="shared" si="7"/>
         <v>68.359375</v>
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="N27" s="7" t="s">
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="N27" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O27" s="9">
-        <v>1</v>
-      </c>
-      <c r="P27" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="8">
+      <c r="O27" s="8">
+        <v>1</v>
+      </c>
+      <c r="P27" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="7">
         <v>2</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="7">
         <v>5</v>
       </c>
-      <c r="S27" s="8">
+      <c r="S27" s="7">
         <v>8</v>
       </c>
-      <c r="T27" s="8">
+      <c r="T27" s="7">
         <v>7</v>
       </c>
-      <c r="V27" s="10">
+      <c r="V27" s="9">
         <v>15</v>
       </c>
-      <c r="W27" s="8">
+      <c r="W27" s="7">
         <f t="shared" si="9"/>
         <v>225</v>
       </c>
-      <c r="X27" s="12">
+      <c r="X27" s="11">
         <f t="shared" si="10"/>
         <v>105</v>
       </c>
-      <c r="Y27" s="11">
+      <c r="Y27" s="10">
         <f t="shared" si="0"/>
         <v>46.666666666666664</v>
       </c>
-      <c r="Z27" s="11">
+      <c r="Z27" s="10">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="AA27" s="11">
+      <c r="AA27" s="10">
         <f t="shared" si="2"/>
         <v>53.333333333333336</v>
       </c>
-      <c r="AB27" s="11">
+      <c r="AB27" s="10">
         <f t="shared" si="11"/>
         <v>7200</v>
       </c>
-      <c r="AC27" s="11">
+      <c r="AC27" s="10">
         <f t="shared" si="3"/>
         <v>6.7055225372314453E-6</v>
       </c>
-      <c r="AD27" s="11">
+      <c r="AD27" s="10">
         <f t="shared" si="4"/>
         <v>75000</v>
       </c>
-      <c r="AE27" s="11">
+      <c r="AE27" s="10">
         <f t="shared" si="5"/>
         <v>6.9849193096160889E-5</v>
       </c>
-      <c r="AF27" s="11">
+      <c r="AF27" s="10">
         <f t="shared" si="6"/>
         <v>7.152557373046875E-2</v>
       </c>
-      <c r="AG27" s="11">
+      <c r="AG27" s="10">
         <f t="shared" si="7"/>
         <v>73.2421875</v>
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="N28" s="7" t="s">
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="N28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="8">
         <v>3</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P28" s="8">
         <v>2</v>
       </c>
-      <c r="Q28" s="8">
-        <v>1</v>
-      </c>
-      <c r="R28" s="8">
+      <c r="Q28" s="7">
+        <v>1</v>
+      </c>
+      <c r="R28" s="7">
         <v>6</v>
       </c>
-      <c r="S28" s="8">
+      <c r="S28" s="7">
         <v>9</v>
       </c>
-      <c r="T28" s="8">
+      <c r="T28" s="7">
         <v>7</v>
       </c>
-      <c r="V28" s="10">
+      <c r="V28" s="9">
         <v>16</v>
       </c>
-      <c r="W28" s="8">
+      <c r="W28" s="7">
         <f t="shared" si="9"/>
         <v>256</v>
       </c>
-      <c r="X28" s="12">
+      <c r="X28" s="11">
         <f t="shared" si="10"/>
         <v>120</v>
       </c>
-      <c r="Y28" s="11">
+      <c r="Y28" s="10">
         <f t="shared" si="0"/>
         <v>46.875</v>
       </c>
-      <c r="Z28" s="11">
+      <c r="Z28" s="10">
         <f t="shared" si="8"/>
         <v>136</v>
       </c>
-      <c r="AA28" s="11">
+      <c r="AA28" s="10">
         <f t="shared" si="2"/>
         <v>53.125</v>
       </c>
-      <c r="AB28" s="11">
+      <c r="AB28" s="10">
         <f t="shared" si="11"/>
         <v>8704</v>
       </c>
-      <c r="AC28" s="11">
+      <c r="AC28" s="10">
         <f t="shared" si="3"/>
         <v>8.106231689453125E-6</v>
       </c>
-      <c r="AD28" s="11">
+      <c r="AD28" s="10">
         <f t="shared" si="4"/>
         <v>80000</v>
       </c>
-      <c r="AE28" s="11">
+      <c r="AE28" s="10">
         <f t="shared" si="5"/>
         <v>7.4505805969238281E-5</v>
       </c>
-      <c r="AF28" s="11">
+      <c r="AF28" s="10">
         <f t="shared" si="6"/>
         <v>7.62939453125E-2</v>
       </c>
-      <c r="AG28" s="11">
+      <c r="AG28" s="10">
         <f t="shared" si="7"/>
         <v>78.125</v>
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="N29" s="7" t="s">
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="N29" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="8">
         <v>4</v>
       </c>
-      <c r="P29" s="9">
+      <c r="P29" s="8">
         <v>5</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="Q29" s="8">
         <v>6</v>
       </c>
-      <c r="R29" s="8">
-        <v>1</v>
-      </c>
-      <c r="S29" s="8">
+      <c r="R29" s="7">
+        <v>1</v>
+      </c>
+      <c r="S29" s="7">
         <v>10</v>
       </c>
-      <c r="T29" s="8">
+      <c r="T29" s="7">
         <v>7</v>
       </c>
-      <c r="V29" s="10">
+      <c r="V29" s="9">
         <v>17</v>
       </c>
-      <c r="W29" s="8">
+      <c r="W29" s="7">
         <f t="shared" si="9"/>
         <v>289</v>
       </c>
-      <c r="X29" s="12">
+      <c r="X29" s="11">
         <f t="shared" si="10"/>
         <v>136</v>
       </c>
-      <c r="Y29" s="11">
+      <c r="Y29" s="10">
         <f t="shared" si="0"/>
         <v>47.058823529411768</v>
       </c>
-      <c r="Z29" s="11">
+      <c r="Z29" s="10">
         <f t="shared" si="8"/>
         <v>153</v>
       </c>
-      <c r="AA29" s="11">
+      <c r="AA29" s="10">
         <f t="shared" si="2"/>
         <v>52.941176470588232</v>
       </c>
-      <c r="AB29" s="11">
+      <c r="AB29" s="10">
         <f t="shared" si="11"/>
         <v>10404</v>
       </c>
-      <c r="AC29" s="11">
+      <c r="AC29" s="10">
         <f t="shared" si="3"/>
         <v>9.6894800662994385E-6</v>
       </c>
-      <c r="AD29" s="11">
+      <c r="AD29" s="10">
         <f t="shared" si="4"/>
         <v>85000</v>
       </c>
-      <c r="AE29" s="11">
+      <c r="AE29" s="10">
         <f t="shared" si="5"/>
         <v>7.9162418842315674E-5</v>
       </c>
-      <c r="AF29" s="11">
+      <c r="AF29" s="10">
         <f t="shared" si="6"/>
         <v>8.106231689453125E-2</v>
       </c>
-      <c r="AG29" s="11">
+      <c r="AG29" s="10">
         <f t="shared" si="7"/>
         <v>83.0078125</v>
       </c>
     </row>
     <row r="30" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N30" s="7" t="s">
+      <c r="N30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="8">
         <v>7</v>
       </c>
-      <c r="P30" s="9">
+      <c r="P30" s="8">
         <v>8</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="Q30" s="8">
         <v>9</v>
       </c>
-      <c r="R30" s="9">
+      <c r="R30" s="8">
         <v>10</v>
       </c>
-      <c r="S30" s="8">
-        <v>1</v>
-      </c>
-      <c r="T30" s="8">
+      <c r="S30" s="7">
+        <v>1</v>
+      </c>
+      <c r="T30" s="7">
         <v>7</v>
       </c>
-      <c r="V30" s="10">
+      <c r="V30" s="9">
         <v>18</v>
       </c>
-      <c r="W30" s="8">
+      <c r="W30" s="7">
         <f t="shared" si="9"/>
         <v>324</v>
       </c>
-      <c r="X30" s="12">
+      <c r="X30" s="11">
         <f t="shared" si="10"/>
         <v>153</v>
       </c>
-      <c r="Y30" s="11">
+      <c r="Y30" s="10">
         <f t="shared" si="0"/>
         <v>47.222222222222221</v>
       </c>
-      <c r="Z30" s="11">
+      <c r="Z30" s="10">
         <f t="shared" si="8"/>
         <v>171</v>
       </c>
-      <c r="AA30" s="11">
+      <c r="AA30" s="10">
         <f t="shared" si="2"/>
         <v>52.777777777777779</v>
       </c>
-      <c r="AB30" s="11">
+      <c r="AB30" s="10">
         <f t="shared" si="11"/>
         <v>12312</v>
       </c>
-      <c r="AC30" s="11">
+      <c r="AC30" s="10">
         <f t="shared" si="3"/>
         <v>1.1466443538665771E-5</v>
       </c>
-      <c r="AD30" s="11">
+      <c r="AD30" s="10">
         <f t="shared" si="4"/>
         <v>90000</v>
       </c>
-      <c r="AE30" s="11">
+      <c r="AE30" s="10">
         <f t="shared" si="5"/>
         <v>8.3819031715393066E-5</v>
       </c>
-      <c r="AF30" s="11">
+      <c r="AF30" s="10">
         <f t="shared" si="6"/>
         <v>8.58306884765625E-2</v>
       </c>
-      <c r="AG30" s="11">
+      <c r="AG30" s="10">
         <f t="shared" si="7"/>
         <v>87.890625</v>
       </c>
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
       </c>
-      <c r="N31" s="7" t="s">
+      <c r="N31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="8">
         <v>7</v>
       </c>
-      <c r="P31" s="9">
+      <c r="P31" s="8">
         <v>7</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="Q31" s="8">
         <v>7</v>
       </c>
-      <c r="R31" s="9">
+      <c r="R31" s="8">
         <v>7</v>
       </c>
-      <c r="S31" s="9">
+      <c r="S31" s="8">
         <v>7</v>
       </c>
-      <c r="T31" s="8">
-        <v>1</v>
-      </c>
-      <c r="V31" s="10">
+      <c r="T31" s="7">
+        <v>1</v>
+      </c>
+      <c r="V31" s="9">
         <v>19</v>
       </c>
-      <c r="W31" s="8">
+      <c r="W31" s="7">
         <f t="shared" si="9"/>
         <v>361</v>
       </c>
-      <c r="X31" s="12">
+      <c r="X31" s="11">
         <f t="shared" si="10"/>
         <v>171</v>
       </c>
-      <c r="Y31" s="11">
+      <c r="Y31" s="10">
         <f t="shared" si="0"/>
         <v>47.368421052631582</v>
       </c>
-      <c r="Z31" s="11">
+      <c r="Z31" s="10">
         <f t="shared" si="8"/>
         <v>190</v>
       </c>
-      <c r="AA31" s="11">
+      <c r="AA31" s="10">
         <f t="shared" si="2"/>
         <v>52.631578947368418</v>
       </c>
-      <c r="AB31" s="11">
+      <c r="AB31" s="10">
         <f t="shared" si="11"/>
         <v>14440</v>
       </c>
-      <c r="AC31" s="11">
+      <c r="AC31" s="10">
         <f t="shared" si="3"/>
         <v>1.344829797744751E-5</v>
       </c>
-      <c r="AD31" s="11">
+      <c r="AD31" s="10">
         <f t="shared" si="4"/>
         <v>95000</v>
       </c>
-      <c r="AE31" s="11">
+      <c r="AE31" s="10">
         <f t="shared" si="5"/>
         <v>8.8475644588470459E-5</v>
       </c>
-      <c r="AF31" s="11">
+      <c r="AF31" s="10">
         <f t="shared" si="6"/>
         <v>9.059906005859375E-2</v>
       </c>
-      <c r="AG31" s="11">
+      <c r="AG31" s="10">
         <f t="shared" si="7"/>
         <v>92.7734375</v>
       </c>
@@ -3530,25 +4012,25 @@
         <f>SQRT(C32*C32+D32*D32+E32*E32++F32*F32)</f>
         <v>2</v>
       </c>
-      <c r="N32" s="7"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="8"/>
-      <c r="V32" s="10"/>
-      <c r="W32" s="8"/>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="11"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="11"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="11"/>
-      <c r="AE32" s="11"/>
-      <c r="AF32" s="11"/>
-      <c r="AG32" s="11"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="7"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
+      <c r="AA32" s="10"/>
+      <c r="AB32" s="10"/>
+      <c r="AC32" s="10"/>
+      <c r="AD32" s="10"/>
+      <c r="AE32" s="10"/>
+      <c r="AF32" s="10"/>
+      <c r="AG32" s="10"/>
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -3570,1008 +4052,1008 @@
         <f>SQRT(C33*C33+D33*D33+E33*E33++F33*F33)</f>
         <v>2</v>
       </c>
-      <c r="V33" s="10">
+      <c r="V33" s="9">
         <v>20</v>
       </c>
-      <c r="W33" s="8">
+      <c r="W33" s="7">
         <f t="shared" ref="W33:W38" si="12">V33*V33</f>
         <v>400</v>
       </c>
-      <c r="X33" s="12">
+      <c r="X33" s="11">
         <f t="shared" si="10"/>
         <v>190</v>
       </c>
-      <c r="Y33" s="11">
+      <c r="Y33" s="10">
         <f t="shared" ref="Y33:Y38" si="13">X33*100/W33</f>
         <v>47.5</v>
       </c>
-      <c r="Z33" s="11">
+      <c r="Z33" s="10">
         <f t="shared" si="8"/>
         <v>210</v>
       </c>
-      <c r="AA33" s="11">
+      <c r="AA33" s="10">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="AB33" s="11">
+      <c r="AB33" s="10">
         <f t="shared" si="11"/>
         <v>16800</v>
       </c>
-      <c r="AC33" s="11">
+      <c r="AC33" s="10">
         <f t="shared" si="3"/>
         <v>1.5646219253540039E-5</v>
       </c>
-      <c r="AD33" s="11">
+      <c r="AD33" s="10">
         <f t="shared" si="4"/>
         <v>100000</v>
       </c>
-      <c r="AE33" s="11">
+      <c r="AE33" s="10">
         <f t="shared" si="5"/>
         <v>9.3132257461547852E-5</v>
       </c>
-      <c r="AF33" s="11">
+      <c r="AF33" s="10">
         <f t="shared" si="6"/>
         <v>9.5367431640625E-2</v>
       </c>
-      <c r="AG33" s="11">
+      <c r="AG33" s="10">
         <f t="shared" si="7"/>
         <v>97.65625</v>
       </c>
     </row>
     <row r="34" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="O34" s="2" t="s">
+      <c r="O34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V34" s="10">
+      <c r="V34" s="9">
         <v>21</v>
       </c>
-      <c r="W34" s="8">
+      <c r="W34" s="7">
         <f t="shared" si="12"/>
         <v>441</v>
       </c>
-      <c r="X34" s="12">
+      <c r="X34" s="11">
         <f t="shared" si="10"/>
         <v>210</v>
       </c>
-      <c r="Y34" s="11">
+      <c r="Y34" s="10">
         <f t="shared" si="13"/>
         <v>47.61904761904762</v>
       </c>
-      <c r="Z34" s="11">
+      <c r="Z34" s="10">
         <f t="shared" si="8"/>
         <v>231</v>
       </c>
-      <c r="AA34" s="11">
+      <c r="AA34" s="10">
         <f t="shared" si="2"/>
         <v>52.38095238095238</v>
       </c>
-      <c r="AB34" s="11">
+      <c r="AB34" s="10">
         <f t="shared" si="11"/>
         <v>19404</v>
       </c>
-      <c r="AC34" s="11">
+      <c r="AC34" s="10">
         <f t="shared" si="3"/>
         <v>1.8071383237838745E-5</v>
       </c>
-      <c r="AD34" s="11">
+      <c r="AD34" s="10">
         <f t="shared" si="4"/>
         <v>105000</v>
       </c>
-      <c r="AE34" s="11">
+      <c r="AE34" s="10">
         <f t="shared" si="5"/>
         <v>9.7788870334625244E-5</v>
       </c>
-      <c r="AF34" s="11">
+      <c r="AF34" s="10">
         <f t="shared" si="6"/>
         <v>0.10013580322265625</v>
       </c>
-      <c r="AG34" s="11">
+      <c r="AG34" s="10">
         <f t="shared" si="7"/>
         <v>102.5390625</v>
       </c>
     </row>
     <row r="35" spans="2:33" ht="24" x14ac:dyDescent="0.3">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <f>C32*C33+D32*D33+E32*E33+F32*F33</f>
         <v>2</v>
       </c>
-      <c r="V35" s="10">
+      <c r="V35" s="9">
         <v>22</v>
       </c>
-      <c r="W35" s="8">
+      <c r="W35" s="7">
         <f t="shared" si="12"/>
         <v>484</v>
       </c>
-      <c r="X35" s="12">
+      <c r="X35" s="11">
         <f t="shared" si="10"/>
         <v>231</v>
       </c>
-      <c r="Y35" s="11">
+      <c r="Y35" s="10">
         <f t="shared" si="13"/>
         <v>47.727272727272727</v>
       </c>
-      <c r="Z35" s="11">
+      <c r="Z35" s="10">
         <f t="shared" si="8"/>
         <v>253</v>
       </c>
-      <c r="AA35" s="11">
+      <c r="AA35" s="10">
         <f t="shared" si="2"/>
         <v>52.272727272727273</v>
       </c>
-      <c r="AB35" s="11">
+      <c r="AB35" s="10">
         <f t="shared" si="11"/>
         <v>22264</v>
       </c>
-      <c r="AC35" s="11">
+      <c r="AC35" s="10">
         <f t="shared" si="3"/>
         <v>2.0734965801239014E-5</v>
       </c>
-      <c r="AD35" s="11">
+      <c r="AD35" s="10">
         <f t="shared" si="4"/>
         <v>110000</v>
       </c>
-      <c r="AE35" s="11">
+      <c r="AE35" s="10">
         <f t="shared" si="5"/>
         <v>1.0244548320770264E-4</v>
       </c>
-      <c r="AF35" s="11">
+      <c r="AF35" s="10">
         <f t="shared" si="6"/>
         <v>0.1049041748046875</v>
       </c>
-      <c r="AG35" s="11">
+      <c r="AG35" s="10">
         <f t="shared" si="7"/>
         <v>107.421875</v>
       </c>
     </row>
     <row r="36" spans="2:33" ht="24" x14ac:dyDescent="0.3">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <f>ROUND(C35/(G32*G33),4)</f>
         <v>0.5</v>
       </c>
-      <c r="O36" s="6" t="s">
+      <c r="O36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P36" s="6" t="s">
+      <c r="P36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Q36" s="6" t="s">
+      <c r="Q36" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="V36" s="10">
+      <c r="V36" s="9">
         <v>23</v>
       </c>
-      <c r="W36" s="8">
+      <c r="W36" s="7">
         <f t="shared" si="12"/>
         <v>529</v>
       </c>
-      <c r="X36" s="12">
+      <c r="X36" s="11">
         <f t="shared" si="10"/>
         <v>253</v>
       </c>
-      <c r="Y36" s="11">
+      <c r="Y36" s="10">
         <f t="shared" si="13"/>
         <v>47.826086956521742</v>
       </c>
-      <c r="Z36" s="11">
+      <c r="Z36" s="10">
         <f t="shared" si="8"/>
         <v>276</v>
       </c>
-      <c r="AA36" s="11">
+      <c r="AA36" s="10">
         <f t="shared" si="2"/>
         <v>52.173913043478258</v>
       </c>
-      <c r="AB36" s="11">
+      <c r="AB36" s="10">
         <f t="shared" si="11"/>
         <v>25392</v>
       </c>
-      <c r="AC36" s="11">
+      <c r="AC36" s="10">
         <f t="shared" si="3"/>
         <v>2.364814281463623E-5</v>
       </c>
-      <c r="AD36" s="11">
+      <c r="AD36" s="10">
         <f t="shared" si="4"/>
         <v>115000</v>
       </c>
-      <c r="AE36" s="11">
+      <c r="AE36" s="10">
         <f t="shared" si="5"/>
         <v>1.0710209608078003E-4</v>
       </c>
-      <c r="AF36" s="11">
+      <c r="AF36" s="10">
         <f t="shared" si="6"/>
         <v>0.10967254638671875</v>
       </c>
-      <c r="AG36" s="11">
+      <c r="AG36" s="10">
         <f t="shared" si="7"/>
         <v>112.3046875</v>
       </c>
     </row>
     <row r="37" spans="2:33" ht="24" x14ac:dyDescent="0.3">
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <f>ACOS(C36)</f>
         <v>1.0471975511965976</v>
       </c>
-      <c r="O37" s="6" t="s">
+      <c r="O37" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P37" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="6">
-        <v>1</v>
-      </c>
-      <c r="V37" s="10">
+      <c r="P37" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>1</v>
+      </c>
+      <c r="V37" s="9">
         <v>24</v>
       </c>
-      <c r="W37" s="8">
+      <c r="W37" s="7">
         <f t="shared" si="12"/>
         <v>576</v>
       </c>
-      <c r="X37" s="12">
+      <c r="X37" s="11">
         <f t="shared" si="10"/>
         <v>276</v>
       </c>
-      <c r="Y37" s="11">
+      <c r="Y37" s="10">
         <f t="shared" si="13"/>
         <v>47.916666666666664</v>
       </c>
-      <c r="Z37" s="11">
+      <c r="Z37" s="10">
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="AA37" s="11">
+      <c r="AA37" s="10">
         <f t="shared" si="2"/>
         <v>52.083333333333336</v>
       </c>
-      <c r="AB37" s="11">
+      <c r="AB37" s="10">
         <f t="shared" si="11"/>
         <v>28800</v>
       </c>
-      <c r="AC37" s="11">
+      <c r="AC37" s="10">
         <f t="shared" si="3"/>
         <v>2.6822090148925781E-5</v>
       </c>
-      <c r="AD37" s="11">
+      <c r="AD37" s="10">
         <f t="shared" si="4"/>
         <v>120000</v>
       </c>
-      <c r="AE37" s="11">
+      <c r="AE37" s="10">
         <f t="shared" si="5"/>
         <v>1.1175870895385742E-4</v>
       </c>
-      <c r="AF37" s="11">
+      <c r="AF37" s="10">
         <f t="shared" si="6"/>
         <v>0.11444091796875</v>
       </c>
-      <c r="AG37" s="11">
+      <c r="AG37" s="10">
         <f t="shared" si="7"/>
         <v>117.1875</v>
       </c>
     </row>
     <row r="38" spans="2:33" ht="24" x14ac:dyDescent="0.3">
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="3">
         <f>ROUND(C37/PI(),4)</f>
         <v>0.33329999999999999</v>
       </c>
-      <c r="O38" s="6" t="s">
+      <c r="O38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="P38" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="6">
-        <v>1</v>
-      </c>
-      <c r="V38" s="10">
+      <c r="P38" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>1</v>
+      </c>
+      <c r="V38" s="9">
         <v>25</v>
       </c>
-      <c r="W38" s="8">
+      <c r="W38" s="7">
         <f t="shared" si="12"/>
         <v>625</v>
       </c>
-      <c r="X38" s="12">
+      <c r="X38" s="11">
         <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="Y38" s="11">
+      <c r="Y38" s="10">
         <f t="shared" si="13"/>
         <v>48</v>
       </c>
-      <c r="Z38" s="11">
+      <c r="Z38" s="10">
         <f t="shared" si="8"/>
         <v>325</v>
       </c>
-      <c r="AA38" s="11">
+      <c r="AA38" s="10">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="AB38" s="11">
+      <c r="AB38" s="10">
         <f t="shared" si="11"/>
         <v>32500</v>
       </c>
-      <c r="AC38" s="11">
+      <c r="AC38" s="10">
         <f t="shared" si="3"/>
         <v>3.0267983675003052E-5</v>
       </c>
-      <c r="AD38" s="11">
+      <c r="AD38" s="10">
         <f t="shared" si="4"/>
         <v>125000</v>
       </c>
-      <c r="AE38" s="11">
+      <c r="AE38" s="10">
         <f t="shared" si="5"/>
         <v>1.1641532182693481E-4</v>
       </c>
-      <c r="AF38" s="11">
+      <c r="AF38" s="10">
         <f t="shared" si="6"/>
         <v>0.11920928955078125</v>
       </c>
-      <c r="AG38" s="11">
+      <c r="AG38" s="10">
         <f t="shared" si="7"/>
         <v>122.0703125</v>
       </c>
     </row>
     <row r="39" spans="2:33" ht="24" x14ac:dyDescent="0.3">
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="3">
         <f>ROUND(DEGREES(C37),0)</f>
         <v>60</v>
       </c>
-      <c r="O39" s="6" t="s">
+      <c r="O39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="5">
         <v>2</v>
       </c>
-      <c r="Q39" s="6">
-        <v>1</v>
-      </c>
-      <c r="U39" s="7" t="s">
+      <c r="Q39" s="5">
+        <v>1</v>
+      </c>
+      <c r="U39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="V39" s="10" t="s">
+      <c r="V39" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="W39" s="8" t="s">
+      <c r="W39" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="X39" s="12" t="s">
+      <c r="X39" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="Y39" s="11" t="s">
+      <c r="Y39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Z39" s="11" t="s">
+      <c r="Z39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AA39" s="11" t="s">
+      <c r="AA39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AB39" s="11" t="s">
+      <c r="AB39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AC39" s="11" t="s">
+      <c r="AC39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AD39" s="11" t="s">
+      <c r="AD39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AE39" s="11" t="s">
+      <c r="AE39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AF39" s="11" t="s">
+      <c r="AF39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AG39" s="11" t="s">
+      <c r="AG39" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40" spans="2:33" ht="25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="4">
         <f>1-ROUND(C38,4)</f>
         <v>0.66670000000000007</v>
       </c>
-      <c r="O40" s="6" t="s">
+      <c r="O40" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P40" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="6">
+      <c r="P40" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="5">
         <v>3</v>
       </c>
-      <c r="U40" s="7" t="s">
+      <c r="U40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="V40" s="10">
+      <c r="V40" s="9">
         <v>74550</v>
       </c>
-      <c r="W40" s="8">
+      <c r="W40" s="7">
         <f>V40*V40</f>
         <v>5557702500</v>
       </c>
-      <c r="X40" s="12">
+      <c r="X40" s="11">
         <f t="shared" si="10"/>
         <v>2778813975</v>
       </c>
-      <c r="Y40" s="11">
+      <c r="Y40" s="10">
         <f>X40*100/W40</f>
         <v>49.999329309188461</v>
       </c>
-      <c r="Z40" s="11">
+      <c r="Z40" s="10">
         <f t="shared" si="8"/>
         <v>2778888525</v>
       </c>
-      <c r="AA40" s="11">
+      <c r="AA40" s="10">
         <f t="shared" si="2"/>
         <v>50.000670690811539</v>
       </c>
-      <c r="AB40" s="11">
+      <c r="AB40" s="10">
         <f t="shared" si="11"/>
         <v>828664558155000</v>
       </c>
-      <c r="AC40" s="11">
+      <c r="AC40" s="10">
         <f t="shared" si="3"/>
         <v>771754.00979351252</v>
       </c>
-      <c r="AD40" s="11">
+      <c r="AD40" s="10">
         <f t="shared" si="4"/>
         <v>372750000</v>
       </c>
-      <c r="AE40" s="11">
+      <c r="AE40" s="10">
         <f t="shared" si="5"/>
         <v>0.34715048968791962</v>
       </c>
-      <c r="AF40" s="11">
+      <c r="AF40" s="10">
         <f t="shared" si="6"/>
         <v>355.48210144042969</v>
       </c>
-      <c r="AG40" s="11">
+      <c r="AG40" s="10">
         <f t="shared" si="7"/>
         <v>364013.671875</v>
       </c>
     </row>
     <row r="41" spans="2:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O41" s="6" t="s">
+      <c r="O41" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="5">
         <v>2</v>
       </c>
-      <c r="Q41" s="6">
+      <c r="Q41" s="5">
         <v>2</v>
       </c>
-      <c r="U41" s="13">
+      <c r="U41" s="12">
         <v>5000</v>
       </c>
-      <c r="V41" s="14">
+      <c r="V41" s="13">
         <v>5000</v>
       </c>
-      <c r="W41" s="15">
+      <c r="W41" s="14">
         <f>V41*V41</f>
         <v>25000000</v>
       </c>
-      <c r="X41" s="16">
+      <c r="X41" s="15">
         <f t="shared" si="10"/>
         <v>12497500</v>
       </c>
-      <c r="Y41" s="17">
+      <c r="Y41" s="16">
         <f>X41*100/W41</f>
         <v>49.99</v>
       </c>
-      <c r="Z41" s="17">
+      <c r="Z41" s="16">
         <f t="shared" si="8"/>
         <v>12502500</v>
       </c>
-      <c r="AA41" s="17">
+      <c r="AA41" s="16">
         <f t="shared" si="2"/>
         <v>50.01</v>
       </c>
-      <c r="AB41" s="17">
+      <c r="AB41" s="16">
         <f t="shared" si="11"/>
         <v>250050000000</v>
       </c>
-      <c r="AC41" s="17">
+      <c r="AC41" s="16">
         <f t="shared" si="3"/>
         <v>232.8772097826004</v>
       </c>
-      <c r="AD41" s="18">
+      <c r="AD41" s="17">
         <f t="shared" si="4"/>
         <v>25000000</v>
       </c>
-      <c r="AE41" s="19">
+      <c r="AE41" s="18">
         <f t="shared" si="5"/>
         <v>2.3283064365386963E-2</v>
       </c>
-      <c r="AF41" s="19">
+      <c r="AF41" s="18">
         <f t="shared" si="6"/>
         <v>23.84185791015625</v>
       </c>
-      <c r="AG41" s="20">
+      <c r="AG41" s="19">
         <f t="shared" si="7"/>
         <v>24414.0625</v>
       </c>
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="O42" s="6" t="s">
+      <c r="O42" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P42" s="6">
+      <c r="P42" s="5">
         <v>3</v>
       </c>
-      <c r="Q42" s="6">
+      <c r="Q42" s="5">
         <v>1</v>
       </c>
       <c r="U42">
         <v>1000</v>
       </c>
-      <c r="V42" s="10">
+      <c r="V42" s="9">
         <v>1000</v>
       </c>
-      <c r="W42" s="8">
+      <c r="W42" s="7">
         <f>V42*V42</f>
         <v>1000000</v>
       </c>
-      <c r="X42" s="12">
+      <c r="X42" s="11">
         <f t="shared" si="10"/>
         <v>499500</v>
       </c>
-      <c r="Y42" s="11">
+      <c r="Y42" s="10">
         <f>X42*100/W42</f>
         <v>49.95</v>
       </c>
-      <c r="Z42" s="11">
+      <c r="Z42" s="10">
         <f t="shared" si="8"/>
         <v>500500</v>
       </c>
-      <c r="AA42" s="11">
+      <c r="AA42" s="10">
         <f t="shared" si="2"/>
         <v>50.05</v>
       </c>
-      <c r="AB42" s="11">
+      <c r="AB42" s="10">
         <f t="shared" si="11"/>
         <v>2002000000</v>
       </c>
-      <c r="AC42" s="11">
+      <c r="AC42" s="10">
         <f t="shared" si="3"/>
         <v>1.864507794380188</v>
       </c>
-      <c r="AD42" s="11">
+      <c r="AD42" s="10">
         <f t="shared" si="4"/>
         <v>5000000</v>
       </c>
-      <c r="AE42" s="11">
+      <c r="AE42" s="10">
         <f t="shared" si="5"/>
         <v>4.6566128730773926E-3</v>
       </c>
-      <c r="AF42" s="11">
+      <c r="AF42" s="10">
         <f t="shared" si="6"/>
         <v>4.76837158203125</v>
       </c>
-      <c r="AG42" s="11">
+      <c r="AG42" s="10">
         <f t="shared" si="7"/>
         <v>4882.8125</v>
       </c>
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="O43" s="6" t="s">
+      <c r="O43" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P43" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="6">
+      <c r="P43" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="2:33" ht="27" x14ac:dyDescent="0.2">
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="O44" s="6" t="s">
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="O44" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="5">
         <v>2</v>
       </c>
-      <c r="Q44" s="6">
+      <c r="Q44" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="45" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="O45" s="6" t="s">
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="O45" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="5">
         <v>3</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="Q45" s="5">
         <v>6</v>
       </c>
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23" t="s">
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23" t="s">
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="I46" s="21"/>
-      <c r="O46" s="6" t="s">
+      <c r="I46" s="20"/>
+      <c r="O46" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P46" s="6">
+      <c r="P46" s="5">
         <v>4</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="Q46" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B47" s="26" t="s">
+      <c r="B47" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="26" t="s">
+      <c r="D47" s="20"/>
+      <c r="E47" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="G47" s="21"/>
-      <c r="H47" s="26" t="s">
+      <c r="G47" s="20"/>
+      <c r="H47" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="29" t="s">
+      <c r="I47" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="O47" s="6" t="s">
+      <c r="O47" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P47" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="6">
+      <c r="P47" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="21"/>
-      <c r="E48" s="26" t="s">
+      <c r="D48" s="20"/>
+      <c r="E48" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="26" t="s">
+      <c r="G48" s="20"/>
+      <c r="H48" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I48" s="29" t="s">
+      <c r="I48" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="O48" s="6" t="s">
+      <c r="O48" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P48" s="6">
+      <c r="P48" s="5">
         <v>2</v>
       </c>
-      <c r="Q48" s="6">
+      <c r="Q48" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="26" t="s">
+      <c r="D49" s="20"/>
+      <c r="E49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="29" t="s">
+      <c r="F49" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="26" t="s">
+      <c r="G49" s="20"/>
+      <c r="H49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I49" s="29" t="s">
+      <c r="I49" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O49" s="6" t="s">
+      <c r="O49" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P49" s="6">
+      <c r="P49" s="5">
         <v>3</v>
       </c>
-      <c r="Q49" s="6">
+      <c r="Q49" s="5">
         <v>9</v>
       </c>
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B50" s="26"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="O50" s="6" t="s">
+      <c r="B50" s="25"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="O50" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P50" s="6">
+      <c r="P50" s="5">
         <v>4</v>
       </c>
-      <c r="Q50" s="6">
+      <c r="Q50" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="23" t="s">
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="O51" s="6" t="s">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="O51" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P51" s="6">
+      <c r="P51" s="5">
         <v>5</v>
       </c>
-      <c r="Q51" s="6">
+      <c r="Q51" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="O52" s="6" t="s">
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="O52" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P52" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="6">
+      <c r="P52" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B53" s="26" t="s">
+      <c r="B53" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="O53" s="6" t="s">
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="O53" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P53" s="6">
+      <c r="P53" s="5">
         <v>2</v>
       </c>
-      <c r="Q53" s="6">
+      <c r="Q53" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21" t="s">
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="O54" s="6" t="s">
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="O54" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P54" s="6">
+      <c r="P54" s="5">
         <v>3</v>
       </c>
-      <c r="Q54" s="6">
+      <c r="Q54" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C55" s="21">
+      <c r="C55" s="20">
         <v>-1</v>
       </c>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="O55" s="6" t="s">
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="O55" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P55" s="6">
+      <c r="P55" s="5">
         <v>4</v>
       </c>
-      <c r="Q55" s="6">
+      <c r="Q55" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="O56" s="6" t="s">
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="O56" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="6">
+      <c r="P56" s="5">
         <v>5</v>
       </c>
-      <c r="Q56" s="6">
+      <c r="Q56" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="57" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B57" s="21"/>
-      <c r="C57" s="31" t="s">
+      <c r="B57" s="20"/>
+      <c r="C57" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="O57" s="6" t="s">
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="O57" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P57" s="6">
+      <c r="P57" s="5">
         <v>6</v>
       </c>
-      <c r="Q57" s="6">
+      <c r="Q57" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B59" s="26" t="s">
+      <c r="B59" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21" t="s">
+      <c r="C59" s="20"/>
+      <c r="D59" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B60" s="26" t="s">
+      <c r="B60" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21" t="s">
+      <c r="C60" s="20"/>
+      <c r="D60" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="O60" s="25" t="s">
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="O60" s="24" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="61" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B61" s="26" t="s">
+      <c r="B61" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21" t="s">
+      <c r="C61" s="20"/>
+      <c r="D61" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="21" t="s">
+      <c r="E61" s="29"/>
+      <c r="F61" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="O61" s="6" t="s">
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="O61" s="5" t="s">
         <v>34</v>
       </c>
       <c r="P61" t="s">
@@ -4579,20 +5061,20 @@
       </c>
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21" t="s">
+      <c r="C62" s="20"/>
+      <c r="D62" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="32">
-        <v>1</v>
-      </c>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="31">
+        <v>1</v>
+      </c>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
       <c r="O62">
         <v>1</v>
       </c>
@@ -4601,48 +5083,48 @@
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
     </row>
     <row r="64" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B64" s="21"/>
-      <c r="C64" s="31" t="s">
+      <c r="B64" s="20"/>
+      <c r="C64" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B65" s="26"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B66" s="26" t="s">
+      <c r="B66" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21" t="s">
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="G66" s="21"/>
+      <c r="G66" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokenkino/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D727BC18-9C3F-2049-9D3C-AA407D50BB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7938D3-9CC4-424F-A5BF-28DBE0E3CE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21460" activeTab="1" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
     <sheet name="Key Concepts" sheetId="3" r:id="rId2"/>
-    <sheet name="Test sheet" sheetId="2" r:id="rId3"/>
+    <sheet name="LL" sheetId="5" r:id="rId3"/>
+    <sheet name="Test sheet 1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="277">
   <si>
     <t>essere</t>
   </si>
@@ -742,12 +743,6 @@
     <t>how?</t>
   </si>
   <si>
-    <t>Analisi di IF</t>
-  </si>
-  <si>
-    <t>Analisi di NOT</t>
-  </si>
-  <si>
     <t>mode</t>
   </si>
   <si>
@@ -784,15 +779,9 @@
     <t>facts</t>
   </si>
   <si>
-    <t>believes</t>
-  </si>
-  <si>
     <t>collection</t>
   </si>
   <si>
-    <t>statements[]</t>
-  </si>
-  <si>
     <t>opinions</t>
   </si>
   <si>
@@ -808,30 +797,12 @@
     <t>operations</t>
   </si>
   <si>
-    <t>eval(statement)</t>
-  </si>
-  <si>
     <t>low level</t>
   </si>
   <si>
-    <t>similarity to facts, believes, opinions -&gt; fuzzy (-1,1)</t>
-  </si>
-  <si>
-    <t>find something clever</t>
-  </si>
-  <si>
-    <t>code myself</t>
-  </si>
-  <si>
-    <t>find common sense statements</t>
-  </si>
-  <si>
     <t>spaCy costruisce SL da NL</t>
   </si>
   <si>
-    <t>Analysis</t>
-  </si>
-  <si>
     <t>base|place|core-statement</t>
   </si>
   <si>
@@ -851,13 +822,268 @@
   </si>
   <si>
     <t>core-statement</t>
+  </si>
+  <si>
+    <t>axioms</t>
+  </si>
+  <si>
+    <t>collect common sense truths</t>
+  </si>
+  <si>
+    <t>Deduzione</t>
+  </si>
+  <si>
+    <t>statements</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>&amp;&amp;,||,!</t>
+  </si>
+  <si>
+    <t>operator</t>
+  </si>
+  <si>
+    <t>truth</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">logical: or, and, not (A op B): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>io sono contento oppure non sono contento, io non sono contento, io sono contento e sono vivo</t>
+    </r>
+  </si>
+  <si>
+    <t>XNOR</t>
+  </si>
+  <si>
+    <t>IMPLY</t>
+  </si>
+  <si>
+    <t>CONVERSE</t>
+  </si>
+  <si>
+    <t>OP</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>math op</t>
+  </si>
+  <si>
+    <t>input NL (natural language)</t>
+  </si>
+  <si>
+    <t>compiler to LL (logical language)</t>
+  </si>
+  <si>
+    <t>compile</t>
+  </si>
+  <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">equivalence (A&lt;=&gt;C): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>io sono contento se e solo se sono vivo e sono vivo solo se e solo se sono contento</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(A===C)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">necessary  (A&lt;=C): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>io sono contento se e solo se sono vivo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">sufficient  (A=&gt;C): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>io sono contento se suono</t>
+    </r>
+  </si>
+  <si>
+    <t>A=antecedent (io suono) (IF A)</t>
+  </si>
+  <si>
+    <t>A=antecedent (io sono vivo) (ONLY IF A)</t>
+  </si>
+  <si>
+    <t>A=antecedent (io sono vivo)</t>
+  </si>
+  <si>
+    <t>C=consequent (io sono contento) (THEN B)</t>
+  </si>
+  <si>
+    <t>B=consequent (io sono contento)</t>
+  </si>
+  <si>
+    <t>connection</t>
+  </si>
+  <si>
+    <t>===</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>OP2</t>
+  </si>
+  <si>
+    <t>OP1</t>
+  </si>
+  <si>
+    <t>S=simple (io sono vivo)</t>
+  </si>
+  <si>
+    <t>S=simple (io sono contento)</t>
+  </si>
+  <si>
+    <t>OP1 x OP2 y …</t>
+  </si>
+  <si>
+    <t>Steps:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">evaluate each part with logic rules, es: ((A1 &amp;&amp; A2 =&gt; C1) || (A3 === C2)) &amp;&amp; S1 = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;fuzzy value&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>LL statement</t>
+  </si>
+  <si>
+    <t>fuzzy value</t>
+  </si>
+  <si>
+    <t>LL statement[]</t>
+  </si>
+  <si>
+    <t>split statements</t>
+  </si>
+  <si>
+    <t>LL statements[]</t>
+  </si>
+  <si>
+    <t>eval statements[]</t>
+  </si>
+  <si>
+    <t>eval statement</t>
+  </si>
+  <si>
+    <t>similarity to facts, axioms</t>
+  </si>
+  <si>
+    <t>agree</t>
+  </si>
+  <si>
+    <t>similarity to facts, axioms, opinions</t>
+  </si>
+  <si>
+    <t>fuzzy value, list of assumptions (believes, opinions)</t>
+  </si>
+  <si>
+    <t>steps</t>
+  </si>
+  <si>
+    <t>experienced + hardcoded</t>
+  </si>
+  <si>
+    <t>collect strong believes + deduce from axioms, facts and opinions</t>
+  </si>
+  <si>
+    <t>deduce from axioms, facts</t>
+  </si>
+  <si>
+    <t>solve equation for missing values (facts, axioms) having the value of the entire statement (present in facts, axioms)</t>
+  </si>
+  <si>
+    <t>solve equation for missing values (facts, axioms, opinions) having the value of the entire statement (present in facts, axioms, opinion)</t>
+  </si>
+  <si>
+    <t>demonstrate</t>
+  </si>
+  <si>
+    <t>new fact</t>
+  </si>
+  <si>
+    <t>new opinion</t>
+  </si>
+  <si>
+    <t>formOpinion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -962,8 +1188,15 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -991,8 +1224,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1061,6 +1300,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1068,7 +1396,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1173,14 +1501,103 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1853,12 +2270,12 @@
       <c r="D30" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
       <c r="I30" s="22" t="s">
         <v>123</v>
       </c>
@@ -1929,12 +2346,12 @@
       <c r="D36" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="42" t="s">
+      <c r="E36" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B37" s="22">
@@ -2129,7 +2546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FCF69A-7541-8F49-8917-87CA28DC0269}">
-  <dimension ref="B2:M28"/>
+  <dimension ref="B2:M29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="3.83203125" style="20" customWidth="1"/>
@@ -2137,7 +2554,8 @@
     <col min="4" max="4" width="18.33203125" style="20" customWidth="1"/>
     <col min="5" max="5" width="25.6640625" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="14" width="19" style="20" customWidth="1"/>
+    <col min="7" max="7" width="23.5" style="20" customWidth="1"/>
+    <col min="8" max="14" width="19" style="20" customWidth="1"/>
     <col min="15" max="16384" width="10.83203125" style="20"/>
   </cols>
   <sheetData>
@@ -2157,7 +2575,7 @@
         <v>177</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G4" s="37" t="s">
         <v>147</v>
@@ -2183,13 +2601,13 @@
     </row>
     <row r="5" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="C5" s="20" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>182</v>
@@ -2207,10 +2625,10 @@
         <v>184</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
@@ -2227,11 +2645,8 @@
       <c r="L6" s="31"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="C7" s="20" t="s">
-        <v>190</v>
-      </c>
       <c r="E7" s="22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F7" s="37" t="s">
         <v>182</v>
@@ -2246,17 +2661,16 @@
         <v>183</v>
       </c>
       <c r="J7" s="37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="L7" s="31"/>
+        <v>190</v>
+      </c>
+      <c r="L7" s="37" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="8" spans="2:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="C8" s="20" t="s">
-        <v>191</v>
-      </c>
       <c r="F8" s="39" t="s">
         <v>79</v>
       </c>
@@ -2264,22 +2678,24 @@
         <v>79</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="J8" s="39" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="L8" s="39"/>
+        <v>191</v>
+      </c>
+      <c r="L8" s="39" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="9" spans="2:13" ht="34" x14ac:dyDescent="0.2">
       <c r="E9" s="22" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F9" s="39" t="s">
         <v>8</v>
@@ -2288,10 +2704,10 @@
         <v>8</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="J9" s="39" t="s">
         <v>8</v>
@@ -2299,7 +2715,9 @@
       <c r="K9" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="39"/>
+      <c r="L9" s="39" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E10" s="22"/>
@@ -2322,21 +2740,21 @@
     </row>
     <row r="12" spans="2:13" ht="19" x14ac:dyDescent="0.2">
       <c r="E12" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>197</v>
-      </c>
       <c r="G12" s="22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="34" x14ac:dyDescent="0.2">
       <c r="E13" s="23" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>79</v>
@@ -2347,7 +2765,7 @@
         <v>125</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>125</v>
@@ -2355,102 +2773,93 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E15" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="3:10" ht="19" x14ac:dyDescent="0.2">
       <c r="E17" s="27" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.2">
       <c r="E18" s="25" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="E19" s="25" t="s">
-        <v>204</v>
+      <c r="E19" s="20" t="s">
+        <v>201</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>216</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.2">
       <c r="E20" s="25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" ht="19" x14ac:dyDescent="0.2">
-      <c r="E22" s="27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="E23" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" ht="19" x14ac:dyDescent="0.2">
+      <c r="E23" s="27"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="36"/>
       <c r="J24" s="36"/>
     </row>
-    <row r="25" spans="3:10" ht="27" x14ac:dyDescent="0.2">
-      <c r="C25" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+    </row>
+    <row r="26" spans="3:10" ht="27" x14ac:dyDescent="0.2">
+      <c r="C26" s="21"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="36"/>
-      <c r="J26" s="36"/>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="F27" s="25"/>
+      <c r="G27" s="36"/>
+      <c r="J27" s="36"/>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.2">
       <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F29" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2458,7 +2867,978 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840613CA-C2FC-084B-A8EC-CC09502BFF2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0889CCB1-49C5-2548-AD66-B49F18C82431}">
+  <dimension ref="C2:U46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="4" width="14.5" customWidth="1"/>
+    <col min="5" max="17" width="13.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.1640625" style="5" customWidth="1"/>
+    <col min="21" max="21" width="16.83203125" style="5" customWidth="1"/>
+    <col min="22" max="22" width="36.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:18" ht="32" x14ac:dyDescent="0.4">
+      <c r="C2" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" s="42"/>
+    </row>
+    <row r="4" spans="3:18" ht="27" x14ac:dyDescent="0.35">
+      <c r="C4" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="R4" s="69" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+    </row>
+    <row r="6" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C6" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C7" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C8" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J8" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="K8" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="L8" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="M8" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="N8" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="O8" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="P8" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C9" s="58" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="K9" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="53"/>
+      <c r="Q9" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="61"/>
+    </row>
+    <row r="10" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C10" s="70"/>
+      <c r="D10" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5"/>
+    </row>
+    <row r="11" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C11" s="70"/>
+      <c r="D11" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="53"/>
+      <c r="Q11" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5"/>
+    </row>
+    <row r="12" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C12" s="59"/>
+      <c r="D12" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="5"/>
+    </row>
+    <row r="13" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+    </row>
+    <row r="14" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C14" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="54" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C15" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+    </row>
+    <row r="16" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C16" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="K16" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="L16" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="M16" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="N16" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="O16" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="P16" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C17" s="58" t="s">
+        <v>247</v>
+      </c>
+      <c r="D17" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="K17" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="5"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C18" s="70"/>
+      <c r="D18" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="5"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C19" s="70"/>
+      <c r="D19" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C20" s="59"/>
+      <c r="D20" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="60" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="5"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C22" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C23" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C24" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I24" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="K24" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="M24" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="N24" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="P24" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C25" s="58" t="s">
+        <v>247</v>
+      </c>
+      <c r="D25" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="71" t="s">
+        <v>246</v>
+      </c>
+      <c r="K25" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" s="5"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C26" s="70"/>
+      <c r="D26" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C27" s="70"/>
+      <c r="D27" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="63" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="5"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C28" s="59"/>
+      <c r="D28" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="60" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" s="5"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="5"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C30" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="51"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="54" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C31" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="K31" s="47"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="47"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C32" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="K32" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="L32" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="M32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="N32" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="O32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="P32" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+    </row>
+    <row r="33" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C33" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="K33" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="55" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="35" spans="3:21" ht="27" x14ac:dyDescent="0.35">
+      <c r="C35" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="D35" s="68"/>
+    </row>
+    <row r="36" spans="3:21" ht="27" x14ac:dyDescent="0.35">
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="F36" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="56"/>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C37" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37" s="57">
+        <v>1</v>
+      </c>
+      <c r="H37" s="57">
+        <v>2</v>
+      </c>
+      <c r="K37" s="57">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="57" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" t="s">
+        <v>233</v>
+      </c>
+      <c r="F39" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>258</v>
+      </c>
+      <c r="T39"/>
+    </row>
+    <row r="40" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>236</v>
+      </c>
+      <c r="D40" t="s">
+        <v>260</v>
+      </c>
+      <c r="F40" t="s">
+        <v>261</v>
+      </c>
+      <c r="H40" t="s">
+        <v>259</v>
+      </c>
+      <c r="K40" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>257</v>
+      </c>
+      <c r="T40"/>
+      <c r="U40"/>
+    </row>
+    <row r="41" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" t="s">
+        <v>256</v>
+      </c>
+      <c r="F41" t="s">
+        <v>262</v>
+      </c>
+      <c r="H41" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>257</v>
+      </c>
+      <c r="T41"/>
+      <c r="U41"/>
+    </row>
+    <row r="42" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>264</v>
+      </c>
+      <c r="D42" t="s">
+        <v>260</v>
+      </c>
+      <c r="F42" t="s">
+        <v>261</v>
+      </c>
+      <c r="H42" t="s">
+        <v>259</v>
+      </c>
+      <c r="K42" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>264</v>
+      </c>
+      <c r="D43" t="s">
+        <v>256</v>
+      </c>
+      <c r="F43" t="s">
+        <v>262</v>
+      </c>
+      <c r="H43" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C44" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" t="s">
+        <v>261</v>
+      </c>
+      <c r="H44" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C45" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" t="s">
+        <v>260</v>
+      </c>
+      <c r="F45" t="s">
+        <v>261</v>
+      </c>
+      <c r="H45" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C46" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="K19:P19"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBDF187D-47D8-524F-BF49-BA78AE579A0A}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
@@ -2522,13 +3902,13 @@
       <c r="R7" s="44"/>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
       <c r="O8" s="44"/>
       <c r="P8" s="44"/>
       <c r="Q8" s="44"/>
@@ -2825,7 +4205,7 @@
         <v>66.666666666666671</v>
       </c>
       <c r="AB15" s="10">
-        <f t="shared" ref="AB15:AB20" si="1">((V15 * (V15+1)) / 2)*4*V15</f>
+        <f t="shared" ref="AB15:AB42" si="1">((V15 * (V15+1)) / 2)*4*V15</f>
         <v>72</v>
       </c>
       <c r="AC15" s="10">
@@ -3248,7 +4628,7 @@
         <v>55.555555555555557</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" ref="AB21:AB42" si="11">((V21 * (V21+1)) / 2)*4*V21</f>
+        <f t="shared" si="1"/>
         <v>1620</v>
       </c>
       <c r="AC21" s="10">
@@ -3321,7 +4701,7 @@
         <v>55</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>2200</v>
       </c>
       <c r="AC22" s="10">
@@ -3394,7 +4774,7 @@
         <v>54.545454545454547</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>2904</v>
       </c>
       <c r="AC23" s="10">
@@ -3443,7 +4823,7 @@
         <v>54.166666666666664</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>3744</v>
       </c>
       <c r="AC24" s="10">
@@ -3517,7 +4897,7 @@
         <v>53.846153846153847</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>4732</v>
       </c>
       <c r="AC25" s="10">
@@ -3591,7 +4971,7 @@
         <v>53.571428571428569</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>5880</v>
       </c>
       <c r="AC26" s="10">
@@ -3665,7 +5045,7 @@
         <v>53.333333333333336</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>7200</v>
       </c>
       <c r="AC27" s="10">
@@ -3739,7 +5119,7 @@
         <v>53.125</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>8704</v>
       </c>
       <c r="AC28" s="10">
@@ -3813,7 +5193,7 @@
         <v>52.941176470588232</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>10404</v>
       </c>
       <c r="AC29" s="10">
@@ -3883,7 +5263,7 @@
         <v>52.777777777777779</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>12312</v>
       </c>
       <c r="AC30" s="10">
@@ -3968,7 +5348,7 @@
         <v>52.631578947368418</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>14440</v>
       </c>
       <c r="AC31" s="10">
@@ -4056,7 +5436,7 @@
         <v>20</v>
       </c>
       <c r="W33" s="7">
-        <f t="shared" ref="W33:W38" si="12">V33*V33</f>
+        <f t="shared" ref="W33:W38" si="11">V33*V33</f>
         <v>400</v>
       </c>
       <c r="X33" s="11">
@@ -4064,7 +5444,7 @@
         <v>190</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33:Y38" si="13">X33*100/W33</f>
+        <f t="shared" ref="Y33:Y38" si="12">X33*100/W33</f>
         <v>47.5</v>
       </c>
       <c r="Z33" s="10">
@@ -4076,7 +5456,7 @@
         <v>52.5</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>16800</v>
       </c>
       <c r="AC33" s="10">
@@ -4108,7 +5488,7 @@
         <v>21</v>
       </c>
       <c r="W34" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>441</v>
       </c>
       <c r="X34" s="11">
@@ -4116,7 +5496,7 @@
         <v>210</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>47.61904761904762</v>
       </c>
       <c r="Z34" s="10">
@@ -4128,7 +5508,7 @@
         <v>52.38095238095238</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>19404</v>
       </c>
       <c r="AC34" s="10">
@@ -4164,7 +5544,7 @@
         <v>22</v>
       </c>
       <c r="W35" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>484</v>
       </c>
       <c r="X35" s="11">
@@ -4172,7 +5552,7 @@
         <v>231</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>47.727272727272727</v>
       </c>
       <c r="Z35" s="10">
@@ -4184,7 +5564,7 @@
         <v>52.272727272727273</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>22264</v>
       </c>
       <c r="AC35" s="10">
@@ -4229,7 +5609,7 @@
         <v>23</v>
       </c>
       <c r="W36" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>529</v>
       </c>
       <c r="X36" s="11">
@@ -4237,7 +5617,7 @@
         <v>253</v>
       </c>
       <c r="Y36" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>47.826086956521742</v>
       </c>
       <c r="Z36" s="10">
@@ -4249,7 +5629,7 @@
         <v>52.173913043478258</v>
       </c>
       <c r="AB36" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>25392</v>
       </c>
       <c r="AC36" s="10">
@@ -4294,7 +5674,7 @@
         <v>24</v>
       </c>
       <c r="W37" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>576</v>
       </c>
       <c r="X37" s="11">
@@ -4302,7 +5682,7 @@
         <v>276</v>
       </c>
       <c r="Y37" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>47.916666666666664</v>
       </c>
       <c r="Z37" s="10">
@@ -4314,7 +5694,7 @@
         <v>52.083333333333336</v>
       </c>
       <c r="AB37" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>28800</v>
       </c>
       <c r="AC37" s="10">
@@ -4359,7 +5739,7 @@
         <v>25</v>
       </c>
       <c r="W38" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>625</v>
       </c>
       <c r="X38" s="11">
@@ -4367,7 +5747,7 @@
         <v>300</v>
       </c>
       <c r="Y38" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
       <c r="Z38" s="10">
@@ -4379,7 +5759,7 @@
         <v>52</v>
       </c>
       <c r="AB38" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>32500</v>
       </c>
       <c r="AC38" s="10">
@@ -4504,7 +5884,7 @@
         <v>50.000670690811539</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>828664558155000</v>
       </c>
       <c r="AC40" s="10">
@@ -4565,7 +5945,7 @@
         <v>50.01</v>
       </c>
       <c r="AB41" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>250050000000</v>
       </c>
       <c r="AC41" s="16">
@@ -4626,7 +6006,7 @@
         <v>50.05</v>
       </c>
       <c r="AB42" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>2002000000</v>
       </c>
       <c r="AC42" s="10">
@@ -5128,14 +6508,11 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B2:E6"/>
+    <mergeCell ref="O6:R10"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="O6:R10"/>
-    <mergeCell ref="B2:E6"/>
     <mergeCell ref="B25:E29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="AD33:AD42 AD15:AD31" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokenkino/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7938D3-9CC4-424F-A5BF-28DBE0E3CE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F27A410-1F97-0D4D-9E5C-3DAE11CB35D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="2" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
     <sheet name="Key Concepts" sheetId="3" r:id="rId2"/>
     <sheet name="LL" sheetId="5" r:id="rId3"/>
-    <sheet name="Test sheet 1" sheetId="4" r:id="rId4"/>
+    <sheet name="Components" sheetId="6" r:id="rId4"/>
+    <sheet name="Test sheet 1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="315">
   <si>
     <t>essere</t>
   </si>
@@ -219,9 +220,6 @@
   </si>
   <si>
     <t>Append dopo le parole principali, duplica record di cui è sinonimo + phase (-1 to 1 che rappresenta la somiglianza massima (1) o la negazione massima (-1))</t>
-  </si>
-  <si>
-    <t>Modeling</t>
   </si>
   <si>
     <t>word</t>
@@ -1077,6 +1075,142 @@
   </si>
   <si>
     <t>formOpinion</t>
+  </si>
+  <si>
+    <t>tagger</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>LLC</t>
+  </si>
+  <si>
+    <t>tokenKino components</t>
+  </si>
+  <si>
+    <t>python lib, http api</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tagger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: given a text, return tags from the sets: base words, names, geography, time, events, iptc categories</t>
+    </r>
+  </si>
+  <si>
+    <t>Logic Language Compiler:  givent a text, returns a LLC statement</t>
+  </si>
+  <si>
+    <t>people (db)</t>
+  </si>
+  <si>
+    <t>Modeling tokenKino knowledge base</t>
+  </si>
+  <si>
+    <t>facts (db)</t>
+  </si>
+  <si>
+    <t>theorems (db)</t>
+  </si>
+  <si>
+    <t>definitions (db)</t>
+  </si>
+  <si>
+    <t>Modeling tokenKino</t>
+  </si>
+  <si>
+    <t>opinions (db)</t>
+  </si>
+  <si>
+    <t>Fuzzy Operations</t>
+  </si>
+  <si>
+    <t>If true = 1, false = -1, agnostic = 0</t>
+  </si>
+  <si>
+    <t>&amp;&amp;</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>||</t>
+  </si>
+  <si>
+    <t>Table truths</t>
+  </si>
+  <si>
+    <t>NOT</t>
+  </si>
+  <si>
+    <t>v1,v2</t>
+  </si>
+  <si>
+    <t>v1 &amp;&amp; v2</t>
+  </si>
+  <si>
+    <t>XOR</t>
+  </si>
+  <si>
+    <t>BOOL</t>
+  </si>
+  <si>
+    <t>FUZZY (0,1)</t>
+  </si>
+  <si>
+    <t>v1*v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuzzy </t>
+  </si>
+  <si>
+    <t>1-v1</t>
+  </si>
+  <si>
+    <t>xor</t>
+  </si>
+  <si>
+    <t>max(min(v1, 1-v2), min(1-v1,v2))</t>
+  </si>
+  <si>
+    <t>xnor</t>
+  </si>
+  <si>
+    <t>1-max(min(v1, 1-v2), min(1-v1,v2))</t>
+  </si>
+  <si>
+    <t>imply</t>
+  </si>
+  <si>
+    <t>converse</t>
+  </si>
+  <si>
+    <t>v1&lt;=v2 ? 1 : v2</t>
+  </si>
+  <si>
+    <t>EQUALITY</t>
+  </si>
+  <si>
+    <t>FUZZY (-1,1)</t>
   </si>
 </sst>
 </file>
@@ -1396,7 +1530,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1502,35 +1636,8 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1538,19 +1645,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1565,27 +1660,24 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1596,8 +1688,57 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1939,7 +2080,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B2:N58"/>
+  <dimension ref="B2:N70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="20" customWidth="1"/>
@@ -1956,24 +2097,24 @@
   <sheetData>
     <row r="2" spans="2:12" ht="27" x14ac:dyDescent="0.2">
       <c r="C2" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I3" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="J3" s="22" t="s">
-        <v>143</v>
-      </c>
       <c r="K3" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.2">
@@ -1981,19 +2122,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
@@ -2001,19 +2142,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
@@ -2021,19 +2162,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="20" t="s">
         <v>153</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
@@ -2041,7 +2182,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
@@ -2049,7 +2190,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
@@ -2057,7 +2198,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
@@ -2065,7 +2206,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
@@ -2073,7 +2214,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
@@ -2081,7 +2222,7 @@
     </row>
     <row r="13" spans="2:12" ht="27" x14ac:dyDescent="0.2">
       <c r="C13" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>48</v>
@@ -2136,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>53</v>
@@ -2148,10 +2289,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H19" s="23"/>
     </row>
@@ -2160,10 +2301,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H20" s="23"/>
     </row>
@@ -2172,10 +2313,10 @@
         <v>8</v>
       </c>
       <c r="C21" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="20" t="s">
         <v>115</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>116</v>
       </c>
       <c r="H21" s="23"/>
     </row>
@@ -2184,10 +2325,10 @@
         <v>9</v>
       </c>
       <c r="C22" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="20" t="s">
         <v>117</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>118</v>
       </c>
       <c r="H22" s="23"/>
     </row>
@@ -2196,343 +2337,351 @@
         <v>10</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="27" x14ac:dyDescent="0.2">
       <c r="C25" s="21" t="s">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="19" x14ac:dyDescent="0.2">
       <c r="C26" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="27" t="s">
-        <v>81</v>
-      </c>
       <c r="I26" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N26" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I27" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="19" x14ac:dyDescent="0.2">
       <c r="C28" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B29" s="22"/>
+      <c r="C29" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="26" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="22">
-        <v>1</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>127</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="22">
-        <v>2</v>
-      </c>
+      <c r="B30" s="22"/>
       <c r="C30" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="E30" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B31" s="22"/>
+      <c r="C31" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="22">
-        <v>3</v>
-      </c>
-      <c r="C31" s="25" t="s">
+      <c r="D31" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>64</v>
-      </c>
       <c r="E31" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="19" x14ac:dyDescent="0.2">
       <c r="C33" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B34" s="22"/>
+      <c r="C34" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B35" s="22"/>
+      <c r="C35" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B36" s="22"/>
+      <c r="C36" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B37" s="22"/>
+      <c r="C37" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C39" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B34" s="22">
-        <v>1</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B35" s="22">
-        <v>2</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B36" s="22">
-        <v>3</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B37" s="22">
-        <v>4</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="19" x14ac:dyDescent="0.2">
-      <c r="C39" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>146</v>
-      </c>
       <c r="I39" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="J39" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="J39" s="20" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B40" s="22">
-        <v>1</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>127</v>
-      </c>
+      <c r="B40" s="22"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="22">
-        <v>2</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>134</v>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="22">
-        <v>3</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="33" t="s">
-        <v>138</v>
-      </c>
+      <c r="B42" s="22"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="22">
-        <v>4</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>152</v>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B44" s="22">
-        <v>5</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="26" t="s">
-        <v>150</v>
-      </c>
+      <c r="B44" s="22"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B45" s="22">
-        <v>6</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>151</v>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C47" s="22" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B48" s="22"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="22"/>
+      <c r="C49" s="22" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="22"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C51" s="22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="27" x14ac:dyDescent="0.2">
+      <c r="C53" s="21" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="C55" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C56" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C57" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C58" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C59" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C60" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C61" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C63" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C64" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C65" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C66" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C68" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D47" s="26" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="22">
-        <v>1</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E48" s="26" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B49" s="22">
-        <v>2</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="22">
-        <v>4</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C52" s="22" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C54" s="22" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C56" s="22" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C58" s="22" t="s">
-        <v>175</v>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C70" s="22" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2561,10 +2710,10 @@
   <sheetData>
     <row r="2" spans="2:13" ht="27" x14ac:dyDescent="0.2">
       <c r="C2" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
@@ -2572,68 +2721,68 @@
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C4" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I4" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="K4" s="37" t="s">
+      <c r="L4" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="M4" s="37" t="s">
         <v>188</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="C5" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G5" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="J5" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="J5" s="39" t="s">
+      <c r="K5" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>184</v>
-      </c>
       <c r="L5" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C6" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="22"/>
       <c r="F6" s="39"/>
@@ -2646,56 +2795,56 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E7" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F7" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G7" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>183</v>
-      </c>
       <c r="J7" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="2:13" ht="51" x14ac:dyDescent="0.2">
       <c r="F8" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H8" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="I8" s="39" t="s">
-        <v>211</v>
-      </c>
       <c r="J8" s="39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L8" s="39" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="34" x14ac:dyDescent="0.2">
       <c r="E9" s="22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F9" s="39" t="s">
         <v>8</v>
@@ -2704,10 +2853,10 @@
         <v>8</v>
       </c>
       <c r="H9" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="I9" s="39" t="s">
         <v>214</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>215</v>
       </c>
       <c r="J9" s="39" t="s">
         <v>8</v>
@@ -2716,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
@@ -2740,93 +2889,93 @@
     </row>
     <row r="12" spans="2:13" ht="19" x14ac:dyDescent="0.2">
       <c r="E12" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="34" x14ac:dyDescent="0.2">
       <c r="E13" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E14" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E15" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="3:10" ht="19" x14ac:dyDescent="0.2">
       <c r="E17" s="27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.2">
       <c r="E18" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H18" s="20" t="s">
         <v>217</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.2">
       <c r="E19" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.2">
       <c r="E20" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G20" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>268</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="23" spans="3:10" ht="19" x14ac:dyDescent="0.2">
@@ -2868,7 +3017,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0889CCB1-49C5-2548-AD66-B49F18C82431}">
-  <dimension ref="C2:U46"/>
+  <dimension ref="B2:U88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="14.5" customWidth="1"/>
@@ -2880,923 +3029,1957 @@
     <col min="22" max="22" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:18" ht="32" x14ac:dyDescent="0.4">
+    <row r="2" spans="3:21" ht="32" x14ac:dyDescent="0.4">
       <c r="C2" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="42"/>
+    </row>
+    <row r="4" spans="3:21" ht="27" x14ac:dyDescent="0.35">
+      <c r="C4" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="D2" s="42"/>
-    </row>
-    <row r="4" spans="3:18" ht="27" x14ac:dyDescent="0.35">
-      <c r="C4" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="69" t="s">
-        <v>224</v>
-      </c>
-      <c r="R4" s="69" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="R4" s="52" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="3:21" x14ac:dyDescent="0.2">
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C6" s="50" t="s">
+    <row r="6" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C6" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="U6"/>
+    </row>
+    <row r="7" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C7" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C7" s="46" t="s">
-        <v>240</v>
-      </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="48"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="57"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C8" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="F8" s="49" t="s">
+      <c r="U7"/>
+    </row>
+    <row r="8" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C8" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="I8" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L8" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="H8" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="J8" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="K8" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="L8" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="M8" s="49" t="s">
+      <c r="N8" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="O8" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="N8" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="O8" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="P8" s="49" t="s">
-        <v>189</v>
+      <c r="P8" s="43" t="s">
+        <v>188</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C9" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="D9" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="58" t="s">
-        <v>228</v>
-      </c>
-      <c r="K9" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="55" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" s="61"/>
-    </row>
-    <row r="10" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C10" s="70"/>
-      <c r="D10" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="67"/>
-      <c r="P10" s="67"/>
-      <c r="Q10" s="62" t="b">
+      <c r="U8"/>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C9" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="K9" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="68"/>
+      <c r="Q9" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="48"/>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C10" s="65"/>
+      <c r="D10" s="58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="49" t="b">
         <v>0</v>
       </c>
       <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C11" s="70"/>
-      <c r="D11" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="55" t="b">
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C11" s="65"/>
+      <c r="D11" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="68"/>
+      <c r="Q11" s="44" t="b">
         <v>1</v>
       </c>
       <c r="R11" s="5"/>
-    </row>
-    <row r="12" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C12" s="59"/>
-      <c r="D12" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="55" t="b">
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C12" s="66"/>
+      <c r="D12" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="44" t="b">
         <v>1</v>
       </c>
       <c r="R12" s="5"/>
-    </row>
-    <row r="13" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.2">
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
-    </row>
-    <row r="14" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C14" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="52"/>
+      <c r="U13"/>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C14" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="63"/>
       <c r="Q14" s="5"/>
-      <c r="R14" s="54" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C15" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="48"/>
+      <c r="R14" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="U14"/>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C15" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="57"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
-    </row>
-    <row r="16" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C16" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="F16" s="49" t="s">
+      <c r="U15"/>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C16" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="H16" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="G16" s="49" t="s">
+      <c r="I16" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="M16" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="H16" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="K16" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="L16" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="M16" s="49" t="s">
+      <c r="N16" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="O16" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="N16" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="O16" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="P16" s="49" t="s">
-        <v>189</v>
+      <c r="P16" s="43" t="s">
+        <v>188</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C17" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="D17" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="K17" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="55" t="b">
+      <c r="U16"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C17" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="D17" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="64" t="s">
+        <v>228</v>
+      </c>
+      <c r="K17" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="44" t="b">
         <v>1</v>
       </c>
       <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C18" s="70"/>
-      <c r="D18" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="55" t="b">
+      <c r="U17"/>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C18" s="65"/>
+      <c r="D18" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="44" t="b">
         <v>1</v>
       </c>
       <c r="R18" s="5"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C19" s="70"/>
-      <c r="D19" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="67"/>
-      <c r="Q19" s="62" t="b">
+      <c r="U18"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C19" s="65"/>
+      <c r="D19" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="49" t="b">
         <v>0</v>
       </c>
       <c r="R19" s="5"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C20" s="59"/>
-      <c r="D20" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="60" t="b">
+      <c r="U19"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C20" s="66"/>
+      <c r="D20" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="47" t="b">
         <v>1</v>
       </c>
       <c r="R20" s="5"/>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C22" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="52"/>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C22" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="63"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="54" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C23" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="48"/>
+      <c r="R22" s="45" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C23" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="55" t="s">
+        <v>243</v>
+      </c>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="57"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C24" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="F24" s="49" t="s">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C24" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="G24" s="49" t="s">
+      <c r="I24" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="K24" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L24" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="M24" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="H24" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="I24" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="J24" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="K24" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="L24" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="M24" s="49" t="s">
+      <c r="N24" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="O24" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="N24" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="O24" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="P24" s="49" t="s">
-        <v>189</v>
+      <c r="P24" s="43" t="s">
+        <v>188</v>
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C25" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="D25" s="50" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="71" t="s">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C25" s="64" t="s">
         <v>246</v>
       </c>
-      <c r="K25" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="55" t="b">
+      <c r="D25" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="67" t="s">
+        <v>245</v>
+      </c>
+      <c r="K25" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="68"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="68"/>
+      <c r="Q25" s="44" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="5"/>
     </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C26" s="70"/>
-      <c r="D26" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="67"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="62" t="b">
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C26" s="65"/>
+      <c r="D26" s="58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="49" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="5"/>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C27" s="70"/>
-      <c r="D27" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="63" t="b">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C27" s="65"/>
+      <c r="D27" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="69"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="50" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="5"/>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C28" s="59"/>
-      <c r="D28" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="60" t="b">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C28" s="66"/>
+      <c r="D28" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="68"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="47" t="b">
         <v>1</v>
       </c>
       <c r="R28" s="5"/>
     </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="R29" s="5"/>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C30" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="52"/>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C30" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="63"/>
       <c r="Q30" s="5"/>
-      <c r="R30" s="54" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C31" s="64" t="s">
+      <c r="R30" s="45" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C31" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="55" t="s">
         <v>250</v>
       </c>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="47"/>
-      <c r="P31" s="48"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="57"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
     </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C32" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="F32" s="49" t="s">
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="C32" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="I32" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="J32" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L32" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="M32" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="H32" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="I32" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="J32" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="K32" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="L32" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="M32" s="49" t="s">
+      <c r="N32" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="O32" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="N32" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="O32" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="P32" s="49" t="s">
-        <v>189</v>
+      <c r="P32" s="43" t="s">
+        <v>188</v>
       </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
     </row>
     <row r="33" spans="3:21" x14ac:dyDescent="0.2">
-      <c r="C33" s="55" t="s">
-        <v>249</v>
-      </c>
-      <c r="D33" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="55" t="s">
+      <c r="C33" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="K33" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="55" t="s">
+      <c r="D33" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="K33" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="L33" s="68"/>
+      <c r="M33" s="68"/>
+      <c r="N33" s="68"/>
+      <c r="O33" s="68"/>
+      <c r="P33" s="68"/>
+      <c r="Q33" s="44" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="3:21" ht="27" x14ac:dyDescent="0.35">
+      <c r="C35" s="51" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="35" spans="3:21" ht="27" x14ac:dyDescent="0.35">
-      <c r="C35" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="51"/>
     </row>
     <row r="36" spans="3:21" ht="27" x14ac:dyDescent="0.35">
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="F36" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="56"/>
-      <c r="O36" s="56"/>
-      <c r="P36" s="56"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="F36" s="73" t="s">
+        <v>266</v>
+      </c>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="73"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="73"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="73"/>
     </row>
     <row r="37" spans="3:21" x14ac:dyDescent="0.2">
-      <c r="C37" s="75" t="s">
-        <v>207</v>
+      <c r="C37" s="53" t="s">
+        <v>206</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F37" s="57">
-        <v>1</v>
-      </c>
-      <c r="H37" s="57">
+        <v>220</v>
+      </c>
+      <c r="F37" s="46">
+        <v>1</v>
+      </c>
+      <c r="H37" s="46">
         <v>2</v>
       </c>
-      <c r="K37" s="57">
+      <c r="K37" s="46">
         <v>3</v>
       </c>
-      <c r="Q37" s="57" t="s">
-        <v>255</v>
+      <c r="Q37" s="46" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D39" t="s">
+        <v>232</v>
+      </c>
+      <c r="F39" t="s">
         <v>233</v>
       </c>
-      <c r="F39" t="s">
-        <v>234</v>
-      </c>
       <c r="Q39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T39"/>
     </row>
     <row r="40" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D40" t="s">
+        <v>259</v>
+      </c>
+      <c r="F40" t="s">
         <v>260</v>
       </c>
-      <c r="F40" t="s">
-        <v>261</v>
-      </c>
       <c r="H40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T40"/>
       <c r="U40"/>
     </row>
     <row r="41" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D41" t="s">
+        <v>255</v>
+      </c>
+      <c r="F41" t="s">
+        <v>261</v>
+      </c>
+      <c r="H41" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q41" t="s">
         <v>256</v>
-      </c>
-      <c r="F41" t="s">
-        <v>262</v>
-      </c>
-      <c r="H41" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>257</v>
       </c>
       <c r="T41"/>
       <c r="U41"/>
     </row>
     <row r="42" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" t="s">
         <v>260</v>
       </c>
-      <c r="F42" t="s">
-        <v>261</v>
-      </c>
       <c r="H42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
+        <v>263</v>
+      </c>
+      <c r="D43" t="s">
+        <v>255</v>
+      </c>
+      <c r="F43" t="s">
+        <v>261</v>
+      </c>
+      <c r="H43" t="s">
         <v>264</v>
       </c>
-      <c r="D43" t="s">
-        <v>256</v>
-      </c>
-      <c r="F43" t="s">
-        <v>262</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="Q43" t="s">
         <v>265</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="44" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" t="s">
+        <v>259</v>
+      </c>
+      <c r="F44" t="s">
+        <v>260</v>
+      </c>
+      <c r="H44" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q44" t="s">
         <v>273</v>
-      </c>
-      <c r="D44" t="s">
-        <v>260</v>
-      </c>
-      <c r="F44" t="s">
-        <v>261</v>
-      </c>
-      <c r="H44" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="45" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D45" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" t="s">
         <v>260</v>
       </c>
-      <c r="F45" t="s">
-        <v>261</v>
-      </c>
       <c r="H45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1"/>
     </row>
+    <row r="48" spans="3:21" ht="27" x14ac:dyDescent="0.35">
+      <c r="C48" s="51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C52" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>298</v>
+      </c>
+      <c r="C53" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>298</v>
+      </c>
+      <c r="C54" t="s">
+        <v>295</v>
+      </c>
+      <c r="E54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
+        <v>152</v>
+      </c>
+      <c r="E55" s="77" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>298</v>
+      </c>
+      <c r="C56" t="s">
+        <v>306</v>
+      </c>
+      <c r="E56" s="77" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>298</v>
+      </c>
+      <c r="C57" t="s">
+        <v>308</v>
+      </c>
+      <c r="E57" s="77" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>298</v>
+      </c>
+      <c r="C58" t="s">
+        <v>310</v>
+      </c>
+      <c r="E58" s="77" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>298</v>
+      </c>
+      <c r="C59" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C61" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C63" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>293</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="G63" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="I63" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="J63" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="K63" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="L63" s="45" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C64" s="78" t="s">
+        <v>301</v>
+      </c>
+      <c r="D64" s="78"/>
+      <c r="E64" s="78"/>
+      <c r="F64" s="78"/>
+      <c r="G64" s="78"/>
+      <c r="H64" s="78"/>
+      <c r="I64" s="78"/>
+      <c r="J64" s="78"/>
+      <c r="K64" s="78"/>
+      <c r="L64" s="78"/>
+    </row>
+    <row r="65" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="b">
+        <f>AND(C65,D65)</f>
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="b">
+        <f>OR(C65,D65)</f>
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="b">
+        <f>NOT(C65)</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="5" t="b">
+        <f>_xlfn.XOR(C65,D65)</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="5" t="b">
+        <f>NOT(_xlfn.XOR(C65,D65))</f>
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="b">
+        <f t="shared" ref="E66:E68" si="0">AND(C66,D66)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="b">
+        <f>OR(C66,D66)</f>
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="b">
+        <f t="shared" ref="G66:G68" si="1">NOT(C66)</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="5" t="b">
+        <f>_xlfn.XOR(C66,D66)</f>
+        <v>1</v>
+      </c>
+      <c r="I66" s="5" t="b">
+        <f>NOT(_xlfn.XOR(C66,D66))</f>
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C67" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="b">
+        <f>OR(C67,D67)</f>
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H67" s="5" t="b">
+        <f>_xlfn.XOR(C67,D67)</f>
+        <v>1</v>
+      </c>
+      <c r="I67" s="5" t="b">
+        <f>NOT(_xlfn.XOR(C67,D67))</f>
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C68" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="b">
+        <f>OR(C68,D68)</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H68" s="5" t="b">
+        <f>_xlfn.XOR(C68,D68)</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="5" t="b">
+        <f>NOT(_xlfn.XOR(C68,D68))</f>
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+    </row>
+    <row r="70" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C70" s="78" t="s">
+        <v>302</v>
+      </c>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="78"/>
+      <c r="H70" s="78"/>
+      <c r="I70" s="78"/>
+      <c r="J70" s="78"/>
+      <c r="K70" s="78"/>
+      <c r="L70" s="78"/>
+    </row>
+    <row r="71" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C71" s="5">
+        <v>1</v>
+      </c>
+      <c r="D71" s="5">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5">
+        <f>MIN(C71,D71)</f>
+        <v>1</v>
+      </c>
+      <c r="F71" s="5">
+        <f>MAX(C71,D71)</f>
+        <v>1</v>
+      </c>
+      <c r="G71" s="5">
+        <f>1-C71</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="5">
+        <f>MAX(MIN(C71, 1-D71), MIN(1-C71,D71))</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="5">
+        <f>1-MAX(MIN(C71,1-D71),MIN(1-C71,D71))</f>
+        <v>1</v>
+      </c>
+      <c r="J71" s="5">
+        <f>IF(C71&lt;=D71,1,D71)</f>
+        <v>1</v>
+      </c>
+      <c r="K71" s="5">
+        <f>IF(D71&lt;=C71,1,C71)</f>
+        <v>1</v>
+      </c>
+      <c r="L71" s="5">
+        <f>MIN(IF(C71&lt;=D71,1,D71),IF(D71&lt;=C71,1,C71))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C72" s="5">
+        <v>1</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0</v>
+      </c>
+      <c r="E72" s="5">
+        <f>MIN(C72,D72)</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="5">
+        <f>MAX(C72,D72)</f>
+        <v>1</v>
+      </c>
+      <c r="G72" s="5">
+        <f>1-C72</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="5">
+        <f>MAX(MIN(C72, 1-D72), MIN(1-C72,D72))</f>
+        <v>1</v>
+      </c>
+      <c r="I72" s="5">
+        <f>1-MAX(MIN(C72,1-D72),MIN(1-C72,D72))</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="5">
+        <f>IF(C72&lt;=D72,1,D72)</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="5">
+        <f>IF(D72&lt;=C72,1,C72)</f>
+        <v>1</v>
+      </c>
+      <c r="L72" s="5">
+        <f>MIN(IF(C72&lt;=D72,1,D72),IF(D72&lt;=C72,1,C72))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C73" s="5">
+        <v>0</v>
+      </c>
+      <c r="D73" s="5">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5">
+        <f>MIN(C73,D73)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="5">
+        <f>MAX(C73,D73)</f>
+        <v>1</v>
+      </c>
+      <c r="G73" s="5">
+        <f>1-C73</f>
+        <v>1</v>
+      </c>
+      <c r="H73" s="5">
+        <f>MAX(MIN(C73, 1-D73), MIN(1-C73,D73))</f>
+        <v>1</v>
+      </c>
+      <c r="I73" s="5">
+        <f>1-MAX(MIN(C73,1-D73),MIN(1-C73,D73))</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="5">
+        <f>IF(C73&lt;=D73,1,D73)</f>
+        <v>1</v>
+      </c>
+      <c r="K73" s="5">
+        <f>IF(D73&lt;=C73,1,C73)</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="5">
+        <f>MIN(IF(C73&lt;=D73,1,D73),IF(D73&lt;=C73,1,C73))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C74" s="5">
+        <v>0</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0</v>
+      </c>
+      <c r="E74" s="5">
+        <f>MIN(C74,D74)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="5">
+        <f>MAX(C74,D74)</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="5">
+        <f>1-C74</f>
+        <v>1</v>
+      </c>
+      <c r="H74" s="5">
+        <f>MAX(MIN(C74, 1-D74), MIN(1-C74,D74))</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="5">
+        <f>1-MAX(MIN(C74,1-D74),MIN(1-C74,D74))</f>
+        <v>1</v>
+      </c>
+      <c r="J74" s="5">
+        <f>IF(C74&lt;=D74,1,D74)</f>
+        <v>1</v>
+      </c>
+      <c r="K74" s="5">
+        <f>IF(D74&lt;=C74,1,C74)</f>
+        <v>1</v>
+      </c>
+      <c r="L74" s="5">
+        <f>MIN(IF(C74&lt;=D74,1,D74),IF(D74&lt;=C74,1,C74))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C75" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E75" s="5">
+        <f>MIN(C75,D75)</f>
+        <v>0.8</v>
+      </c>
+      <c r="F75" s="5">
+        <f>MAX(C75,D75)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G75" s="5">
+        <f>1-C75</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H75" s="5">
+        <f>MAX(MIN(C75, 1-D75), MIN(1-C75,D75))</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="I75" s="5">
+        <f>1-MAX(MIN(C75,1-D75),MIN(1-C75,D75))</f>
+        <v>0.8</v>
+      </c>
+      <c r="J75" s="5">
+        <f>IF(C75&lt;=D75,1,D75)</f>
+        <v>1</v>
+      </c>
+      <c r="K75" s="5">
+        <f>IF(D75&lt;=C75,1,C75)</f>
+        <v>1</v>
+      </c>
+      <c r="L75" s="5">
+        <f>MIN(IF(C75&lt;=D75,1,D75),IF(D75&lt;=C75,1,C75))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C76" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E76" s="5">
+        <f>MIN(C76,D76)</f>
+        <v>0.1</v>
+      </c>
+      <c r="F76" s="5">
+        <f>MAX(C76,D76)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G76" s="5">
+        <f>1-C76</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="H76" s="5">
+        <f>MAX(MIN(C76, 1-D76), MIN(1-C76,D76))</f>
+        <v>0.9</v>
+      </c>
+      <c r="I76" s="5">
+        <f>1-MAX(MIN(C76,1-D76),MIN(1-C76,D76))</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="J76" s="5">
+        <f>IF(C76&lt;=D76,1,D76)</f>
+        <v>0.1</v>
+      </c>
+      <c r="K76" s="5">
+        <f>IF(D76&lt;=C76,1,C76)</f>
+        <v>1</v>
+      </c>
+      <c r="L76" s="5">
+        <f>MIN(IF(C76&lt;=D76,1,D76),IF(D76&lt;=C76,1,C76))</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="77" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C77" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D77" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E77" s="5">
+        <f>MIN(C77,D77)</f>
+        <v>0.1</v>
+      </c>
+      <c r="F77" s="5">
+        <f>MAX(C77,D77)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G77" s="5">
+        <f>1-C77</f>
+        <v>0.9</v>
+      </c>
+      <c r="H77" s="5">
+        <f>MAX(MIN(C77, 1-D77), MIN(1-C77,D77))</f>
+        <v>0.9</v>
+      </c>
+      <c r="I77" s="5">
+        <f>1-MAX(MIN(C77,1-D77),MIN(1-C77,D77))</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="J77" s="5">
+        <f>IF(C77&lt;=D77,1,D77)</f>
+        <v>1</v>
+      </c>
+      <c r="K77" s="5">
+        <f>IF(D77&lt;=C77,1,C77)</f>
+        <v>0.1</v>
+      </c>
+      <c r="L77" s="5">
+        <f>MIN(IF(C77&lt;=D77,1,D77),IF(D77&lt;=C77,1,C77))</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="78" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C78" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E78" s="5">
+        <f>MIN(C78,D78)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F78" s="5">
+        <f>MAX(C78,D78)</f>
+        <v>0.2</v>
+      </c>
+      <c r="G78" s="5">
+        <f>1-C78</f>
+        <v>0.8</v>
+      </c>
+      <c r="H78" s="5">
+        <f>MAX(MIN(C78, 1-D78), MIN(1-C78,D78))</f>
+        <v>0.2</v>
+      </c>
+      <c r="I78" s="5">
+        <f>1-MAX(MIN(C78,1-D78),MIN(1-C78,D78))</f>
+        <v>0.8</v>
+      </c>
+      <c r="J78" s="5">
+        <f>IF(C78&lt;=D78,1,D78)</f>
+        <v>1</v>
+      </c>
+      <c r="K78" s="5">
+        <f>IF(D78&lt;=C78,1,C78)</f>
+        <v>1</v>
+      </c>
+      <c r="L78" s="5">
+        <f>MIN(IF(C78&lt;=D78,1,D78),IF(D78&lt;=C78,1,C78))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C80" s="78" t="s">
+        <v>314</v>
+      </c>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="78"/>
+      <c r="I80" s="78"/>
+      <c r="J80" s="78"/>
+      <c r="K80" s="78"/>
+      <c r="L80" s="78"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C81" s="5">
+        <f>C71 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="D81" s="5">
+        <f t="shared" ref="D81:L81" si="2">D71 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="E81" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F81" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G81" s="5">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="H81" s="5">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="I81" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J81" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K81" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L81" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C82" s="5">
+        <f>C72 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="D82" s="5">
+        <f t="shared" ref="D82:L82" si="3">D72 * 2 -1</f>
+        <v>-1</v>
+      </c>
+      <c r="E82" s="5">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="F82" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G82" s="5">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="H82" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="I82" s="5">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="J82" s="5">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="K82" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L82" s="5">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C83" s="5">
+        <f>C73 * 2 -1</f>
+        <v>-1</v>
+      </c>
+      <c r="D83" s="5">
+        <f t="shared" ref="D83:L83" si="4">D73 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="E83" s="5">
+        <f t="shared" si="4"/>
+        <v>-1</v>
+      </c>
+      <c r="F83" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G83" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H83" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I83" s="5">
+        <f t="shared" si="4"/>
+        <v>-1</v>
+      </c>
+      <c r="J83" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K83" s="5">
+        <f t="shared" si="4"/>
+        <v>-1</v>
+      </c>
+      <c r="L83" s="5">
+        <f t="shared" si="4"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C84" s="5">
+        <f>C74 * 2 -1</f>
+        <v>-1</v>
+      </c>
+      <c r="D84" s="5">
+        <f t="shared" ref="D84:L84" si="5">D74 * 2 -1</f>
+        <v>-1</v>
+      </c>
+      <c r="E84" s="5">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="F84" s="5">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="G84" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H84" s="5">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="I84" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="J84" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K84" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="L84" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C85" s="5">
+        <f>C75 * 2 -1</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="D85" s="5">
+        <f t="shared" ref="D85:L85" si="6">D75 * 2 -1</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="E85" s="5">
+        <f t="shared" si="6"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="F85" s="5">
+        <f t="shared" si="6"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G85" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="H85" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="I85" s="5">
+        <f t="shared" si="6"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="J85" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K85" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="L85" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C86" s="5">
+        <f>C76 * 2 -1</f>
+        <v>0.8</v>
+      </c>
+      <c r="D86" s="5">
+        <f t="shared" ref="D86:L86" si="7">D76 * 2 -1</f>
+        <v>-0.8</v>
+      </c>
+      <c r="E86" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.8</v>
+      </c>
+      <c r="F86" s="5">
+        <f t="shared" si="7"/>
+        <v>0.8</v>
+      </c>
+      <c r="G86" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.8</v>
+      </c>
+      <c r="H86" s="5">
+        <f t="shared" si="7"/>
+        <v>0.8</v>
+      </c>
+      <c r="I86" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J86" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.8</v>
+      </c>
+      <c r="K86" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="L86" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C87" s="5">
+        <f>C77 * 2 -1</f>
+        <v>-0.8</v>
+      </c>
+      <c r="D87" s="5">
+        <f t="shared" ref="D87:L87" si="8">D77 * 2 -1</f>
+        <v>0.8</v>
+      </c>
+      <c r="E87" s="5">
+        <f t="shared" si="8"/>
+        <v>-0.8</v>
+      </c>
+      <c r="F87" s="5">
+        <f t="shared" si="8"/>
+        <v>0.8</v>
+      </c>
+      <c r="G87" s="5">
+        <f t="shared" si="8"/>
+        <v>0.8</v>
+      </c>
+      <c r="H87" s="5">
+        <f t="shared" si="8"/>
+        <v>0.8</v>
+      </c>
+      <c r="I87" s="5">
+        <f t="shared" si="8"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J87" s="5">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K87" s="5">
+        <f t="shared" si="8"/>
+        <v>-0.8</v>
+      </c>
+      <c r="L87" s="5">
+        <f t="shared" si="8"/>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C88" s="5">
+        <f>C78 * 2 -1</f>
+        <v>-0.6</v>
+      </c>
+      <c r="D88" s="5">
+        <f t="shared" ref="D88:L88" si="9">D78 * 2 -1</f>
+        <v>-0.6</v>
+      </c>
+      <c r="E88" s="5">
+        <f t="shared" si="9"/>
+        <v>-0.6</v>
+      </c>
+      <c r="F88" s="5">
+        <f t="shared" si="9"/>
+        <v>-0.6</v>
+      </c>
+      <c r="G88" s="5">
+        <f t="shared" si="9"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="H88" s="5">
+        <f t="shared" si="9"/>
+        <v>-0.6</v>
+      </c>
+      <c r="I88" s="5">
+        <f t="shared" si="9"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="J88" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K88" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="L88" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
+  <mergeCells count="48">
+    <mergeCell ref="C80:L80"/>
+    <mergeCell ref="C64:L64"/>
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
     <mergeCell ref="C6:P6"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="J25:J28"/>
@@ -3813,31 +4996,84 @@
     <mergeCell ref="K17:P17"/>
     <mergeCell ref="K18:P18"/>
     <mergeCell ref="K19:P19"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
     <mergeCell ref="K20:P20"/>
     <mergeCell ref="D17:I17"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4F5D0B4-B679-5D48-82AD-BDDDF440A9F2}">
+  <dimension ref="B2:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="20"/>
+    <col min="3" max="3" width="53.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" style="20" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="27" x14ac:dyDescent="0.2">
+      <c r="B2" s="21" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B5" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBDF187D-47D8-524F-BF49-BA78AE579A0A}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -3857,62 +5093,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B2" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
+      <c r="B2" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="O6" s="44" t="s">
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="O6" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="74"/>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
+      <c r="Q8" s="74"/>
+      <c r="R8" s="74"/>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
@@ -3943,10 +5179,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="74"/>
+      <c r="Q9" s="74"/>
+      <c r="R9" s="74"/>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
@@ -3976,10 +5212,10 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="74"/>
+      <c r="Q10" s="74"/>
+      <c r="R10" s="74"/>
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
@@ -4848,12 +6084,12 @@
       </c>
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B25" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
+      <c r="B25" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
       <c r="O25" t="s">
         <v>23</v>
       </c>
@@ -4922,10 +6158,10 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
       <c r="N26" s="6" t="s">
         <v>23</v>
       </c>
@@ -4996,10 +6232,10 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
       <c r="N27" s="6" t="s">
         <v>24</v>
       </c>
@@ -5070,10 +6306,10 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
       <c r="N28" s="6" t="s">
         <v>25</v>
       </c>
@@ -5144,10 +6380,10 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
       <c r="N29" s="6" t="s">
         <v>27</v>
       </c>
@@ -6043,7 +7279,7 @@
     </row>
     <row r="44" spans="2:33" ht="27" x14ac:dyDescent="0.2">
       <c r="B44" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
@@ -6083,17 +7319,17 @@
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B46" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
       <c r="E46" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F46" s="22"/>
       <c r="G46" s="22"/>
       <c r="H46" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I46" s="20"/>
       <c r="O46" s="5" t="s">
@@ -6108,24 +7344,24 @@
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B47" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D47" s="20"/>
       <c r="E47" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I47" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O47" s="5" t="s">
         <v>29</v>
@@ -6139,24 +7375,24 @@
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B48" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" s="20"/>
       <c r="E48" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F48" s="28" t="s">
         <v>4</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I48" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O48" s="5" t="s">
         <v>29</v>
@@ -6170,21 +7406,21 @@
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B49" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="28" t="s">
         <v>23</v>
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F49" s="28" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="20"/>
       <c r="H49" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I49" s="28" t="s">
         <v>25</v>
@@ -6220,13 +7456,13 @@
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B51" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
       <c r="F51" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
@@ -6243,10 +7479,10 @@
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B52" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
@@ -6266,10 +7502,10 @@
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B53" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
@@ -6289,15 +7525,15 @@
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B54" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
       <c r="F54" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
@@ -6314,7 +7550,7 @@
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B55" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55" s="20">
         <v>-1</v>
@@ -6357,7 +7593,7 @@
     <row r="57" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B57" s="20"/>
       <c r="C57" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
@@ -6377,7 +7613,7 @@
     </row>
     <row r="58" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B58" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
@@ -6389,11 +7625,11 @@
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B59" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" s="20"/>
       <c r="D59" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
@@ -6403,11 +7639,11 @@
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B60" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
@@ -6420,11 +7656,11 @@
     </row>
     <row r="61" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B61" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" s="20"/>
       <c r="D61" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E61" s="29"/>
       <c r="F61" s="20" t="s">
@@ -6442,11 +7678,11 @@
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B62" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62" s="20"/>
       <c r="D62" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62" s="20"/>
       <c r="F62" s="31">
@@ -6475,7 +7711,7 @@
     <row r="64" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B64" s="20"/>
       <c r="C64" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D64" s="28"/>
       <c r="E64" s="29"/>
@@ -6496,13 +7732,13 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G66" s="20"/>
     </row>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokenkino/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE31AB3B-E34E-AD4A-B7AE-61821657FD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A10C785-153C-4E4A-B8FF-BAB3E27E9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="5" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Components" sheetId="6" r:id="rId4"/>
     <sheet name="Test sheet Similarity" sheetId="4" r:id="rId5"/>
     <sheet name="Test sheet LL" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="461">
   <si>
     <t>essere</t>
   </si>
@@ -1560,6 +1561,69 @@
   </si>
   <si>
     <t>([e1,v_essere,null,(v_bianco &amp;&amp; v_nero),null,null] &amp;&amp; [e1, v_essere,null,v_simpatico &amp;&amp; v_intelligente,null,t1] &amp;&amp;  [e3, v_prendere,e1,null,null,t1]  &amp;&amp; [e2, v_amare, e1,null,null,t1+0.1]) -&gt; [e3 &amp;&amp; e2, v_pensare, [e3 &amp;&amp; e2, v_adottare, e1, null, null, &gt; t1 + 0.2], null, null, t1 + 0.2]</t>
+  </si>
+  <si>
+    <t>I nsubj lift VERB [and, Mari]</t>
+  </si>
+  <si>
+    <t>and cc I PRON []</t>
+  </si>
+  <si>
+    <t>Mari conj I PRON []</t>
+  </si>
+  <si>
+    <t>lift ROOT lift VERB [I, couch, ,, are]</t>
+  </si>
+  <si>
+    <t>the det couch NOUN []</t>
+  </si>
+  <si>
+    <t>couch dobj lift VERB [the, in]</t>
+  </si>
+  <si>
+    <t>in prep couch NOUN [room]</t>
+  </si>
+  <si>
+    <t>the det room NOUN []</t>
+  </si>
+  <si>
+    <t>living compound room NOUN []</t>
+  </si>
+  <si>
+    <t>room pobj in ADP [the, living]</t>
+  </si>
+  <si>
+    <t>, punct lift VERB []</t>
+  </si>
+  <si>
+    <t>because mark are AUX []</t>
+  </si>
+  <si>
+    <t>we nsubj are AUX []</t>
+  </si>
+  <si>
+    <t>are advcl lift VERB [because, we, team, and, help]</t>
+  </si>
+  <si>
+    <t>a det team NOUN []</t>
+  </si>
+  <si>
+    <t>team attr are AUX [a]</t>
+  </si>
+  <si>
+    <t>and cc are AUX []</t>
+  </si>
+  <si>
+    <t>we nsubj help VERB []</t>
+  </si>
+  <si>
+    <t>help conj are AUX [we, other]</t>
+  </si>
+  <si>
+    <t>each det other ADJ []</t>
+  </si>
+  <si>
+    <t>other dobj help VERB [each]</t>
   </si>
 </sst>
 </file>
@@ -2060,24 +2124,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2096,7 +2142,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2109,6 +2164,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3538,22 +3602,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="70"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="74"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3561,24 +3625,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="72" t="s">
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="74"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="67"/>
+      <c r="P7" s="68"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3631,28 +3695,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="79" t="s">
+      <c r="D9" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="76" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="67"/>
-      <c r="P9" s="67"/>
+      <c r="K9" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3668,24 +3732,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="80"/>
-      <c r="D10" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="80"/>
+      <c r="M10" s="80"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -3701,24 +3765,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="80"/>
-      <c r="D11" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -3734,24 +3798,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="81"/>
-      <c r="D12" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="75"/>
+      <c r="O12" s="75"/>
+      <c r="P12" s="75"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -3772,22 +3836,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="70"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="74"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -3795,24 +3859,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="66" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="72" t="s">
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="73"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="74"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="68"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -3865,28 +3929,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="79" t="s">
+      <c r="D17" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="76" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="67"/>
+      <c r="K17" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="75"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="75"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -3894,24 +3958,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="80"/>
-      <c r="D18" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -3919,24 +3983,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="80"/>
-      <c r="D19" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="80"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -3944,24 +4008,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="81"/>
-      <c r="D20" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="67"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="75"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="75"/>
+      <c r="P20" s="75"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -3972,46 +4036,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="70"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="74"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="66" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="72" t="s">
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="66" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="73"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="73"/>
-      <c r="P23" s="74"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="68"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4062,100 +4126,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="82" t="s">
+      <c r="D25" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="79" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="67"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="67"/>
+      <c r="K25" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="80"/>
-      <c r="D26" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="78"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="80"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="80"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="80"/>
-      <c r="D27" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="80"/>
-      <c r="K27" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="80"/>
+      <c r="M27" s="80"/>
+      <c r="N27" s="80"/>
+      <c r="O27" s="80"/>
+      <c r="P27" s="80"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="81"/>
-      <c r="D28" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="67"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="78"/>
+      <c r="K28" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="75"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4165,46 +4229,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="72" t="s">
         <v>347</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="70"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="74"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="72" t="s">
+      <c r="C31" s="66" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="72" t="s">
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="73"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="74"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="68"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4258,25 +4322,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D33" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="70"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="74"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="67" t="s">
+      <c r="K33" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="67"/>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="67"/>
+      <c r="L33" s="75"/>
+      <c r="M33" s="75"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="75"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4290,19 +4354,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="71" t="s">
+      <c r="F36" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="71"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4584,18 +4648,18 @@
       </c>
     </row>
     <row r="64" spans="2:12">
-      <c r="C64" s="66" t="s">
+      <c r="C64" s="81" t="s">
         <v>286</v>
       </c>
-      <c r="D64" s="66"/>
-      <c r="E64" s="66"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="66"/>
-      <c r="I64" s="66"/>
-      <c r="J64" s="66"/>
-      <c r="K64" s="66"/>
-      <c r="L64" s="66"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
+      <c r="H64" s="81"/>
+      <c r="I64" s="81"/>
+      <c r="J64" s="81"/>
+      <c r="K64" s="81"/>
+      <c r="L64" s="81"/>
     </row>
     <row r="65" spans="3:12">
       <c r="C65" s="19" t="b">
@@ -4753,18 +4817,18 @@
       <c r="G69" s="19"/>
     </row>
     <row r="70" spans="3:12">
-      <c r="C70" s="66" t="s">
+      <c r="C70" s="81" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="66"/>
-      <c r="E70" s="66"/>
-      <c r="F70" s="66"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="66"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="66"/>
-      <c r="K70" s="66"/>
-      <c r="L70" s="66"/>
+      <c r="D70" s="81"/>
+      <c r="E70" s="81"/>
+      <c r="F70" s="81"/>
+      <c r="G70" s="81"/>
+      <c r="H70" s="81"/>
+      <c r="I70" s="81"/>
+      <c r="J70" s="81"/>
+      <c r="K70" s="81"/>
+      <c r="L70" s="81"/>
     </row>
     <row r="71" spans="3:12">
       <c r="C71" s="19">
@@ -5087,18 +5151,18 @@
       </c>
     </row>
     <row r="80" spans="3:12">
-      <c r="C80" s="66" t="s">
+      <c r="C80" s="81" t="s">
         <v>299</v>
       </c>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
-      <c r="J80" s="66"/>
-      <c r="K80" s="66"/>
-      <c r="L80" s="66"/>
+      <c r="D80" s="81"/>
+      <c r="E80" s="81"/>
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="81"/>
+      <c r="I80" s="81"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="81"/>
+      <c r="L80" s="81"/>
     </row>
     <row r="81" spans="3:14">
       <c r="C81" s="19">
@@ -5612,6 +5676,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="C80:L80"/>
+    <mergeCell ref="C64:L64"/>
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="K19:P19"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="J7:P7"/>
@@ -5628,38 +5724,6 @@
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C80:L80"/>
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9438,4 +9502,119 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF83A4B8-03E1-8F47-A654-49287922FEC9}">
+  <dimension ref="C4:C24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>460</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokenkino/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A10C785-153C-4E4A-B8FF-BAB3E27E9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED19C436-4FC2-C549-9BC6-084192C8C6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="5" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="6" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Components" sheetId="6" r:id="rId4"/>
     <sheet name="Test sheet Similarity" sheetId="4" r:id="rId5"/>
     <sheet name="Test sheet LL" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
+    <sheet name="Compiler" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="458">
   <si>
     <t>essere</t>
   </si>
@@ -1563,74 +1563,65 @@
     <t>([e1,v_essere,null,(v_bianco &amp;&amp; v_nero),null,null] &amp;&amp; [e1, v_essere,null,v_simpatico &amp;&amp; v_intelligente,null,t1] &amp;&amp;  [e3, v_prendere,e1,null,null,t1]  &amp;&amp; [e2, v_amare, e1,null,null,t1+0.1]) -&gt; [e3 &amp;&amp; e2, v_pensare, [e3 &amp;&amp; e2, v_adottare, e1, null, null, &gt; t1 + 0.2], null, null, t1 + 0.2]</t>
   </si>
   <si>
-    <t>I nsubj lift VERB [and, Mari]</t>
-  </si>
-  <si>
-    <t>and cc I PRON []</t>
-  </si>
-  <si>
-    <t>Mari conj I PRON []</t>
-  </si>
-  <si>
-    <t>lift ROOT lift VERB [I, couch, ,, are]</t>
-  </si>
-  <si>
-    <t>the det couch NOUN []</t>
-  </si>
-  <si>
-    <t>couch dobj lift VERB [the, in]</t>
-  </si>
-  <si>
-    <t>in prep couch NOUN [room]</t>
-  </si>
-  <si>
-    <t>the det room NOUN []</t>
-  </si>
-  <si>
-    <t>living compound room NOUN []</t>
-  </si>
-  <si>
-    <t>room pobj in ADP [the, living]</t>
-  </si>
-  <si>
-    <t>, punct lift VERB []</t>
-  </si>
-  <si>
-    <t>because mark are AUX []</t>
-  </si>
-  <si>
-    <t>we nsubj are AUX []</t>
-  </si>
-  <si>
-    <t>are advcl lift VERB [because, we, team, and, help]</t>
-  </si>
-  <si>
-    <t>a det team NOUN []</t>
-  </si>
-  <si>
-    <t>team attr are AUX [a]</t>
-  </si>
-  <si>
-    <t>and cc are AUX []</t>
-  </si>
-  <si>
-    <t>we nsubj help VERB []</t>
-  </si>
-  <si>
-    <t>help conj are AUX [we, other]</t>
-  </si>
-  <si>
-    <t>each det other ADJ []</t>
-  </si>
-  <si>
-    <t>other dobj help VERB [each]</t>
+    <t>tokenKino flat compiler</t>
+  </si>
+  <si>
+    <t>examples</t>
+  </si>
+  <si>
+    <t>I think you are not paying attention to what I have to say</t>
+  </si>
+  <si>
+    <t>cat be feline mammal</t>
+  </si>
+  <si>
+    <t>the cat is a feline mammal having thick soft fur and no ability to roar</t>
+  </si>
+  <si>
+    <t>roar</t>
+  </si>
+  <si>
+    <t>I have to say</t>
+  </si>
+  <si>
+    <t>you not pay attention to 3</t>
+  </si>
+  <si>
+    <t>I think 2</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>you or me can prepare the meal</t>
+  </si>
+  <si>
+    <t>you can prepare the meal</t>
+  </si>
+  <si>
+    <t>OR I can prepare the meal</t>
+  </si>
+  <si>
+    <t>cat can have fur thick soft</t>
+  </si>
+  <si>
+    <t>cat can have no ability to 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isolate all entities (across the nested structure) </t>
+  </si>
+  <si>
+    <t>merge entities and rebuild statements with the correct reference</t>
+  </si>
+  <si>
+    <t>isolate all the statements (across the nested structure) with duplication for conjuncts and subordinates, matching all entities</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1754,6 +1745,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Menlo Regular"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1957,7 +1955,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2124,6 +2122,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2142,16 +2158,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2166,20 +2173,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3602,22 +3618,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="68" t="s">
         <v>344</v>
       </c>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="74"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="70"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3625,24 +3641,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="72" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="66" t="s">
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="72" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="68"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="74"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3695,28 +3711,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="76" t="s">
+      <c r="C9" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="76" t="s">
+      <c r="D9" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="79" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="75"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="75"/>
+      <c r="K9" s="67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="67"/>
+      <c r="P9" s="67"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3732,24 +3748,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="77"/>
-      <c r="D10" s="69" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="80" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="80"/>
-      <c r="M10" s="80"/>
-      <c r="N10" s="80"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="78"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -3765,24 +3781,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="77"/>
-      <c r="D11" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="75"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -3798,24 +3814,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="78"/>
-      <c r="D12" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="75"/>
-      <c r="M12" s="75"/>
-      <c r="N12" s="75"/>
-      <c r="O12" s="75"/>
-      <c r="P12" s="75"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -3836,22 +3852,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="68" t="s">
         <v>345</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="74"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="70"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -3859,24 +3875,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="66" t="s">
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="72" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="67"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="68"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="74"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -3929,28 +3945,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="76" t="s">
+      <c r="C17" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="76" t="s">
+      <c r="D17" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="79" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="75"/>
-      <c r="M17" s="75"/>
-      <c r="N17" s="75"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75"/>
+      <c r="K17" s="67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -3958,24 +3974,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="77"/>
-      <c r="D18" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="75"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="75"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -3983,24 +3999,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="77"/>
-      <c r="D19" s="69" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -4008,24 +4024,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="78"/>
-      <c r="D20" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="75"/>
-      <c r="M20" s="75"/>
-      <c r="N20" s="75"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="75"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="67"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4036,46 +4052,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="68" t="s">
         <v>346</v>
       </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="73"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="74"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="70"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="66" t="s">
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="72" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="73"/>
+      <c r="P23" s="74"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4126,100 +4142,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="79" t="s">
+      <c r="D25" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
+      <c r="K25" s="67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="77"/>
-      <c r="D26" s="69" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="80" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="78"/>
+      <c r="M26" s="78"/>
+      <c r="N26" s="78"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="78"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="77"/>
-      <c r="D27" s="69" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="80"/>
-      <c r="M27" s="80"/>
-      <c r="N27" s="80"/>
-      <c r="O27" s="80"/>
-      <c r="P27" s="80"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="78"/>
+      <c r="M27" s="78"/>
+      <c r="N27" s="78"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="78"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="78"/>
-      <c r="D28" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="75"/>
-      <c r="M28" s="75"/>
-      <c r="N28" s="75"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="75"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4229,46 +4245,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="72" t="s">
+      <c r="C30" s="68" t="s">
         <v>347</v>
       </c>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="74"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="69"/>
+      <c r="O30" s="69"/>
+      <c r="P30" s="70"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="72" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="66" t="s">
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="72" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="68"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="74"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4322,25 +4338,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="72" t="s">
+      <c r="D33" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="74"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="70"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="75" t="s">
+      <c r="K33" s="67" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="75"/>
-      <c r="M33" s="75"/>
-      <c r="N33" s="75"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="75"/>
+      <c r="L33" s="67"/>
+      <c r="M33" s="67"/>
+      <c r="N33" s="67"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="67"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4354,19 +4370,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="82" t="s">
+      <c r="F36" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="82"/>
-      <c r="K36" s="82"/>
-      <c r="L36" s="82"/>
-      <c r="M36" s="82"/>
-      <c r="N36" s="82"/>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="71"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="71"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4648,18 +4664,18 @@
       </c>
     </row>
     <row r="64" spans="2:12">
-      <c r="C64" s="81" t="s">
+      <c r="C64" s="66" t="s">
         <v>286</v>
       </c>
-      <c r="D64" s="81"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
-      <c r="H64" s="81"/>
-      <c r="I64" s="81"/>
-      <c r="J64" s="81"/>
-      <c r="K64" s="81"/>
-      <c r="L64" s="81"/>
+      <c r="D64" s="66"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="66"/>
+      <c r="H64" s="66"/>
+      <c r="I64" s="66"/>
+      <c r="J64" s="66"/>
+      <c r="K64" s="66"/>
+      <c r="L64" s="66"/>
     </row>
     <row r="65" spans="3:12">
       <c r="C65" s="19" t="b">
@@ -4817,18 +4833,18 @@
       <c r="G69" s="19"/>
     </row>
     <row r="70" spans="3:12">
-      <c r="C70" s="81" t="s">
+      <c r="C70" s="66" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="81"/>
-      <c r="E70" s="81"/>
-      <c r="F70" s="81"/>
-      <c r="G70" s="81"/>
-      <c r="H70" s="81"/>
-      <c r="I70" s="81"/>
-      <c r="J70" s="81"/>
-      <c r="K70" s="81"/>
-      <c r="L70" s="81"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="66"/>
+      <c r="I70" s="66"/>
+      <c r="J70" s="66"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="66"/>
     </row>
     <row r="71" spans="3:12">
       <c r="C71" s="19">
@@ -5151,18 +5167,18 @@
       </c>
     </row>
     <row r="80" spans="3:12">
-      <c r="C80" s="81" t="s">
+      <c r="C80" s="66" t="s">
         <v>299</v>
       </c>
-      <c r="D80" s="81"/>
-      <c r="E80" s="81"/>
-      <c r="F80" s="81"/>
-      <c r="G80" s="81"/>
-      <c r="H80" s="81"/>
-      <c r="I80" s="81"/>
-      <c r="J80" s="81"/>
-      <c r="K80" s="81"/>
-      <c r="L80" s="81"/>
+      <c r="D80" s="66"/>
+      <c r="E80" s="66"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="66"/>
+      <c r="H80" s="66"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="66"/>
+      <c r="K80" s="66"/>
+      <c r="L80" s="66"/>
     </row>
     <row r="81" spans="3:14">
       <c r="C81" s="19">
@@ -5676,22 +5692,22 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C80:L80"/>
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C30:P30"/>
     <mergeCell ref="C6:P6"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="J25:J28"/>
@@ -5708,22 +5724,22 @@
     <mergeCell ref="K17:P17"/>
     <mergeCell ref="K18:P18"/>
     <mergeCell ref="K19:P19"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="K20:P20"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C80:L80"/>
+    <mergeCell ref="C64:L64"/>
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9506,112 +9522,131 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF83A4B8-03E1-8F47-A654-49287922FEC9}">
-  <dimension ref="C4:C24"/>
+  <dimension ref="B2:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="4.5" style="85" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" style="89" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="3:3">
-      <c r="C4" t="s">
+    <row r="2" spans="2:10" ht="26">
+      <c r="B2" s="87" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="5" spans="3:3">
+    <row r="4" spans="2:10">
+      <c r="B4" s="88" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="C5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3">
-      <c r="C6" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3">
+        <v>444</v>
+      </c>
+      <c r="I5" s="90" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="85">
+        <v>1</v>
+      </c>
       <c r="C7" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="8" spans="3:3">
+      <c r="I7" s="89">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="85">
+        <v>2</v>
+      </c>
       <c r="C8" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3">
+        <v>453</v>
+      </c>
+      <c r="I8" s="89">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="85">
+        <v>3</v>
+      </c>
       <c r="C9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="85">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="10" spans="3:3">
-      <c r="C10" t="s">
+    <row r="12" spans="2:10">
+      <c r="C12" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="85">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="85">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="85">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="11" spans="3:3">
-      <c r="C11" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13" t="s">
+    <row r="18" spans="2:3">
+      <c r="B18" s="86" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="3:3">
-      <c r="C14" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="15" spans="3:3">
-      <c r="C15" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="16" spans="3:3">
-      <c r="C16" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
+    <row r="19" spans="2:3">
+      <c r="B19" s="85">
+        <v>1</v>
+      </c>
       <c r="C19" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="20" spans="3:3">
+    <row r="20" spans="2:3">
+      <c r="B20" s="85">
+        <v>2</v>
+      </c>
       <c r="C20" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="85">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
         <v>456</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" t="s">
-        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED19C436-4FC2-C549-9BC6-084192C8C6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D129946-74A5-0C40-B9DB-E23C3E0E3F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="6" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="7" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Test sheet Similarity" sheetId="4" r:id="rId5"/>
     <sheet name="Test sheet LL" sheetId="7" r:id="rId6"/>
     <sheet name="Compiler" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="464">
   <si>
     <t>essere</t>
   </si>
@@ -1615,6 +1616,24 @@
   </si>
   <si>
     <t>isolate all the statements (across the nested structure) with duplication for conjuncts and subordinates, matching all entities</t>
+  </si>
+  <si>
+    <t>sentence</t>
+  </si>
+  <si>
+    <t>subject + properties</t>
+  </si>
+  <si>
+    <t>predicate + properties</t>
+  </si>
+  <si>
+    <t>direct + properties</t>
+  </si>
+  <si>
+    <t>ind (foreach type) + properties</t>
+  </si>
+  <si>
+    <t>100 + 2925</t>
   </si>
 </sst>
 </file>
@@ -2113,32 +2132,26 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2158,7 +2171,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2173,29 +2195,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2865,12 +2884,12 @@
       <c r="D30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="69" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
       <c r="I30" s="4" t="s">
         <v>341</v>
       </c>
@@ -2933,12 +2952,12 @@
       <c r="D36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="69" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="4"/>
@@ -3618,22 +3637,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="76" t="s">
         <v>344</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="70"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="78"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3641,24 +3660,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="70" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="72" t="s">
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="74"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="72"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3711,28 +3730,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="79" t="s">
+      <c r="D9" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="80" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="67"/>
-      <c r="P9" s="67"/>
+      <c r="K9" s="79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3748,24 +3767,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="80"/>
-      <c r="D10" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="84"/>
+      <c r="P10" s="84"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -3781,24 +3800,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="80"/>
-      <c r="D11" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="79"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -3814,24 +3833,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="81"/>
-      <c r="D12" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="79"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="79"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -3852,22 +3871,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="76" t="s">
         <v>345</v>
       </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="70"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="78"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -3875,24 +3894,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="70" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="72" t="s">
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="73"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="74"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -3945,28 +3964,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="79" t="s">
+      <c r="D17" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="80" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="67"/>
+      <c r="K17" s="79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="79"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -3974,24 +3993,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="80"/>
-      <c r="D18" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -3999,24 +4018,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="80"/>
-      <c r="D19" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -4024,24 +4043,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="81"/>
-      <c r="D20" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="67"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="79"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4052,46 +4071,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="76" t="s">
         <v>346</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="70"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="77"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="77"/>
+      <c r="P22" s="78"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="70" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="72" t="s">
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="70" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="73"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="73"/>
-      <c r="P23" s="74"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4142,100 +4161,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="82" t="s">
+      <c r="D25" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="67" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="67"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="67"/>
+      <c r="K25" s="79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="79"/>
+      <c r="O25" s="79"/>
+      <c r="P25" s="79"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="80"/>
-      <c r="D26" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="78"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="84"/>
+      <c r="P26" s="84"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="80"/>
-      <c r="D27" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="80"/>
-      <c r="K27" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="84"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="81"/>
-      <c r="D28" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="67"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="78"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="79"/>
+      <c r="P28" s="79"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4245,46 +4264,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="76" t="s">
         <v>347</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="70"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="77"/>
+      <c r="M30" s="77"/>
+      <c r="N30" s="77"/>
+      <c r="O30" s="77"/>
+      <c r="P30" s="78"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="72" t="s">
+      <c r="C31" s="70" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="72" t="s">
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="70" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="73"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="74"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4338,25 +4357,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D33" s="76" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="70"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="78"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="67" t="s">
+      <c r="K33" s="79" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="67"/>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="67"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="79"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4370,19 +4389,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="71" t="s">
+      <c r="F36" s="86" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="71"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="86"/>
+      <c r="M36" s="86"/>
+      <c r="N36" s="86"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="86"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4664,18 +4683,18 @@
       </c>
     </row>
     <row r="64" spans="2:12">
-      <c r="C64" s="66" t="s">
+      <c r="C64" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D64" s="66"/>
-      <c r="E64" s="66"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="66"/>
-      <c r="I64" s="66"/>
-      <c r="J64" s="66"/>
-      <c r="K64" s="66"/>
-      <c r="L64" s="66"/>
+      <c r="D64" s="85"/>
+      <c r="E64" s="85"/>
+      <c r="F64" s="85"/>
+      <c r="G64" s="85"/>
+      <c r="H64" s="85"/>
+      <c r="I64" s="85"/>
+      <c r="J64" s="85"/>
+      <c r="K64" s="85"/>
+      <c r="L64" s="85"/>
     </row>
     <row r="65" spans="3:12">
       <c r="C65" s="19" t="b">
@@ -4833,18 +4852,18 @@
       <c r="G69" s="19"/>
     </row>
     <row r="70" spans="3:12">
-      <c r="C70" s="66" t="s">
+      <c r="C70" s="85" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="66"/>
-      <c r="E70" s="66"/>
-      <c r="F70" s="66"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="66"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="66"/>
-      <c r="K70" s="66"/>
-      <c r="L70" s="66"/>
+      <c r="D70" s="85"/>
+      <c r="E70" s="85"/>
+      <c r="F70" s="85"/>
+      <c r="G70" s="85"/>
+      <c r="H70" s="85"/>
+      <c r="I70" s="85"/>
+      <c r="J70" s="85"/>
+      <c r="K70" s="85"/>
+      <c r="L70" s="85"/>
     </row>
     <row r="71" spans="3:12">
       <c r="C71" s="19">
@@ -5167,18 +5186,18 @@
       </c>
     </row>
     <row r="80" spans="3:12">
-      <c r="C80" s="66" t="s">
+      <c r="C80" s="85" t="s">
         <v>299</v>
       </c>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
-      <c r="J80" s="66"/>
-      <c r="K80" s="66"/>
-      <c r="L80" s="66"/>
+      <c r="D80" s="85"/>
+      <c r="E80" s="85"/>
+      <c r="F80" s="85"/>
+      <c r="G80" s="85"/>
+      <c r="H80" s="85"/>
+      <c r="I80" s="85"/>
+      <c r="J80" s="85"/>
+      <c r="K80" s="85"/>
+      <c r="L80" s="85"/>
     </row>
     <row r="81" spans="3:14">
       <c r="C81" s="19">
@@ -5692,6 +5711,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="C80:L80"/>
+    <mergeCell ref="C64:L64"/>
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="K19:P19"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="J7:P7"/>
@@ -5708,38 +5759,6 @@
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C80:L80"/>
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5833,62 +5852,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
     </row>
     <row r="3" spans="2:33">
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
       <c r="M3" s="31"/>
     </row>
     <row r="4" spans="2:33">
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
     </row>
     <row r="5" spans="2:33">
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
     </row>
     <row r="6" spans="2:33">
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="O6" s="83" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="O6" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
+      <c r="P6" s="87"/>
+      <c r="Q6" s="87"/>
+      <c r="R6" s="87"/>
     </row>
     <row r="7" spans="2:33">
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87"/>
+      <c r="R7" s="87"/>
     </row>
     <row r="8" spans="2:33">
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="O8" s="87"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="87"/>
     </row>
     <row r="9" spans="2:33">
       <c r="B9" s="33" t="s">
@@ -5919,10 +5938,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="31"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="87"/>
+      <c r="R9" s="87"/>
     </row>
     <row r="10" spans="2:33">
       <c r="B10" s="31" t="s">
@@ -5952,10 +5971,10 @@
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
+      <c r="O10" s="87"/>
+      <c r="P10" s="87"/>
+      <c r="Q10" s="87"/>
+      <c r="R10" s="87"/>
     </row>
     <row r="11" spans="2:33">
       <c r="B11" s="31" t="s">
@@ -6824,12 +6843,12 @@
       </c>
     </row>
     <row r="25" spans="2:33">
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
       <c r="O25" s="2" t="s">
         <v>23</v>
       </c>
@@ -6898,10 +6917,10 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1">
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="N26" s="34" t="s">
         <v>23</v>
       </c>
@@ -6972,10 +6991,10 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1">
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
       <c r="N27" s="34" t="s">
         <v>24</v>
       </c>
@@ -7046,10 +7065,10 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1">
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
       <c r="N28" s="34" t="s">
         <v>25</v>
       </c>
@@ -7120,10 +7139,10 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1">
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
       <c r="N29" s="34" t="s">
         <v>27</v>
       </c>
@@ -8607,7 +8626,7 @@
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="39" customHeight="1">
-      <c r="A19" s="63">
+      <c r="A19" s="89">
         <v>2</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -8651,7 +8670,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="39" customHeight="1">
-      <c r="A20" s="63"/>
+      <c r="A20" s="89"/>
       <c r="B20" s="6" t="s">
         <v>98</v>
       </c>
@@ -8870,12 +8889,12 @@
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="64" t="s">
+      <c r="I29" s="90" t="s">
         <v>419</v>
       </c>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="64"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
     </row>
     <row r="30" spans="1:15" ht="39" customHeight="1">
       <c r="A30" s="6"/>
@@ -9240,12 +9259,12 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="90" t="s">
         <v>420</v>
       </c>
-      <c r="J47" s="64"/>
-      <c r="K47" s="64"/>
-      <c r="L47" s="64"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="90"/>
+      <c r="L47" s="90"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
@@ -9525,17 +9544,17 @@
   <dimension ref="B2:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="4.5" style="85" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="89" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="63" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="26">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="65" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="66" t="s">
         <v>441</v>
       </c>
     </row>
@@ -9543,18 +9562,18 @@
       <c r="C5" t="s">
         <v>444</v>
       </c>
-      <c r="I5" s="90" t="s">
+      <c r="I5" s="68" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="85">
+      <c r="B7" s="63">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>443</v>
       </c>
-      <c r="I7" s="89">
+      <c r="I7" s="67">
         <v>1</v>
       </c>
       <c r="J7" t="s">
@@ -9562,13 +9581,13 @@
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="85">
+      <c r="B8" s="63">
         <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>453</v>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="67">
         <v>2</v>
       </c>
       <c r="J8" t="s">
@@ -9576,7 +9595,7 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="85">
+      <c r="B9" s="63">
         <v>3</v>
       </c>
       <c r="C9" t="s">
@@ -9584,7 +9603,7 @@
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="85">
+      <c r="B10" s="63">
         <v>4</v>
       </c>
       <c r="C10" t="s">
@@ -9597,7 +9616,7 @@
       </c>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="85">
+      <c r="B14" s="63">
         <v>1</v>
       </c>
       <c r="C14" t="s">
@@ -9605,7 +9624,7 @@
       </c>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="85">
+      <c r="B15" s="63">
         <v>2</v>
       </c>
       <c r="C15" t="s">
@@ -9613,7 +9632,7 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="85">
+      <c r="B16" s="63">
         <v>3</v>
       </c>
       <c r="C16" t="s">
@@ -9621,12 +9640,12 @@
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="64" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="85">
+      <c r="B19" s="63">
         <v>1</v>
       </c>
       <c r="C19" t="s">
@@ -9634,7 +9653,7 @@
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="85">
+      <c r="B20" s="63">
         <v>2</v>
       </c>
       <c r="C20" t="s">
@@ -9642,11 +9661,59 @@
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="85">
+      <c r="B21" s="63">
         <v>3</v>
       </c>
       <c r="C21" t="s">
         <v>456</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DD2502-0F1B-8E4C-91C2-32C74D9C1A25}">
+  <dimension ref="B4:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:5">
+      <c r="B4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8">
+        <v>2925</v>
+      </c>
+      <c r="C8">
+        <v>2925</v>
+      </c>
+      <c r="D8">
+        <v>2925</v>
+      </c>
+      <c r="E8" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D129946-74A5-0C40-B9DB-E23C3E0E3F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F57B7A7-C879-D241-AEE7-1D32BC609854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="7" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="2" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="468">
   <si>
     <t>essere</t>
   </si>
@@ -908,9 +908,6 @@
   </si>
   <si>
     <t>FUZZY (0,1)</t>
-  </si>
-  <si>
-    <t>v1*v2</t>
   </si>
   <si>
     <t xml:space="preserve">fuzzy </t>
@@ -1634,6 +1631,21 @@
   </si>
   <si>
     <t>100 + 2925</t>
+  </si>
+  <si>
+    <t>v2&lt;=v1 ? 1 : v1</t>
+  </si>
+  <si>
+    <t>equality</t>
+  </si>
+  <si>
+    <t>min(imply, converse)</t>
+  </si>
+  <si>
+    <t>min(v1, v2)</t>
+  </si>
+  <si>
+    <t>max(v1, v2)</t>
   </si>
 </sst>
 </file>
@@ -2153,6 +2165,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2171,16 +2201,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2193,15 +2214,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2769,7 +2781,7 @@
         <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H19" s="6"/>
     </row>
@@ -2781,7 +2793,7 @@
         <v>108</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H20" s="6"/>
     </row>
@@ -2836,7 +2848,7 @@
         <v>80</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>160</v>
@@ -2844,7 +2856,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="I27" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="18">
@@ -2873,7 +2885,7 @@
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="16" customHeight="1">
@@ -2891,7 +2903,7 @@
       <c r="G30" s="69"/>
       <c r="H30" s="69"/>
       <c r="I30" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="2:14">
@@ -2909,7 +2921,7 @@
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="18">
@@ -3074,7 +3086,7 @@
         <v>63</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="2:5">
@@ -3474,91 +3486,91 @@
     </row>
     <row r="26" spans="3:10">
       <c r="C26" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="3:10">
       <c r="C27" s="53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G27" s="15"/>
       <c r="J27" s="15"/>
     </row>
     <row r="28" spans="3:10">
       <c r="C28" s="53" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="3:10">
       <c r="C29" s="53" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="3:10">
       <c r="C30" s="53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="3:10">
       <c r="C31" s="53" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="3:10">
       <c r="C32" s="53" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" s="53" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" s="53" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" s="53" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" spans="3:3">
       <c r="C36" s="53" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" s="53" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="3:3">
       <c r="C38" s="53" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" s="53" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="3:3">
       <c r="C40" s="53" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="3:3">
       <c r="C41" s="53" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="3:3">
       <c r="C42" s="53" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -3587,7 +3599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0889CCB1-49C5-2548-AD66-B49F18C82431}">
-  <dimension ref="B2:U104"/>
+  <dimension ref="B2:U105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="2"/>
@@ -3637,22 +3649,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="76" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="78"/>
+      <c r="C6" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="74"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3660,24 +3672,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="70" t="s">
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="76" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="72"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="78"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3730,28 +3742,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="83" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="80" t="s">
+      <c r="D9" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="79"/>
-      <c r="M9" s="79"/>
-      <c r="N9" s="79"/>
-      <c r="O9" s="79"/>
-      <c r="P9" s="79"/>
+      <c r="K9" s="71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3767,24 +3779,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="81"/>
-      <c r="D10" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="84"/>
-      <c r="M10" s="84"/>
-      <c r="N10" s="84"/>
-      <c r="O10" s="84"/>
-      <c r="P10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="82"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="82"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -3800,24 +3812,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="81"/>
-      <c r="D11" s="76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -3833,24 +3845,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="82"/>
-      <c r="D12" s="76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -3871,22 +3883,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="76" t="s">
-        <v>345</v>
-      </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="78"/>
+      <c r="C14" s="72" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="74"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -3894,24 +3906,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="70" t="s">
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="76" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="78"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -3964,28 +3976,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="83" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="80" t="s">
+      <c r="D17" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="83" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="79"/>
+      <c r="K17" s="71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -3993,24 +4005,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="81"/>
-      <c r="D18" s="76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="71"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -4018,24 +4030,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="81"/>
-      <c r="D19" s="73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="84"/>
-      <c r="M19" s="84"/>
-      <c r="N19" s="84"/>
-      <c r="O19" s="84"/>
-      <c r="P19" s="84"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="82"/>
+      <c r="M19" s="82"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="82"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -4043,24 +4055,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="82"/>
-      <c r="D20" s="76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="71"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4071,46 +4083,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="76" t="s">
-        <v>346</v>
-      </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="78"/>
+      <c r="C22" s="72" t="s">
+        <v>345</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="74"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="70" t="s">
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="76" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="77"/>
+      <c r="M23" s="77"/>
+      <c r="N23" s="77"/>
+      <c r="O23" s="77"/>
+      <c r="P23" s="78"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4161,100 +4173,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="83" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="83" t="s">
+      <c r="D25" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="86" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
-      <c r="P25" s="79"/>
+      <c r="K25" s="71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="81"/>
-      <c r="D26" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="84"/>
-      <c r="P26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="81"/>
-      <c r="D27" s="73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="84"/>
-      <c r="P27" s="84"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="82"/>
-      <c r="D28" s="76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="79"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="71"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4264,46 +4276,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="76" t="s">
-        <v>347</v>
-      </c>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
-      <c r="L30" s="77"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="77"/>
-      <c r="P30" s="78"/>
+      <c r="C30" s="72" t="s">
+        <v>346</v>
+      </c>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="74"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="76" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="70" t="s">
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="76" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="72"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="77"/>
+      <c r="P31" s="78"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4357,25 +4369,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="76" t="s">
+      <c r="D33" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="78"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="74"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="79" t="s">
+      <c r="K33" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="79"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="71"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4389,19 +4401,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="86" t="s">
+      <c r="F36" s="75" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="86"/>
-      <c r="H36" s="86"/>
-      <c r="I36" s="86"/>
-      <c r="J36" s="86"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="86"/>
-      <c r="M36" s="86"/>
-      <c r="N36" s="86"/>
-      <c r="O36" s="86"/>
-      <c r="P36" s="86"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="75"/>
+      <c r="L36" s="75"/>
+      <c r="M36" s="75"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="75"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4452,7 +4464,7 @@
         <v>245</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>243</v>
@@ -4493,7 +4505,7 @@
         <v>245</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>243</v>
@@ -4568,7 +4580,7 @@
         <v>279</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -4579,7 +4591,7 @@
         <v>284</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>288</v>
+        <v>466</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -4590,7 +4602,7 @@
         <v>280</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>26</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -4601,7 +4613,7 @@
         <v>146</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -4609,10 +4621,10 @@
         <v>283</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E56" s="32" t="s">
         <v>291</v>
-      </c>
-      <c r="E56" s="32" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -4620,10 +4632,10 @@
         <v>283</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E57" s="32" t="s">
         <v>293</v>
-      </c>
-      <c r="E57" s="32" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -4631,10 +4643,10 @@
         <v>283</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -4642,143 +4654,120 @@
         <v>283</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12">
-      <c r="C61" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12">
+      <c r="B60" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12">
+      <c r="C62" s="31" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="63" spans="2:12">
-      <c r="C63" s="22" t="s">
+    <row r="64" spans="2:12">
+      <c r="C64" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D64" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E64" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F64" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="G63" s="22" t="s">
+      <c r="G64" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H64" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="I63" s="22" t="s">
+      <c r="I64" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="J63" s="22" t="s">
+      <c r="J64" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="K63" s="22" t="s">
+      <c r="K64" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="L63" s="22" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12">
-      <c r="C64" s="85" t="s">
+      <c r="L64" s="22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="65" spans="3:12">
+      <c r="C65" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="D64" s="85"/>
-      <c r="E64" s="85"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="85"/>
-      <c r="H64" s="85"/>
-      <c r="I64" s="85"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="85"/>
-      <c r="L64" s="85"/>
-    </row>
-    <row r="65" spans="3:12">
-      <c r="C65" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="D65" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="19" t="b">
-        <f>AND(C65,D65)</f>
-        <v>1</v>
-      </c>
-      <c r="F65" s="19" t="b">
-        <f>OR(C65,D65)</f>
-        <v>1</v>
-      </c>
-      <c r="G65" s="19" t="b">
-        <f>NOT(C65)</f>
-        <v>0</v>
-      </c>
-      <c r="H65" s="19" t="b">
-        <f>_xlfn.XOR(C65,D65)</f>
-        <v>0</v>
-      </c>
-      <c r="I65" s="19" t="b">
-        <f>NOT(_xlfn.XOR(C65,D65))</f>
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K65" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L65" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="D65" s="70"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="70"/>
+      <c r="G65" s="70"/>
+      <c r="H65" s="70"/>
+      <c r="I65" s="70"/>
+      <c r="J65" s="70"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="70"/>
     </row>
     <row r="66" spans="3:12">
       <c r="C66" s="19" t="b">
         <v>1</v>
       </c>
       <c r="D66" s="19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="19" t="b">
-        <f t="shared" ref="E66:E68" si="0">AND(C66,D66)</f>
-        <v>0</v>
+        <f>AND(C66,D66)</f>
+        <v>1</v>
       </c>
       <c r="F66" s="19" t="b">
         <f>OR(C66,D66)</f>
         <v>1</v>
       </c>
       <c r="G66" s="19" t="b">
-        <f t="shared" ref="G66:G68" si="1">NOT(C66)</f>
+        <f>NOT(C66)</f>
         <v>0</v>
       </c>
       <c r="H66" s="19" t="b">
         <f>_xlfn.XOR(C66,D66)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" s="19" t="b">
         <f>NOT(_xlfn.XOR(C66,D66))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L66" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="3:12">
       <c r="C67" s="19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" s="19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="19" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E67:E69" si="0">AND(C67,D67)</f>
         <v>0</v>
       </c>
       <c r="F67" s="19" t="b">
@@ -4786,8 +4775,8 @@
         <v>1</v>
       </c>
       <c r="G67" s="19" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" ref="G67:G69" si="1">NOT(C67)</f>
+        <v>0</v>
       </c>
       <c r="H67" s="19" t="b">
         <f>_xlfn.XOR(C67,D67)</f>
@@ -4798,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="b">
         <v>0</v>
@@ -4812,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="19" t="b">
         <f t="shared" si="0"/>
@@ -4820,7 +4809,7 @@
       </c>
       <c r="F68" s="19" t="b">
         <f>OR(C68,D68)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="19" t="b">
         <f t="shared" si="1"/>
@@ -4828,129 +4817,126 @@
       </c>
       <c r="H68" s="19" t="b">
         <f>_xlfn.XOR(C68,D68)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="19" t="b">
         <f>NOT(_xlfn.XOR(C68,D68))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="b">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="3:12">
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
+      <c r="C69" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="19" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="19" t="b">
+        <f>OR(C69,D69)</f>
+        <v>0</v>
+      </c>
+      <c r="G69" s="19" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H69" s="19" t="b">
+        <f>_xlfn.XOR(C69,D69)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="19" t="b">
+        <f>NOT(_xlfn.XOR(C69,D69))</f>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="3:12">
-      <c r="C70" s="85" t="s">
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="3:12">
+      <c r="C71" s="70" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="85"/>
-      <c r="E70" s="85"/>
-      <c r="F70" s="85"/>
-      <c r="G70" s="85"/>
-      <c r="H70" s="85"/>
-      <c r="I70" s="85"/>
-      <c r="J70" s="85"/>
-      <c r="K70" s="85"/>
-      <c r="L70" s="85"/>
-    </row>
-    <row r="71" spans="3:12">
-      <c r="C71" s="19">
-        <v>1</v>
-      </c>
-      <c r="D71" s="19">
-        <v>1</v>
-      </c>
-      <c r="E71" s="19">
-        <f t="shared" ref="E71:E78" si="2">MIN(C71,D71)</f>
-        <v>1</v>
-      </c>
-      <c r="F71" s="19">
-        <f t="shared" ref="F71:F78" si="3">MAX(C71,D71)</f>
-        <v>1</v>
-      </c>
-      <c r="G71" s="19">
-        <f t="shared" ref="G71:G78" si="4">1-C71</f>
-        <v>0</v>
-      </c>
-      <c r="H71" s="19">
-        <f t="shared" ref="H71:H78" si="5">MAX(MIN(C71, 1-D71), MIN(1-C71,D71))</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="19">
-        <f t="shared" ref="I71:I78" si="6">1-MAX(MIN(C71,1-D71),MIN(1-C71,D71))</f>
-        <v>1</v>
-      </c>
-      <c r="J71" s="19">
-        <f t="shared" ref="J71:J78" si="7">IF(C71&lt;=D71,1,D71)</f>
-        <v>1</v>
-      </c>
-      <c r="K71" s="19">
-        <f t="shared" ref="K71:K78" si="8">IF(D71&lt;=C71,1,C71)</f>
-        <v>1</v>
-      </c>
-      <c r="L71" s="19">
-        <f t="shared" ref="L71:L78" si="9">MIN(IF(C71&lt;=D71,1,D71),IF(D71&lt;=C71,1,C71))</f>
-        <v>1</v>
-      </c>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
     </row>
     <row r="72" spans="3:12">
       <c r="C72" s="19">
         <v>1</v>
       </c>
       <c r="D72" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="E72:E79" si="2">MIN(C72,D72)</f>
+        <v>1</v>
       </c>
       <c r="F72" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F72:F79" si="3">MAX(C72,D72)</f>
         <v>1</v>
       </c>
       <c r="G72" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G72:G79" si="4">1-C72</f>
         <v>0</v>
       </c>
       <c r="H72" s="19">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" ref="H72:H79" si="5">MAX(MIN(C72, 1-D72), MIN(1-C72,D72))</f>
+        <v>0</v>
       </c>
       <c r="I72" s="19">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="I72:I79" si="6">1-MAX(MIN(C72,1-D72),MIN(1-C72,D72))</f>
+        <v>1</v>
       </c>
       <c r="J72" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" ref="J72:J79" si="7">IF(C72&lt;=D72,1,D72)</f>
+        <v>1</v>
       </c>
       <c r="K72" s="19">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="K72:K79" si="8">IF(D72&lt;=C72,1,C72)</f>
         <v>1</v>
       </c>
       <c r="L72" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" ref="L72:L79" si="9">MIN(IF(C72&lt;=D72,1,D72),IF(D72&lt;=C72,1,C72))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="3:12">
       <c r="C73" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="19">
         <f t="shared" si="2"/>
@@ -4962,7 +4948,7 @@
       </c>
       <c r="G73" s="19">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="19">
         <f t="shared" si="5"/>
@@ -4974,11 +4960,11 @@
       </c>
       <c r="J73" s="19">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="19">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="19">
         <f t="shared" si="9"/>
@@ -4990,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="19">
         <f t="shared" si="2"/>
@@ -4998,7 +4984,7 @@
       </c>
       <c r="F74" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="19">
         <f t="shared" si="4"/>
@@ -5006,11 +4992,11 @@
       </c>
       <c r="H74" s="19">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="19">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="19">
         <f t="shared" si="7"/>
@@ -5018,39 +5004,39 @@
       </c>
       <c r="K74" s="19">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="19">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="3:12">
       <c r="C75" s="19">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D75" s="19">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E75" s="19">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F75" s="19">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G75" s="19">
         <f t="shared" si="4"/>
-        <v>0.19999999999999996</v>
+        <v>1</v>
       </c>
       <c r="H75" s="19">
         <f t="shared" si="5"/>
-        <v>0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="I75" s="19">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J75" s="19">
         <f t="shared" si="7"/>
@@ -5067,34 +5053,34 @@
     </row>
     <row r="76" spans="3:12">
       <c r="C76" s="19">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D76" s="19">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E76" s="19">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="F76" s="19">
         <f t="shared" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G76" s="19">
         <f t="shared" si="4"/>
-        <v>9.9999999999999978E-2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H76" s="19">
         <f t="shared" si="5"/>
-        <v>0.9</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="I76" s="19">
         <f t="shared" si="6"/>
-        <v>9.9999999999999978E-2</v>
+        <v>0.8</v>
       </c>
       <c r="J76" s="19">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K76" s="19">
         <f t="shared" si="8"/>
@@ -5102,15 +5088,15 @@
       </c>
       <c r="L76" s="19">
         <f t="shared" si="9"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="3:12">
       <c r="C77" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="D77" s="19">
         <v>0.1</v>
-      </c>
-      <c r="D77" s="19">
-        <v>0.9</v>
       </c>
       <c r="E77" s="19">
         <f t="shared" si="2"/>
@@ -5122,7 +5108,7 @@
       </c>
       <c r="G77" s="19">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="H77" s="19">
         <f t="shared" si="5"/>
@@ -5134,11 +5120,11 @@
       </c>
       <c r="J77" s="19">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K77" s="19">
         <f t="shared" si="8"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L77" s="19">
         <f t="shared" si="9"/>
@@ -5147,30 +5133,30 @@
     </row>
     <row r="78" spans="3:12">
       <c r="C78" s="19">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D78" s="19">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="E78" s="19">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F78" s="19">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="G78" s="19">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H78" s="19">
         <f t="shared" si="5"/>
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="I78" s="19">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="J78" s="19">
         <f t="shared" si="7"/>
@@ -5178,555 +5164,595 @@
       </c>
       <c r="K78" s="19">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L78" s="19">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="3:12">
-      <c r="C80" s="85" t="s">
-        <v>299</v>
-      </c>
-      <c r="D80" s="85"/>
-      <c r="E80" s="85"/>
-      <c r="F80" s="85"/>
-      <c r="G80" s="85"/>
-      <c r="H80" s="85"/>
-      <c r="I80" s="85"/>
-      <c r="J80" s="85"/>
-      <c r="K80" s="85"/>
-      <c r="L80" s="85"/>
-    </row>
-    <row r="81" spans="3:14">
-      <c r="C81" s="19">
-        <f t="shared" ref="C81:C88" si="10">C71 * 2 -1</f>
-        <v>1</v>
-      </c>
-      <c r="D81" s="19">
-        <f t="shared" ref="D81:L81" si="11">D71 * 2 -1</f>
-        <v>1</v>
-      </c>
-      <c r="E81" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79" spans="3:12">
+      <c r="C79" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="D79" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="E79" s="19">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="F79" s="19">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="G79" s="19">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="H79" s="19">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="I79" s="19">
+        <f t="shared" si="6"/>
+        <v>0.8</v>
+      </c>
+      <c r="J79" s="19">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K79" s="19">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="L79" s="19">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12">
+      <c r="C81" s="70" t="s">
+        <v>298</v>
+      </c>
+      <c r="D81" s="70"/>
+      <c r="E81" s="70"/>
+      <c r="F81" s="70"/>
+      <c r="G81" s="70"/>
+      <c r="H81" s="70"/>
+      <c r="I81" s="70"/>
+      <c r="J81" s="70"/>
+      <c r="K81" s="70"/>
+      <c r="L81" s="70"/>
+    </row>
+    <row r="82" spans="3:12">
+      <c r="C82" s="19">
+        <f t="shared" ref="C82:C89" si="10">C72 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="D82" s="19">
+        <f t="shared" ref="D82:L82" si="11">D72 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="E82" s="19">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="F81" s="19">
+      <c r="F82" s="19">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="G81" s="19">
+      <c r="G82" s="19">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="H81" s="19">
+      <c r="H82" s="19">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="I81" s="19">
+      <c r="I82" s="19">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="J81" s="19">
+      <c r="J82" s="19">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="K81" s="19">
+      <c r="K82" s="19">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L81" s="19">
+      <c r="L82" s="19">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="3:14">
-      <c r="C82" s="19">
+    <row r="83" spans="3:12">
+      <c r="C83" s="19">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D82" s="19">
-        <f t="shared" ref="D82:L82" si="12">D72 * 2 -1</f>
+      <c r="D83" s="19">
+        <f t="shared" ref="D83:L83" si="12">D73 * 2 -1</f>
         <v>-1</v>
       </c>
-      <c r="E82" s="19">
+      <c r="E83" s="19">
         <f t="shared" si="12"/>
         <v>-1</v>
       </c>
-      <c r="F82" s="19">
+      <c r="F83" s="19">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="G82" s="19">
+      <c r="G83" s="19">
         <f t="shared" si="12"/>
         <v>-1</v>
       </c>
-      <c r="H82" s="19">
+      <c r="H83" s="19">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="I82" s="19">
+      <c r="I83" s="19">
         <f t="shared" si="12"/>
         <v>-1</v>
       </c>
-      <c r="J82" s="19">
+      <c r="J83" s="19">
         <f t="shared" si="12"/>
         <v>-1</v>
       </c>
-      <c r="K82" s="19">
+      <c r="K83" s="19">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="L82" s="19">
+      <c r="L83" s="19">
         <f t="shared" si="12"/>
         <v>-1</v>
       </c>
     </row>
-    <row r="83" spans="3:14">
-      <c r="C83" s="19">
-        <f t="shared" si="10"/>
-        <v>-1</v>
-      </c>
-      <c r="D83" s="19">
-        <f t="shared" ref="D83:L83" si="13">D73 * 2 -1</f>
-        <v>1</v>
-      </c>
-      <c r="E83" s="19">
-        <f t="shared" si="13"/>
-        <v>-1</v>
-      </c>
-      <c r="F83" s="19">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="G83" s="19">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="H83" s="19">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="I83" s="19">
-        <f t="shared" si="13"/>
-        <v>-1</v>
-      </c>
-      <c r="J83" s="19">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="K83" s="19">
-        <f t="shared" si="13"/>
-        <v>-1</v>
-      </c>
-      <c r="L83" s="19">
-        <f t="shared" si="13"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="84" spans="3:14">
+    <row r="84" spans="3:12">
       <c r="C84" s="19">
         <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="D84" s="19">
-        <f t="shared" ref="D84:L84" si="14">D74 * 2 -1</f>
+        <f t="shared" ref="D84:L84" si="13">D74 * 2 -1</f>
+        <v>1</v>
+      </c>
+      <c r="E84" s="19">
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
-      <c r="E84" s="19">
+      <c r="F84" s="19">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G84" s="19">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="H84" s="19">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="I84" s="19">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+      <c r="J84" s="19">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="K84" s="19">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+      <c r="L84" s="19">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12">
+      <c r="C85" s="19">
+        <f t="shared" si="10"/>
+        <v>-1</v>
+      </c>
+      <c r="D85" s="19">
+        <f t="shared" ref="D85:L85" si="14">D75 * 2 -1</f>
+        <v>-1</v>
+      </c>
+      <c r="E85" s="19">
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="F84" s="19">
+      <c r="F85" s="19">
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="G84" s="19">
+      <c r="G85" s="19">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="H84" s="19">
+      <c r="H85" s="19">
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="I84" s="19">
+      <c r="I85" s="19">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="J84" s="19">
+      <c r="J85" s="19">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="K84" s="19">
+      <c r="K85" s="19">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="L84" s="19">
+      <c r="L85" s="19">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="3:14">
-      <c r="C85" s="19">
+    <row r="86" spans="3:12">
+      <c r="C86" s="19">
         <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="D85" s="19">
-        <f t="shared" ref="D85:L85" si="15">D75 * 2 -1</f>
+      <c r="D86" s="19">
+        <f t="shared" ref="D86:L86" si="15">D76 * 2 -1</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="E85" s="19">
+      <c r="E86" s="19">
         <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="F85" s="19">
+      <c r="F86" s="19">
         <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G85" s="19">
+      <c r="G86" s="19">
         <f t="shared" si="15"/>
         <v>-0.60000000000000009</v>
       </c>
-      <c r="H85" s="19">
+      <c r="H86" s="19">
         <f t="shared" si="15"/>
         <v>-0.60000000000000009</v>
       </c>
-      <c r="I85" s="19">
+      <c r="I86" s="19">
         <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J86" s="19">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="K85" s="19">
+      <c r="K86" s="19">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L86" s="19">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="3:14">
-      <c r="C86" s="19">
+    <row r="87" spans="3:12">
+      <c r="C87" s="19">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="D86" s="19">
-        <f t="shared" ref="D86:L86" si="16">D76 * 2 -1</f>
+      <c r="D87" s="19">
+        <f t="shared" ref="D87:L87" si="16">D77 * 2 -1</f>
         <v>-0.8</v>
       </c>
-      <c r="E86" s="19">
+      <c r="E87" s="19">
         <f t="shared" si="16"/>
         <v>-0.8</v>
       </c>
-      <c r="F86" s="19">
+      <c r="F87" s="19">
         <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
-      <c r="G86" s="19">
+      <c r="G87" s="19">
         <f t="shared" si="16"/>
         <v>-0.8</v>
       </c>
-      <c r="H86" s="19">
+      <c r="H87" s="19">
         <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
-      <c r="I86" s="19">
+      <c r="I87" s="19">
         <f t="shared" si="16"/>
         <v>-0.8</v>
       </c>
-      <c r="J86" s="19">
+      <c r="J87" s="19">
         <f t="shared" si="16"/>
         <v>-0.8</v>
       </c>
-      <c r="K86" s="19">
+      <c r="K87" s="19">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="L86" s="19">
+      <c r="L87" s="19">
         <f t="shared" si="16"/>
         <v>-0.8</v>
       </c>
     </row>
-    <row r="87" spans="3:14">
-      <c r="C87" s="19">
+    <row r="88" spans="3:12">
+      <c r="C88" s="19">
         <f t="shared" si="10"/>
         <v>-0.8</v>
       </c>
-      <c r="D87" s="19">
-        <f t="shared" ref="D87:L87" si="17">D77 * 2 -1</f>
+      <c r="D88" s="19">
+        <f t="shared" ref="D88:L88" si="17">D78 * 2 -1</f>
         <v>0.8</v>
       </c>
-      <c r="E87" s="19">
+      <c r="E88" s="19">
         <f t="shared" si="17"/>
         <v>-0.8</v>
       </c>
-      <c r="F87" s="19">
+      <c r="F88" s="19">
         <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="G87" s="19">
+      <c r="G88" s="19">
         <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="H87" s="19">
+      <c r="H88" s="19">
         <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="I87" s="19">
+      <c r="I88" s="19">
         <f t="shared" si="17"/>
         <v>-0.8</v>
       </c>
-      <c r="J87" s="19">
+      <c r="J88" s="19">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K87" s="19">
+      <c r="K88" s="19">
         <f t="shared" si="17"/>
         <v>-0.8</v>
       </c>
-      <c r="L87" s="19">
+      <c r="L88" s="19">
         <f t="shared" si="17"/>
         <v>-0.8</v>
       </c>
     </row>
-    <row r="88" spans="3:14">
-      <c r="C88" s="19">
+    <row r="89" spans="3:12">
+      <c r="C89" s="19">
         <f t="shared" si="10"/>
         <v>-0.6</v>
       </c>
-      <c r="D88" s="19">
-        <f t="shared" ref="D88:L88" si="18">D78 * 2 -1</f>
+      <c r="D89" s="19">
+        <f t="shared" ref="D89:L89" si="18">D79 * 2 -1</f>
         <v>-0.6</v>
       </c>
-      <c r="E88" s="19">
+      <c r="E89" s="19">
         <f t="shared" si="18"/>
         <v>-0.6</v>
       </c>
-      <c r="F88" s="19">
+      <c r="F89" s="19">
         <f t="shared" si="18"/>
         <v>-0.6</v>
       </c>
-      <c r="G88" s="19">
+      <c r="G89" s="19">
         <f t="shared" si="18"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H88" s="19">
+      <c r="H89" s="19">
         <f t="shared" si="18"/>
         <v>-0.6</v>
       </c>
-      <c r="I88" s="19">
+      <c r="I89" s="19">
         <f t="shared" si="18"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="J88" s="19">
+      <c r="J89" s="19">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="K88" s="19">
+      <c r="K89" s="19">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="L88" s="19">
+      <c r="L89" s="19">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="3:14">
-      <c r="C90" s="2" t="s">
+    <row r="91" spans="3:12">
+      <c r="C91" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12">
+      <c r="C93" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12">
+      <c r="C95" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="D95" s="31" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="92" spans="3:14">
-      <c r="C92" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="94" spans="3:14">
-      <c r="C94" s="31" t="s">
+      <c r="E95" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="F95" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="G95" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="H95" s="31" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="96" spans="3:12">
+      <c r="C96" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D94" s="31" t="s">
+      <c r="D96" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E94" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="F94" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="G94" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="H94" s="31" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14">
-      <c r="C95" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="K95" s="31" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="96" spans="3:14">
-      <c r="C96" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="N96" s="2" t="s">
+      <c r="K96" s="31" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="97" spans="3:15">
       <c r="C97" s="2" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>305</v>
       </c>
       <c r="F97" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15">
+      <c r="C98" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="I97" s="2" t="s">
+      <c r="H98" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I98" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K97" s="2" t="s">
+      <c r="K98" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="L98" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="L97" s="2" t="s">
+      <c r="M98" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="M97" s="2" t="s">
+    </row>
+    <row r="99" spans="3:15">
+      <c r="D99" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="L99" s="2" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="98" spans="3:15">
-      <c r="D98" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="99" spans="3:15">
-      <c r="C99" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="M99" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="O99" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="100" spans="3:15">
       <c r="C100" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15">
+      <c r="C101" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="103" spans="3:15">
+      <c r="C103" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="L100" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="O100" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="102" spans="3:15">
-      <c r="C102" s="2" t="s">
+    </row>
+    <row r="104" spans="3:15">
+      <c r="D104" s="31" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="103" spans="3:15">
-      <c r="D103" s="31" t="s">
+      <c r="F104" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F103" s="2" t="s">
+    </row>
+    <row r="105" spans="3:15">
+      <c r="F105" s="2" t="s">
         <v>321</v>
-      </c>
-    </row>
-    <row r="104" spans="3:15">
-      <c r="F104" s="2" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C80:L80"/>
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C30:P30"/>
     <mergeCell ref="C6:P6"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="J25:J28"/>
@@ -5743,22 +5769,22 @@
     <mergeCell ref="K17:P17"/>
     <mergeCell ref="K18:P18"/>
     <mergeCell ref="K19:P19"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="K20:P20"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5798,7 +5824,7 @@
         <v>263</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>268</v>
@@ -5809,7 +5835,7 @@
         <v>266</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>268</v>
@@ -8530,38 +8556,38 @@
   <sheetData>
     <row r="2" spans="2:14" ht="26">
       <c r="B2" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="C4" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="2:14">
       <c r="B5" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="C8" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="2:14">
       <c r="C10" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -8569,7 +8595,7 @@
     </row>
     <row r="12" spans="2:14">
       <c r="C12" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -8580,19 +8606,19 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>378</v>
-      </c>
       <c r="K16" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L16" s="15" t="s">
         <v>135</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N16" s="4"/>
     </row>
@@ -8600,25 +8626,25 @@
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="58" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D18" s="58" t="s">
+        <v>367</v>
+      </c>
+      <c r="E18" s="58" t="s">
         <v>368</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="F18" s="58" t="s">
         <v>369</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="G18" s="58" t="s">
+        <v>309</v>
+      </c>
+      <c r="H18" s="58" t="s">
         <v>370</v>
       </c>
-      <c r="G18" s="58" t="s">
-        <v>310</v>
-      </c>
-      <c r="H18" s="58" t="s">
+      <c r="I18" s="58" t="s">
         <v>371</v>
-      </c>
-      <c r="I18" s="58" t="s">
-        <v>372</v>
       </c>
       <c r="J18" s="58"/>
       <c r="K18" s="6"/>
@@ -8633,13 +8659,13 @@
         <v>97</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>123</v>
@@ -8648,25 +8674,25 @@
         <v>123</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J19" s="56" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K19" s="59" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L19" s="60" t="s">
         <v>110</v>
       </c>
       <c r="M19" s="59" t="s">
+        <v>427</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="39" customHeight="1">
@@ -8675,27 +8701,27 @@
         <v>98</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>376</v>
-      </c>
       <c r="J20" s="56" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K20" s="59" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L20" s="60" t="s">
         <v>110</v>
@@ -8715,16 +8741,16 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="K21" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L21" s="54" t="s">
         <v>110</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="39" customHeight="1">
@@ -8733,21 +8759,21 @@
         <v>97</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>123</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="39" customHeight="1">
@@ -8756,23 +8782,23 @@
         <v>98</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>123</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="39" customHeight="1">
@@ -8781,21 +8807,21 @@
         <v>99</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K24"/>
     </row>
@@ -8808,18 +8834,18 @@
         <v>1</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K25"/>
     </row>
@@ -8829,44 +8855,44 @@
         <v>102</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>435</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>436</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="39" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>415</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>416</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="39" customHeight="1">
@@ -8890,7 +8916,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="90" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J29" s="90"/>
       <c r="K29" s="90"/>
@@ -8917,7 +8943,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="57" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J31" s="61">
         <v>0.9</v>
@@ -8939,16 +8965,16 @@
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="57" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J32" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="K32" s="55" t="s">
         <v>386</v>
       </c>
-      <c r="K32" s="55" t="s">
-        <v>387</v>
-      </c>
       <c r="L32" s="55" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="39" customHeight="1">
@@ -8961,16 +8987,16 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="J33" s="55" t="s">
         <v>388</v>
       </c>
-      <c r="J33" s="55" t="s">
+      <c r="K33" s="55" t="s">
         <v>389</v>
       </c>
-      <c r="K33" s="55" t="s">
+      <c r="L33" s="55" t="s">
         <v>390</v>
-      </c>
-      <c r="L33" s="55" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="39" customHeight="1">
@@ -8983,13 +9009,13 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="57" t="s">
+        <v>391</v>
+      </c>
+      <c r="J34" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="K34" s="62" t="s">
         <v>392</v>
-      </c>
-      <c r="J34" s="55" t="s">
-        <v>402</v>
-      </c>
-      <c r="K34" s="62" t="s">
-        <v>393</v>
       </c>
       <c r="L34" s="55"/>
     </row>
@@ -9017,7 +9043,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="57" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J36" s="61">
         <v>0.5</v>
@@ -9040,16 +9066,16 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="57" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J37" s="55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K37" s="55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L37" s="55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
@@ -9064,16 +9090,16 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="57" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J38" s="55" t="s">
+        <v>397</v>
+      </c>
+      <c r="K38" s="55" t="s">
+        <v>389</v>
+      </c>
+      <c r="L38" s="55" t="s">
         <v>398</v>
-      </c>
-      <c r="K38" s="55" t="s">
-        <v>390</v>
-      </c>
-      <c r="L38" s="55" t="s">
-        <v>399</v>
       </c>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
@@ -9088,16 +9114,16 @@
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="J39" s="55" t="s">
+        <v>402</v>
+      </c>
+      <c r="K39" s="62" t="s">
         <v>423</v>
       </c>
-      <c r="J39" s="55" t="s">
-        <v>403</v>
-      </c>
-      <c r="K39" s="62" t="s">
-        <v>424</v>
-      </c>
       <c r="L39" s="62" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
@@ -9112,16 +9138,16 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="57" t="s">
+        <v>391</v>
+      </c>
+      <c r="J40" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="K40" s="62" t="s">
         <v>392</v>
       </c>
-      <c r="J40" s="55" t="s">
-        <v>402</v>
-      </c>
-      <c r="K40" s="62" t="s">
-        <v>393</v>
-      </c>
       <c r="L40" s="62" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
@@ -9152,7 +9178,7 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="57" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J42" s="61">
         <v>0.1</v>
@@ -9176,16 +9202,16 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="57" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J43" s="55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K43" s="55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L43" s="55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
@@ -9200,16 +9226,16 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="J44" s="55" t="s">
         <v>388</v>
       </c>
-      <c r="J44" s="55" t="s">
-        <v>389</v>
-      </c>
       <c r="K44" s="55" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L44" s="55" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
@@ -9224,10 +9250,10 @@
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="57" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J45" s="55" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K45" s="62"/>
       <c r="L45" s="55"/>
@@ -9260,7 +9286,7 @@
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="90" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J47" s="90"/>
       <c r="K47" s="90"/>
@@ -9291,7 +9317,7 @@
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="57" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J49" s="61">
         <v>0.5</v>
@@ -9315,16 +9341,16 @@
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="57" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J50" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K50" s="55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L50" s="55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
@@ -9339,16 +9365,16 @@
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="J51" s="55" t="s">
         <v>388</v>
       </c>
-      <c r="J51" s="55" t="s">
+      <c r="K51" s="55" t="s">
         <v>389</v>
       </c>
-      <c r="K51" s="55" t="s">
+      <c r="L51" s="55" t="s">
         <v>390</v>
-      </c>
-      <c r="L51" s="55" t="s">
-        <v>391</v>
       </c>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
@@ -9363,16 +9389,16 @@
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="57" t="s">
+        <v>391</v>
+      </c>
+      <c r="J52" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="K52" s="62" t="s">
         <v>392</v>
       </c>
-      <c r="J52" s="55" t="s">
-        <v>402</v>
-      </c>
-      <c r="K52" s="62" t="s">
-        <v>393</v>
-      </c>
       <c r="L52" s="62" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
@@ -9387,16 +9413,16 @@
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="J53" s="55" t="s">
+        <v>402</v>
+      </c>
+      <c r="K53" s="62" t="s">
         <v>423</v>
       </c>
-      <c r="J53" s="55" t="s">
-        <v>403</v>
-      </c>
-      <c r="K53" s="62" t="s">
-        <v>424</v>
-      </c>
       <c r="L53" s="62" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
@@ -9550,20 +9576,20 @@
   <sheetData>
     <row r="2" spans="2:10" ht="26">
       <c r="B2" s="65" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="66" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="C5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I5" s="68" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="2:10">
@@ -9571,13 +9597,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I7" s="67">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -9585,13 +9611,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I8" s="67">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="2:10">
@@ -9599,7 +9625,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="2:10">
@@ -9607,12 +9633,12 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="C12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="2:10">
@@ -9620,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="2:10">
@@ -9628,7 +9654,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="2:10">
@@ -9636,12 +9662,12 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="2:3">
@@ -9649,7 +9675,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="2:3">
@@ -9657,7 +9683,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -9665,7 +9691,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -9685,21 +9711,21 @@
   <sheetData>
     <row r="4" spans="2:5">
       <c r="B4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" t="s">
         <v>459</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>460</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>461</v>
-      </c>
-      <c r="E6" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -9713,7 +9739,7 @@
         <v>2925</v>
       </c>
       <c r="E8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F57B7A7-C879-D241-AEE7-1D32BC609854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072B3876-C9B7-EC4D-9F91-126434715310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="2" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="7" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Test sheet Similarity" sheetId="4" r:id="rId5"/>
     <sheet name="Test sheet LL" sheetId="7" r:id="rId6"/>
     <sheet name="Compiler" sheetId="8" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId8"/>
+    <sheet name="Examples" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="467">
   <si>
     <t>essere</t>
   </si>
@@ -1615,24 +1615,6 @@
     <t>isolate all the statements (across the nested structure) with duplication for conjuncts and subordinates, matching all entities</t>
   </si>
   <si>
-    <t>sentence</t>
-  </si>
-  <si>
-    <t>subject + properties</t>
-  </si>
-  <si>
-    <t>predicate + properties</t>
-  </si>
-  <si>
-    <t>direct + properties</t>
-  </si>
-  <si>
-    <t>ind (foreach type) + properties</t>
-  </si>
-  <si>
-    <t>100 + 2925</t>
-  </si>
-  <si>
     <t>v2&lt;=v1 ? 1 : v1</t>
   </si>
   <si>
@@ -1646,6 +1628,21 @@
   </si>
   <si>
     <t>max(v1, v2)</t>
+  </si>
+  <si>
+    <t>memory</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>find which release caused an issue</t>
+  </si>
+  <si>
+    <t>the release A went fine</t>
+  </si>
+  <si>
+    <t>the release B caused an issue</t>
   </si>
 </sst>
 </file>
@@ -2162,27 +2159,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2201,7 +2177,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2215,6 +2200,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2896,12 +2893,12 @@
       <c r="D30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="69" t="s">
+      <c r="E30" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
       <c r="I30" s="4" t="s">
         <v>340</v>
       </c>
@@ -2964,12 +2961,12 @@
       <c r="D36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="69" t="s">
+      <c r="E36" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="4"/>
@@ -3649,22 +3646,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="75" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="74"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="77"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3672,24 +3669,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="76" t="s">
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="69" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="78"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="71"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3742,28 +3739,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="83" t="s">
+      <c r="D9" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="79" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="71" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
+      <c r="K9" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="78"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="78"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3779,24 +3776,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="84"/>
-      <c r="D10" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="82" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="82"/>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -3812,24 +3809,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="84"/>
-      <c r="D11" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="71" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -3845,24 +3842,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="85"/>
-      <c r="D12" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="78"/>
+      <c r="M12" s="78"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="78"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -3883,22 +3880,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="74"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="77"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -3906,24 +3903,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="69" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="76" t="s">
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="69" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="78"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -3976,28 +3973,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="83" t="s">
+      <c r="D17" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="79" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="71" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
+      <c r="K17" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -4005,24 +4002,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="84"/>
-      <c r="D18" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -4030,24 +4027,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="84"/>
-      <c r="D19" s="79" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="82"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="83"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -4055,24 +4052,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="85"/>
-      <c r="D20" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="85"/>
-      <c r="K20" s="71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4083,46 +4080,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="75" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="73"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="74"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="77"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="76" t="s">
+      <c r="C23" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="76" t="s">
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="69" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="77"/>
-      <c r="P23" s="78"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4173,100 +4170,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="79" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="86" t="s">
+      <c r="D25" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="71" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
+      <c r="K25" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="78"/>
+      <c r="M25" s="78"/>
+      <c r="N25" s="78"/>
+      <c r="O25" s="78"/>
+      <c r="P25" s="78"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="84"/>
-      <c r="D26" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="82" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="82"/>
-      <c r="M26" s="82"/>
-      <c r="N26" s="82"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="82"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="83"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="83"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="83"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="84"/>
-      <c r="D27" s="79" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="82"/>
-      <c r="M27" s="82"/>
-      <c r="N27" s="82"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="82"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="83"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="83"/>
+      <c r="O27" s="83"/>
+      <c r="P27" s="83"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="85"/>
-      <c r="D28" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="71"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="78"/>
+      <c r="M28" s="78"/>
+      <c r="N28" s="78"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="78"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4276,46 +4273,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="72" t="s">
+      <c r="C30" s="75" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="74"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="76"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="77"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="76" t="s">
+      <c r="C31" s="69" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="76" t="s">
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="69" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="77"/>
-      <c r="L31" s="77"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="77"/>
-      <c r="O31" s="77"/>
-      <c r="P31" s="78"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4369,25 +4366,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="72" t="s">
+      <c r="D33" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="74"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="77"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="71" t="s">
+      <c r="K33" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
+      <c r="L33" s="78"/>
+      <c r="M33" s="78"/>
+      <c r="N33" s="78"/>
+      <c r="O33" s="78"/>
+      <c r="P33" s="78"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4401,19 +4398,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="75" t="s">
+      <c r="F36" s="85" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="75"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="85"/>
+      <c r="L36" s="85"/>
+      <c r="M36" s="85"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="85"/>
+      <c r="P36" s="85"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4591,7 +4588,7 @@
         <v>284</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -4602,7 +4599,7 @@
         <v>280</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -4657,7 +4654,7 @@
         <v>295</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -4665,10 +4662,10 @@
         <v>283</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -4709,18 +4706,18 @@
       </c>
     </row>
     <row r="65" spans="3:12">
-      <c r="C65" s="70" t="s">
+      <c r="C65" s="84" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="70"/>
-      <c r="E65" s="70"/>
-      <c r="F65" s="70"/>
-      <c r="G65" s="70"/>
-      <c r="H65" s="70"/>
-      <c r="I65" s="70"/>
-      <c r="J65" s="70"/>
-      <c r="K65" s="70"/>
-      <c r="L65" s="70"/>
+      <c r="D65" s="84"/>
+      <c r="E65" s="84"/>
+      <c r="F65" s="84"/>
+      <c r="G65" s="84"/>
+      <c r="H65" s="84"/>
+      <c r="I65" s="84"/>
+      <c r="J65" s="84"/>
+      <c r="K65" s="84"/>
+      <c r="L65" s="84"/>
     </row>
     <row r="66" spans="3:12">
       <c r="C66" s="19" t="b">
@@ -4878,18 +4875,18 @@
       <c r="G70" s="19"/>
     </row>
     <row r="71" spans="3:12">
-      <c r="C71" s="70" t="s">
+      <c r="C71" s="84" t="s">
         <v>287</v>
       </c>
-      <c r="D71" s="70"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="70"/>
-      <c r="H71" s="70"/>
-      <c r="I71" s="70"/>
-      <c r="J71" s="70"/>
-      <c r="K71" s="70"/>
-      <c r="L71" s="70"/>
+      <c r="D71" s="84"/>
+      <c r="E71" s="84"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="84"/>
+      <c r="H71" s="84"/>
+      <c r="I71" s="84"/>
+      <c r="J71" s="84"/>
+      <c r="K71" s="84"/>
+      <c r="L71" s="84"/>
     </row>
     <row r="72" spans="3:12">
       <c r="C72" s="19">
@@ -5212,18 +5209,18 @@
       </c>
     </row>
     <row r="81" spans="3:12">
-      <c r="C81" s="70" t="s">
+      <c r="C81" s="84" t="s">
         <v>298</v>
       </c>
-      <c r="D81" s="70"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="70"/>
-      <c r="G81" s="70"/>
-      <c r="H81" s="70"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="70"/>
-      <c r="K81" s="70"/>
-      <c r="L81" s="70"/>
+      <c r="D81" s="84"/>
+      <c r="E81" s="84"/>
+      <c r="F81" s="84"/>
+      <c r="G81" s="84"/>
+      <c r="H81" s="84"/>
+      <c r="I81" s="84"/>
+      <c r="J81" s="84"/>
+      <c r="K81" s="84"/>
+      <c r="L81" s="84"/>
     </row>
     <row r="82" spans="3:12">
       <c r="C82" s="19">
@@ -5737,6 +5734,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="K19:P19"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="J7:P7"/>
@@ -5753,38 +5782,6 @@
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9701,45 +9698,47 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DD2502-0F1B-8E4C-91C2-32C74D9C1A25}">
-  <dimension ref="B4:E8"/>
+  <dimension ref="B1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" customWidth="1"/>
+    <col min="2" max="2" width="3.6640625" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+    <row r="1" spans="2:3">
+      <c r="B1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3">
+      <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
       <c r="B6" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="C6" t="s">
-        <v>459</v>
-      </c>
-      <c r="D6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E6" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8">
-        <v>2925</v>
-      </c>
-      <c r="C8">
-        <v>2925</v>
-      </c>
-      <c r="D8">
-        <v>2925</v>
-      </c>
-      <c r="E8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072B3876-C9B7-EC4D-9F91-126434715310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C98456-67FB-8949-901F-672EA21032F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="7" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="8" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Test sheet LL" sheetId="7" r:id="rId6"/>
     <sheet name="Compiler" sheetId="8" r:id="rId7"/>
     <sheet name="Examples" sheetId="9" r:id="rId8"/>
+    <sheet name="Problems" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="475">
   <si>
     <t>essere</t>
   </si>
@@ -1615,6 +1616,9 @@
     <t>isolate all the statements (across the nested structure) with duplication for conjuncts and subordinates, matching all entities</t>
   </si>
   <si>
+    <t>sentence</t>
+  </si>
+  <si>
     <t>v2&lt;=v1 ? 1 : v1</t>
   </si>
   <si>
@@ -1643,6 +1647,27 @@
   </si>
   <si>
     <t>the release B caused an issue</t>
+  </si>
+  <si>
+    <t>find x</t>
+  </si>
+  <si>
+    <t>x = release [which] caused a issue</t>
+  </si>
+  <si>
+    <t>think</t>
+  </si>
+  <si>
+    <t>copy</t>
+  </si>
+  <si>
+    <t>a cat is cute to fulfill evolution and to make happy humans and other cats</t>
+  </si>
+  <si>
+    <t>I'm happy</t>
+  </si>
+  <si>
+    <t>problem</t>
   </si>
 </sst>
 </file>
@@ -1983,7 +2008,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2225,6 +2250,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4588,7 +4614,7 @@
         <v>284</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -4599,7 +4625,7 @@
         <v>280</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -4654,7 +4680,7 @@
         <v>295</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -4662,10 +4688,10 @@
         <v>283</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -9698,47 +9724,108 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DD2502-0F1B-8E4C-91C2-32C74D9C1A25}">
-  <dimension ref="B1:C6"/>
+  <dimension ref="B1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.1640625" customWidth="1"/>
     <col min="2" max="2" width="3.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3">
+    <row r="1" spans="2:4">
       <c r="B1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3">
+        <v>463</v>
+      </c>
+      <c r="D1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
       <c r="B2" t="s">
         <v>393</v>
       </c>
       <c r="C2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>394</v>
       </c>
       <c r="C3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>393</v>
       </c>
       <c r="C6" t="s">
-        <v>464</v>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="C8" t="s">
+        <v>468</v>
+      </c>
+      <c r="D8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="C9" t="s">
+        <v>469</v>
+      </c>
+      <c r="D9" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" t="s">
+        <v>394</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18655DDE-A2FE-0D45-A488-8AC5E3F87096}">
+  <dimension ref="A2:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="B2" s="91" t="s">
+        <v>457</v>
+      </c>
+      <c r="H2" s="91" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C98456-67FB-8949-901F-672EA21032F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5338B88-3D1B-A545-BE06-000EDDBACC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="8" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="9" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Compiler" sheetId="8" r:id="rId7"/>
     <sheet name="Examples" sheetId="9" r:id="rId8"/>
     <sheet name="Problems" sheetId="10" r:id="rId9"/>
+    <sheet name="Next step" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="491">
   <si>
     <t>essere</t>
   </si>
@@ -1668,6 +1669,54 @@
   </si>
   <si>
     <t>problem</t>
+  </si>
+  <si>
+    <t>I had a long session of thinking with myself and I reached many conclusions, that will help us defining the next step better.</t>
+  </si>
+  <si>
+    <t>1. Now we have axioms and theorems in our memory (plus the memory, which is just the log of what are tokeniko's inputs and outputs): axioms set the common sense truths, without requiring any demonstration.</t>
+  </si>
+  <si>
+    <t>2. I feel the need to introduce another collection / entity: definitions. In what definitions, axioms and theorems differs? The following points describe how</t>
+  </si>
+  <si>
+    <t>3. Definitions should be strictly single sentence statements arbitrarily defining tokeniko's "rules and vocabulary": for example "truth is not falsehood" (defines one core concept of the logic) or "a thing is equal to itself" (defines basically what equal means) or "words carry meaning" (defines what semantic is). TKZipContent is perfect for it, because it's not about relating concepts through operator but it's about defining our playground (with purely semantic expressions).</t>
+  </si>
+  <si>
+    <t>4. Axioms, instead, are representable by TKZip, because they define general truths in a broader way than the definitions: they establish relations between definitions (or between pure vocabulary semantic). Like "I think because I am". Or "A equal B and A equal C implies A equal C. Like definitions they don't need demonstration, but we trust them as true.</t>
+  </si>
+  <si>
+    <t>5. Theorems are statements that provide a demonstration using the previous items (axioms and definitions) and math (how logical / fuzzy operators work, algebra, etc), hardwired in the code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. The current collection axioms is therefore wrong, but we will get to this point later, once we are done with the coding. </t>
+  </si>
+  <si>
+    <t>Now, what the evaluator should do and why? Here's my bullet point list:</t>
+  </si>
+  <si>
+    <t>Here's a bullet point list, to highlight the core of my first points.</t>
+  </si>
+  <si>
+    <t>1. it should be able to compare the components of an input statement (so each and every TKZipContent) with the definitions, with an output fuzzy representing the "truth" of the part of the statement: from 0.0 (perfect opposite match with one item) to 1.0 (perfect match with one item) passing through every possible intermediate value (for the best match or opposite match).  When there is no match nor opposite match at all, the value is completely neutral 0.5</t>
+  </si>
+  <si>
+    <t>2. it should be able to compare the relation between the matches of the input statements eventually found in axioms or theorems: the output can be a TRUTH value (he finds all the matches, with some degree of truth, both in the single statements and the relations). OR the output can be a neutral truth value (0.5) plus the aknowledgement the there is not enough knowledge and some "variable" is missing, keeping track of what is missing (if he misses some of the matches). OR (last case) a truth value (0) BUT plus the flag "logic inconsistency" (and where) because the statement violate a rule of the math / logic (the one hardwired, basically the math behind our fuzzy operators), like (A eq B) IMPLY (B noteq A) (or any misuse of the logic).</t>
+  </si>
+  <si>
+    <t>1. build the data-modeling / BL / api for the definitions</t>
+  </si>
+  <si>
+    <t>2. refactor the current logic to make some cleansing, like evaluator.py becomes a sub directory (as we did for compiler) with sub modules separated. The cuurrent operators.py should be there, as well</t>
+  </si>
+  <si>
+    <t>3. check our current logic of the evaluator to fulfill the previous points I just set</t>
+  </si>
+  <si>
+    <t>4. for all of this make a plan, no direct edits :)</t>
+  </si>
+  <si>
+    <t>In order to accomplish this goal we should</t>
   </si>
 </sst>
 </file>
@@ -2184,6 +2233,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2202,16 +2273,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2226,18 +2288,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2250,7 +2300,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -2919,12 +2968,12 @@
       <c r="D30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="86" t="s">
+      <c r="E30" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
       <c r="I30" s="4" t="s">
         <v>340</v>
       </c>
@@ -2987,12 +3036,12 @@
       <c r="D36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="86" t="s">
+      <c r="E36" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="86"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="86"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="4"/>
@@ -3202,6 +3251,100 @@
     <mergeCell ref="E36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9ACCF04-0EAB-754F-B918-77C56774BDCB}">
+  <dimension ref="B2:B22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -3672,22 +3815,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="73" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="77"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="75"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3695,24 +3838,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="77" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="69" t="s">
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="77" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="71"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="79"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3765,28 +3908,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="84" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="79" t="s">
+      <c r="D9" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="84" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
+      <c r="K9" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3802,16 +3945,16 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="80"/>
-      <c r="D10" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="80"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="85"/>
       <c r="K10" s="83" t="b">
         <v>0</v>
       </c>
@@ -3835,24 +3978,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="80"/>
-      <c r="D11" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="78"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -3868,24 +4011,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="81"/>
-      <c r="D12" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="78"/>
-      <c r="M12" s="78"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="78"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -3906,22 +4049,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="73" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="76"/>
-      <c r="O14" s="76"/>
-      <c r="P14" s="77"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="75"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -3929,24 +4072,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="77" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="69" t="s">
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="77" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="71"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="79"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -3999,28 +4142,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="84" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="79" t="s">
+      <c r="D17" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="84" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
+      <c r="K17" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -4028,24 +4171,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="80"/>
-      <c r="D18" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -4053,16 +4196,16 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="80"/>
-      <c r="D19" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="80"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="85"/>
       <c r="K19" s="83" t="b">
         <v>1</v>
       </c>
@@ -4078,24 +4221,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="81"/>
-      <c r="D20" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="78"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="78"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4106,46 +4249,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="73" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="76"/>
-      <c r="P22" s="77"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="75"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="77" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="69" t="s">
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="77" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="71"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="78"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="79"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4196,44 +4339,44 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="84" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="82" t="s">
+      <c r="D25" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
-      <c r="N25" s="78"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
+      <c r="K25" s="72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="80"/>
-      <c r="D26" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="80"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="85"/>
       <c r="K26" s="83" t="b">
         <v>0</v>
       </c>
@@ -4248,16 +4391,16 @@
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="80"/>
-      <c r="D27" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="80"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="85"/>
       <c r="K27" s="83" t="b">
         <v>1</v>
       </c>
@@ -4272,24 +4415,24 @@
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="81"/>
-      <c r="D28" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4299,46 +4442,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="75" t="s">
+      <c r="C30" s="73" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="77"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="75"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="77" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="69" t="s">
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="77" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="70"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="71"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="78"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="78"/>
+      <c r="P31" s="79"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4392,25 +4535,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="D33" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="77"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="75"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="78" t="s">
+      <c r="K33" s="72" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="78"/>
-      <c r="M33" s="78"/>
-      <c r="N33" s="78"/>
-      <c r="O33" s="78"/>
-      <c r="P33" s="78"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4424,19 +4567,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="85" t="s">
+      <c r="F36" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="85"/>
-      <c r="L36" s="85"/>
-      <c r="M36" s="85"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
-      <c r="P36" s="85"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="76"/>
+      <c r="M36" s="76"/>
+      <c r="N36" s="76"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4732,18 +4875,18 @@
       </c>
     </row>
     <row r="65" spans="3:12">
-      <c r="C65" s="84" t="s">
+      <c r="C65" s="71" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="84"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="84"/>
-      <c r="G65" s="84"/>
-      <c r="H65" s="84"/>
-      <c r="I65" s="84"/>
-      <c r="J65" s="84"/>
-      <c r="K65" s="84"/>
-      <c r="L65" s="84"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="71"/>
+      <c r="K65" s="71"/>
+      <c r="L65" s="71"/>
     </row>
     <row r="66" spans="3:12">
       <c r="C66" s="19" t="b">
@@ -4901,18 +5044,18 @@
       <c r="G70" s="19"/>
     </row>
     <row r="71" spans="3:12">
-      <c r="C71" s="84" t="s">
+      <c r="C71" s="71" t="s">
         <v>287</v>
       </c>
-      <c r="D71" s="84"/>
-      <c r="E71" s="84"/>
-      <c r="F71" s="84"/>
-      <c r="G71" s="84"/>
-      <c r="H71" s="84"/>
-      <c r="I71" s="84"/>
-      <c r="J71" s="84"/>
-      <c r="K71" s="84"/>
-      <c r="L71" s="84"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="71"/>
+      <c r="F71" s="71"/>
+      <c r="G71" s="71"/>
+      <c r="H71" s="71"/>
+      <c r="I71" s="71"/>
+      <c r="J71" s="71"/>
+      <c r="K71" s="71"/>
+      <c r="L71" s="71"/>
     </row>
     <row r="72" spans="3:12">
       <c r="C72" s="19">
@@ -5235,18 +5378,18 @@
       </c>
     </row>
     <row r="81" spans="3:12">
-      <c r="C81" s="84" t="s">
+      <c r="C81" s="71" t="s">
         <v>298</v>
       </c>
-      <c r="D81" s="84"/>
-      <c r="E81" s="84"/>
-      <c r="F81" s="84"/>
-      <c r="G81" s="84"/>
-      <c r="H81" s="84"/>
-      <c r="I81" s="84"/>
-      <c r="J81" s="84"/>
-      <c r="K81" s="84"/>
-      <c r="L81" s="84"/>
+      <c r="D81" s="71"/>
+      <c r="E81" s="71"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="71"/>
+      <c r="I81" s="71"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="71"/>
+      <c r="L81" s="71"/>
     </row>
     <row r="82" spans="3:12">
       <c r="C82" s="19">
@@ -5760,22 +5903,22 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C30:P30"/>
     <mergeCell ref="C6:P6"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="J25:J28"/>
@@ -5792,22 +5935,22 @@
     <mergeCell ref="K17:P17"/>
     <mergeCell ref="K18:P18"/>
     <mergeCell ref="K19:P19"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="K20:P20"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5901,62 +6044,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
     </row>
     <row r="3" spans="2:33">
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
       <c r="M3" s="31"/>
     </row>
     <row r="4" spans="2:33">
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
     </row>
     <row r="5" spans="2:33">
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
     </row>
     <row r="6" spans="2:33">
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="O6" s="87" t="s">
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="O6" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="87"/>
-      <c r="Q6" s="87"/>
-      <c r="R6" s="87"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="88"/>
+      <c r="R6" s="88"/>
     </row>
     <row r="7" spans="2:33">
-      <c r="O7" s="87"/>
-      <c r="P7" s="87"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="87"/>
+      <c r="O7" s="88"/>
+      <c r="P7" s="88"/>
+      <c r="Q7" s="88"/>
+      <c r="R7" s="88"/>
     </row>
     <row r="8" spans="2:33">
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="O8" s="87"/>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="89"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
     </row>
     <row r="9" spans="2:33">
       <c r="B9" s="33" t="s">
@@ -5987,10 +6130,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="31"/>
-      <c r="O9" s="87"/>
-      <c r="P9" s="87"/>
-      <c r="Q9" s="87"/>
-      <c r="R9" s="87"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
     </row>
     <row r="10" spans="2:33">
       <c r="B10" s="31" t="s">
@@ -6020,10 +6163,10 @@
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="87"/>
-      <c r="P10" s="87"/>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="87"/>
+      <c r="O10" s="88"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
+      <c r="R10" s="88"/>
     </row>
     <row r="11" spans="2:33">
       <c r="B11" s="31" t="s">
@@ -6892,12 +7035,12 @@
       </c>
     </row>
     <row r="25" spans="2:33">
-      <c r="B25" s="87" t="s">
+      <c r="B25" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
       <c r="O25" s="2" t="s">
         <v>23</v>
       </c>
@@ -6966,10 +7109,10 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1">
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
       <c r="N26" s="34" t="s">
         <v>23</v>
       </c>
@@ -7040,10 +7183,10 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1">
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
       <c r="N27" s="34" t="s">
         <v>24</v>
       </c>
@@ -7114,10 +7257,10 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1">
-      <c r="B28" s="87"/>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
       <c r="N28" s="34" t="s">
         <v>25</v>
       </c>
@@ -7188,10 +7331,10 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1">
-      <c r="B29" s="87"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
       <c r="N29" s="34" t="s">
         <v>27</v>
       </c>
@@ -8675,7 +8818,7 @@
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="39" customHeight="1">
-      <c r="A19" s="89">
+      <c r="A19" s="90">
         <v>2</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -8719,7 +8862,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="39" customHeight="1">
-      <c r="A20" s="89"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="6" t="s">
         <v>98</v>
       </c>
@@ -8938,12 +9081,12 @@
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="90" t="s">
+      <c r="I29" s="91" t="s">
         <v>418</v>
       </c>
-      <c r="J29" s="90"/>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
+      <c r="J29" s="91"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="91"/>
     </row>
     <row r="30" spans="1:15" ht="39" customHeight="1">
       <c r="A30" s="6"/>
@@ -9308,12 +9451,12 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="90" t="s">
+      <c r="I47" s="91" t="s">
         <v>419</v>
       </c>
-      <c r="J47" s="90"/>
-      <c r="K47" s="90"/>
-      <c r="L47" s="90"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="91"/>
+      <c r="L47" s="91"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
@@ -9805,10 +9948,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="69" t="s">
         <v>457</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="69" t="s">
         <v>474</v>
       </c>
     </row>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5338B88-3D1B-A545-BE06-000EDDBACC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968B2943-EE54-E149-BA60-3239CC634F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="9" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="10" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Examples" sheetId="9" r:id="rId8"/>
     <sheet name="Problems" sheetId="10" r:id="rId9"/>
     <sheet name="Next step" sheetId="11" r:id="rId10"/>
+    <sheet name="Inconsistencies" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="513">
   <si>
     <t>essere</t>
   </si>
@@ -1717,6 +1718,73 @@
   </si>
   <si>
     <t>In order to accomplish this goal we should</t>
+  </si>
+  <si>
+    <t>a eq b imply a noteq b</t>
+  </si>
+  <si>
+    <t>1-compare</t>
+  </si>
+  <si>
+    <t>a noteq b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compare </t>
+  </si>
+  <si>
+    <t>a eq b</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>1 if t1 &lt;t2 else t2</t>
+  </si>
+  <si>
+    <t>t-res</t>
+  </si>
+  <si>
+    <t>fuzzy result</t>
+  </si>
+  <si>
+    <t>case 1</t>
+  </si>
+  <si>
+    <t>we know a and b</t>
+  </si>
+  <si>
+    <t>case 1.a</t>
+  </si>
+  <si>
+    <t>a) the statement is false, because it's logically inconsistent</t>
+  </si>
+  <si>
+    <t>case 1.b</t>
+  </si>
+  <si>
+    <t>we don't find a eq b imply a noteq b -&gt; we calculate</t>
+  </si>
+  <si>
+    <t>we find a eq b imply a noteq b -&gt; we think it's true but we calculate to double check if we have an axiom or theorem logically inconsistent</t>
+  </si>
+  <si>
+    <t>case 2</t>
+  </si>
+  <si>
+    <t>we don't know a and b</t>
+  </si>
+  <si>
+    <t>a) the statement is NOT 1, -&gt; because it's logically inconsistent and we remove our axiom / theorem</t>
+  </si>
+  <si>
+    <t>2a and 2b, as before, we calculate</t>
+  </si>
+  <si>
+    <t>A note: of course we shouldn't have a eq b imply a noteq b as axiom or theorem (because otherwise we did something logically wrong at the beginning or during the thinking process)</t>
+  </si>
+  <si>
+    <t>So we can simplify: wheter we know or we don't know the values of the vector, we endup discovering that the expression violates logic (a eq b imply a noteq b) 
+because we have HARDWIRED the logic operations (because we consider the logic tokeniko first truth)</t>
   </si>
 </sst>
 </file>
@@ -2057,7 +2125,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2237,24 +2305,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2273,7 +2323,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2288,6 +2347,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2299,6 +2367,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3348,6 +3422,273 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA10A9B-574C-5441-8052-4B0D96BCF7B8}">
+  <dimension ref="B2:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="G3" s="67" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="C4" s="63" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>494</v>
+      </c>
+      <c r="G4" s="67">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="C5" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>492</v>
+      </c>
+      <c r="G5" s="67">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="67"/>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
+        <v>502</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>505</v>
+      </c>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="67"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="C8" s="63"/>
+      <c r="D8" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="63" t="s">
+        <v>496</v>
+      </c>
+      <c r="F8" s="63"/>
+      <c r="G8" s="67" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="C9" s="63" t="s">
+        <v>491</v>
+      </c>
+      <c r="D9" s="63">
+        <v>0.95</v>
+      </c>
+      <c r="E9" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="G9" s="67">
+        <v>0.05</v>
+      </c>
+      <c r="H9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="s">
+        <v>504</v>
+      </c>
+      <c r="C11" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="C12" s="63"/>
+      <c r="D12" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>496</v>
+      </c>
+      <c r="F12" s="63"/>
+      <c r="G12" s="67" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="C13" s="63" t="s">
+        <v>491</v>
+      </c>
+      <c r="D13" s="63">
+        <v>0.95</v>
+      </c>
+      <c r="E13" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="G13" s="67">
+        <v>0.05</v>
+      </c>
+      <c r="H13" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C15" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="G16" s="67" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8">
+      <c r="C17" s="63" t="s">
+        <v>495</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>494</v>
+      </c>
+      <c r="G17" s="67">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8">
+      <c r="C18" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>492</v>
+      </c>
+      <c r="G18" s="67">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8">
+      <c r="C20" s="92" t="s">
+        <v>510</v>
+      </c>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="67"/>
+    </row>
+    <row r="21" spans="3:8">
+      <c r="C21" s="63"/>
+      <c r="D21" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>496</v>
+      </c>
+      <c r="F21" s="63"/>
+      <c r="G21" s="67" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8">
+      <c r="C22" s="63" t="s">
+        <v>491</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="G22" s="67">
+        <v>0.5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" ht="43" customHeight="1">
+      <c r="C24" s="93" t="s">
+        <v>511</v>
+      </c>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+    </row>
+    <row r="25" spans="3:8" ht="80" customHeight="1">
+      <c r="C25" s="93" t="s">
+        <v>512</v>
+      </c>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C24:G24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FCF69A-7541-8F49-8917-87CA28DC0269}">
   <dimension ref="B2:M42"/>
@@ -3815,22 +4156,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="77" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="75"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="78"/>
+      <c r="M6" s="78"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="79"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -3838,24 +4179,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="77" t="s">
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="79"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="73"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -3908,28 +4249,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="84" t="s">
+      <c r="D9" s="77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="81" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
+      <c r="K9" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="80"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -3945,24 +4286,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="85"/>
-      <c r="D10" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -3978,24 +4319,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="85"/>
-      <c r="D11" s="73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -4011,24 +4352,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="86"/>
-      <c r="D12" s="73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="80"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="80"/>
+      <c r="O12" s="80"/>
+      <c r="P12" s="80"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -4049,22 +4390,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="77" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="75"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="79"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -4072,24 +4413,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="77" t="s">
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="79"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="73"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -4142,28 +4483,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="84" t="s">
+      <c r="C17" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="84" t="s">
+      <c r="D17" s="77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="81" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
+      <c r="K17" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="80"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="80"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -4171,24 +4512,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="85"/>
-      <c r="D18" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -4196,24 +4537,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="85"/>
-      <c r="D19" s="80" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="85"/>
-      <c r="K19" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="85"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -4221,24 +4562,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="86"/>
-      <c r="D20" s="73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="72"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4249,46 +4590,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="77" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="75"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="78"/>
+      <c r="M22" s="78"/>
+      <c r="N22" s="78"/>
+      <c r="O22" s="78"/>
+      <c r="P22" s="79"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="77" t="s">
+      <c r="C23" s="71" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="77" t="s">
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="71" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="79"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="73"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4339,100 +4680,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="84" t="s">
+      <c r="C25" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="87" t="s">
+      <c r="D25" s="77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="84" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="72" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
+      <c r="K25" s="80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="85"/>
-      <c r="D26" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="82"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="83"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="85"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="85"/>
-      <c r="D27" s="80" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="83"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="85"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="86"/>
-      <c r="D28" s="73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="78"/>
+      <c r="F28" s="78"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="80"/>
+      <c r="M28" s="80"/>
+      <c r="N28" s="80"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="80"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4442,46 +4783,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="73" t="s">
+      <c r="C30" s="77" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="75"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="78"/>
+      <c r="M30" s="78"/>
+      <c r="N30" s="78"/>
+      <c r="O30" s="78"/>
+      <c r="P30" s="79"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="71" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="77" t="s">
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="71" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="79"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="73"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4535,25 +4876,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="73" t="s">
+      <c r="D33" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="75"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="79"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="72" t="s">
+      <c r="K33" s="80" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="72"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="80"/>
+      <c r="P33" s="80"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4567,19 +4908,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="76" t="s">
+      <c r="F36" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="76"/>
-      <c r="M36" s="76"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="76"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="87"/>
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="87"/>
+      <c r="N36" s="87"/>
+      <c r="O36" s="87"/>
+      <c r="P36" s="87"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -4875,18 +5216,18 @@
       </c>
     </row>
     <row r="65" spans="3:12">
-      <c r="C65" s="71" t="s">
+      <c r="C65" s="86" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="71"/>
-      <c r="E65" s="71"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="71"/>
-      <c r="H65" s="71"/>
-      <c r="I65" s="71"/>
-      <c r="J65" s="71"/>
-      <c r="K65" s="71"/>
-      <c r="L65" s="71"/>
+      <c r="D65" s="86"/>
+      <c r="E65" s="86"/>
+      <c r="F65" s="86"/>
+      <c r="G65" s="86"/>
+      <c r="H65" s="86"/>
+      <c r="I65" s="86"/>
+      <c r="J65" s="86"/>
+      <c r="K65" s="86"/>
+      <c r="L65" s="86"/>
     </row>
     <row r="66" spans="3:12">
       <c r="C66" s="19" t="b">
@@ -5044,18 +5385,18 @@
       <c r="G70" s="19"/>
     </row>
     <row r="71" spans="3:12">
-      <c r="C71" s="71" t="s">
+      <c r="C71" s="86" t="s">
         <v>287</v>
       </c>
-      <c r="D71" s="71"/>
-      <c r="E71" s="71"/>
-      <c r="F71" s="71"/>
-      <c r="G71" s="71"/>
-      <c r="H71" s="71"/>
-      <c r="I71" s="71"/>
-      <c r="J71" s="71"/>
-      <c r="K71" s="71"/>
-      <c r="L71" s="71"/>
+      <c r="D71" s="86"/>
+      <c r="E71" s="86"/>
+      <c r="F71" s="86"/>
+      <c r="G71" s="86"/>
+      <c r="H71" s="86"/>
+      <c r="I71" s="86"/>
+      <c r="J71" s="86"/>
+      <c r="K71" s="86"/>
+      <c r="L71" s="86"/>
     </row>
     <row r="72" spans="3:12">
       <c r="C72" s="19">
@@ -5378,18 +5719,18 @@
       </c>
     </row>
     <row r="81" spans="3:12">
-      <c r="C81" s="71" t="s">
+      <c r="C81" s="86" t="s">
         <v>298</v>
       </c>
-      <c r="D81" s="71"/>
-      <c r="E81" s="71"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="71"/>
-      <c r="I81" s="71"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="71"/>
-      <c r="L81" s="71"/>
+      <c r="D81" s="86"/>
+      <c r="E81" s="86"/>
+      <c r="F81" s="86"/>
+      <c r="G81" s="86"/>
+      <c r="H81" s="86"/>
+      <c r="I81" s="86"/>
+      <c r="J81" s="86"/>
+      <c r="K81" s="86"/>
+      <c r="L81" s="86"/>
     </row>
     <row r="82" spans="3:12">
       <c r="C82" s="19">
@@ -5903,6 +6244,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="K19:P19"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="J7:P7"/>
@@ -5919,38 +6292,6 @@
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
